--- a/gstdatabase/GSTR-1-2020-2021.xlsx
+++ b/gstdatabase/GSTR-1-2020-2021.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Feb-26\GST Statistics Downloads 28th Feb 26\Downloads\GSTR 1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\May-26\GST Statistics Downloads 31st May 26\Downloads\GSTR 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDFC22FC-1788-4F25-825E-0319B78D9027}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BA68264-70BB-4A83-9B15-3B879753E0DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -182,10 +182,10 @@
     <t>Andaman and Nicobar Islands</t>
   </si>
   <si>
-    <t>Data Considered upto 28th Feb 2026</t>
+    <t>Data Considered upto 31st May 2026</t>
   </si>
   <si>
-    <t>Filing %age as on 28th Feb 2026</t>
+    <t>Filing %age as on 31st May 2026</t>
   </si>
 </sst>
 </file>
@@ -440,14 +440,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="17" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -463,12 +469,6 @@
     </xf>
     <xf numFmtId="17" fontId="3" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="9">
@@ -767,13 +767,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
     </row>
     <row r="2" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -783,10 +783,10 @@
       <c r="E2" s="1"/>
     </row>
     <row r="3" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="34" t="s">
+      <c r="A3" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="34"/>
+      <c r="B3" s="36"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
@@ -813,107 +813,107 @@
       <c r="L4" s="1"/>
     </row>
     <row r="5" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="34" t="s">
+      <c r="A5" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="B5" s="34"/>
-      <c r="C5" s="34"/>
+      <c r="B5" s="36"/>
+      <c r="C5" s="36"/>
     </row>
     <row r="8" spans="1:62" s="26" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="35" t="s">
+      <c r="A8" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="B8" s="33" t="s">
+      <c r="B8" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="36">
+      <c r="C8" s="38">
         <v>43922</v>
       </c>
-      <c r="D8" s="37"/>
-      <c r="E8" s="37"/>
-      <c r="F8" s="37"/>
-      <c r="G8" s="38"/>
-      <c r="H8" s="32">
+      <c r="D8" s="39"/>
+      <c r="E8" s="39"/>
+      <c r="F8" s="39"/>
+      <c r="G8" s="40"/>
+      <c r="H8" s="33">
         <v>43952</v>
       </c>
-      <c r="I8" s="33"/>
-      <c r="J8" s="33"/>
-      <c r="K8" s="33"/>
-      <c r="L8" s="33"/>
-      <c r="M8" s="32">
+      <c r="I8" s="34"/>
+      <c r="J8" s="34"/>
+      <c r="K8" s="34"/>
+      <c r="L8" s="34"/>
+      <c r="M8" s="33">
         <v>43983</v>
       </c>
-      <c r="N8" s="33"/>
-      <c r="O8" s="33"/>
-      <c r="P8" s="33"/>
-      <c r="Q8" s="33"/>
-      <c r="R8" s="32">
+      <c r="N8" s="34"/>
+      <c r="O8" s="34"/>
+      <c r="P8" s="34"/>
+      <c r="Q8" s="34"/>
+      <c r="R8" s="33">
         <v>44013</v>
       </c>
-      <c r="S8" s="33"/>
-      <c r="T8" s="33"/>
-      <c r="U8" s="33"/>
-      <c r="V8" s="33"/>
-      <c r="W8" s="32">
+      <c r="S8" s="34"/>
+      <c r="T8" s="34"/>
+      <c r="U8" s="34"/>
+      <c r="V8" s="34"/>
+      <c r="W8" s="33">
         <v>44044</v>
       </c>
-      <c r="X8" s="33"/>
-      <c r="Y8" s="33"/>
-      <c r="Z8" s="33"/>
-      <c r="AA8" s="33"/>
-      <c r="AB8" s="32">
+      <c r="X8" s="34"/>
+      <c r="Y8" s="34"/>
+      <c r="Z8" s="34"/>
+      <c r="AA8" s="34"/>
+      <c r="AB8" s="33">
         <v>44075</v>
       </c>
-      <c r="AC8" s="33"/>
-      <c r="AD8" s="33"/>
-      <c r="AE8" s="33"/>
-      <c r="AF8" s="33"/>
-      <c r="AG8" s="32">
+      <c r="AC8" s="34"/>
+      <c r="AD8" s="34"/>
+      <c r="AE8" s="34"/>
+      <c r="AF8" s="34"/>
+      <c r="AG8" s="33">
         <v>44105</v>
       </c>
-      <c r="AH8" s="33"/>
-      <c r="AI8" s="33"/>
-      <c r="AJ8" s="33"/>
-      <c r="AK8" s="33"/>
-      <c r="AL8" s="32">
+      <c r="AH8" s="34"/>
+      <c r="AI8" s="34"/>
+      <c r="AJ8" s="34"/>
+      <c r="AK8" s="34"/>
+      <c r="AL8" s="33">
         <v>44136</v>
       </c>
-      <c r="AM8" s="33"/>
-      <c r="AN8" s="33"/>
-      <c r="AO8" s="33"/>
-      <c r="AP8" s="33"/>
-      <c r="AQ8" s="32">
+      <c r="AM8" s="34"/>
+      <c r="AN8" s="34"/>
+      <c r="AO8" s="34"/>
+      <c r="AP8" s="34"/>
+      <c r="AQ8" s="33">
         <v>44166</v>
       </c>
-      <c r="AR8" s="33"/>
-      <c r="AS8" s="33"/>
-      <c r="AT8" s="33"/>
-      <c r="AU8" s="33"/>
-      <c r="AV8" s="32">
+      <c r="AR8" s="34"/>
+      <c r="AS8" s="34"/>
+      <c r="AT8" s="34"/>
+      <c r="AU8" s="34"/>
+      <c r="AV8" s="33">
         <v>44197</v>
       </c>
-      <c r="AW8" s="33"/>
-      <c r="AX8" s="33"/>
-      <c r="AY8" s="33"/>
-      <c r="AZ8" s="33"/>
-      <c r="BA8" s="32">
+      <c r="AW8" s="34"/>
+      <c r="AX8" s="34"/>
+      <c r="AY8" s="34"/>
+      <c r="AZ8" s="34"/>
+      <c r="BA8" s="33">
         <v>44228</v>
       </c>
-      <c r="BB8" s="33"/>
-      <c r="BC8" s="33"/>
-      <c r="BD8" s="33"/>
-      <c r="BE8" s="33"/>
-      <c r="BF8" s="32">
+      <c r="BB8" s="34"/>
+      <c r="BC8" s="34"/>
+      <c r="BD8" s="34"/>
+      <c r="BE8" s="34"/>
+      <c r="BF8" s="33">
         <v>44256</v>
       </c>
-      <c r="BG8" s="33"/>
-      <c r="BH8" s="33"/>
-      <c r="BI8" s="33"/>
-      <c r="BJ8" s="33"/>
+      <c r="BG8" s="34"/>
+      <c r="BH8" s="34"/>
+      <c r="BI8" s="34"/>
+      <c r="BJ8" s="34"/>
     </row>
     <row r="9" spans="1:62" s="26" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="35"/>
-      <c r="B9" s="33"/>
+      <c r="A9" s="37"/>
+      <c r="B9" s="34"/>
       <c r="C9" s="27" t="s">
         <v>4</v>
       </c>
@@ -1195,14 +1195,14 @@
       </c>
       <c r="AD10" s="9">
         <f>AE10-AC10</f>
-        <v>41495</v>
+        <v>41497</v>
       </c>
       <c r="AE10" s="8">
-        <v>74581</v>
+        <v>74583</v>
       </c>
       <c r="AF10" s="10">
         <f>AE10/AB10</f>
-        <v>0.84384829490167679</v>
+        <v>0.84387092394378949</v>
       </c>
       <c r="AG10" s="5">
         <v>40367</v>
@@ -1356,14 +1356,14 @@
       </c>
       <c r="O11" s="9">
         <f t="shared" ref="O11:O48" si="4">P11-N11</f>
-        <v>40630</v>
+        <v>40631</v>
       </c>
       <c r="P11" s="8">
-        <v>78755</v>
+        <v>78756</v>
       </c>
       <c r="Q11" s="10">
         <f t="shared" ref="Q11:Q48" si="5">P11/M11</f>
-        <v>0.92321669304261178</v>
+        <v>0.92322841568489533</v>
       </c>
       <c r="R11" s="5">
         <v>34872</v>
@@ -1407,14 +1407,14 @@
       </c>
       <c r="AD11" s="9">
         <f t="shared" ref="AD11:AD48" si="10">AE11-AC11</f>
-        <v>27330</v>
+        <v>27333</v>
       </c>
       <c r="AE11" s="8">
-        <v>81749</v>
+        <v>81752</v>
       </c>
       <c r="AF11" s="10">
         <f t="shared" ref="AF11:AF48" si="11">AE11/AB11</f>
-        <v>0.9146229581561871</v>
+        <v>0.91465652271201614</v>
       </c>
       <c r="AG11" s="5">
         <v>29840</v>
@@ -1458,14 +1458,14 @@
       </c>
       <c r="AS11" s="9">
         <f t="shared" ref="AS11:AS48" si="16">AT11-AR11</f>
-        <v>16646</v>
+        <v>16647</v>
       </c>
       <c r="AT11" s="8">
-        <v>84383</v>
+        <v>84384</v>
       </c>
       <c r="AU11" s="10">
         <f t="shared" ref="AU11:AU48" si="17">AT11/AQ11</f>
-        <v>0.92693938528461894</v>
+        <v>0.92695037019135706</v>
       </c>
       <c r="AV11" s="22">
         <v>40247</v>
@@ -1475,14 +1475,14 @@
       </c>
       <c r="AX11" s="9">
         <f t="shared" ref="AX11:AX48" si="18">AY11-AW11</f>
-        <v>18717</v>
+        <v>18719</v>
       </c>
       <c r="AY11" s="9">
-        <v>34843</v>
+        <v>34845</v>
       </c>
       <c r="AZ11" s="10">
         <f t="shared" ref="AZ11:AZ48" si="19">AY11/AV11</f>
-        <v>0.86572912266752799</v>
+        <v>0.86577881581235872</v>
       </c>
       <c r="BA11" s="22">
         <v>40011</v>
@@ -1492,14 +1492,14 @@
       </c>
       <c r="BC11" s="9">
         <f t="shared" ref="BC11:BC48" si="20">BD11-BB11</f>
-        <v>17870</v>
+        <v>17872</v>
       </c>
       <c r="BD11" s="8">
-        <v>36086</v>
+        <v>36088</v>
       </c>
       <c r="BE11" s="10">
         <f t="shared" ref="BE11:BE48" si="21">BD11/BA11</f>
-        <v>0.901901976956337</v>
+        <v>0.90195196321011717</v>
       </c>
       <c r="BF11" s="9">
         <v>90790</v>
@@ -1509,14 +1509,14 @@
       </c>
       <c r="BH11" s="9">
         <f t="shared" ref="BH11:BH48" si="22">BI11-BG11</f>
-        <v>46020</v>
+        <v>46022</v>
       </c>
       <c r="BI11" s="6">
-        <v>87260</v>
+        <v>87262</v>
       </c>
       <c r="BJ11" s="10">
         <f t="shared" ref="BJ11:BJ48" si="23">BI11/BF11</f>
-        <v>0.96111906597642915</v>
+        <v>0.96114109483423282</v>
       </c>
     </row>
     <row r="12" spans="1:62" x14ac:dyDescent="0.3">
@@ -1534,14 +1534,14 @@
       </c>
       <c r="E12" s="9">
         <f t="shared" si="0"/>
-        <v>15682</v>
+        <v>15684</v>
       </c>
       <c r="F12" s="8">
-        <v>87661</v>
+        <v>87663</v>
       </c>
       <c r="G12" s="10">
         <f t="shared" si="1"/>
-        <v>0.28138140451566102</v>
+        <v>0.2813878242782582</v>
       </c>
       <c r="H12" s="5">
         <v>286301</v>
@@ -1551,14 +1551,14 @@
       </c>
       <c r="J12" s="9">
         <f t="shared" si="2"/>
-        <v>19678</v>
+        <v>19680</v>
       </c>
       <c r="K12" s="8">
-        <v>87893</v>
+        <v>87895</v>
       </c>
       <c r="L12" s="10">
         <f t="shared" si="3"/>
-        <v>0.30699508559173738</v>
+        <v>0.30700207124669493</v>
       </c>
       <c r="M12" s="5">
         <v>312776</v>
@@ -1568,14 +1568,14 @@
       </c>
       <c r="O12" s="9">
         <f t="shared" si="4"/>
-        <v>124076</v>
+        <v>124077</v>
       </c>
       <c r="P12" s="8">
-        <v>286590</v>
+        <v>286591</v>
       </c>
       <c r="Q12" s="10">
         <f t="shared" si="5"/>
-        <v>0.9162787426145228</v>
+        <v>0.91628193979077677</v>
       </c>
       <c r="R12" s="5">
         <v>125200</v>
@@ -1585,14 +1585,14 @@
       </c>
       <c r="T12" s="9">
         <f t="shared" si="6"/>
-        <v>51192</v>
+        <v>51194</v>
       </c>
       <c r="U12" s="8">
-        <v>88943</v>
+        <v>88945</v>
       </c>
       <c r="V12" s="10">
         <f t="shared" si="7"/>
-        <v>0.71040734824281149</v>
+        <v>0.71042332268370612</v>
       </c>
       <c r="W12" s="5">
         <v>120831</v>
@@ -1602,14 +1602,14 @@
       </c>
       <c r="Y12" s="9">
         <f t="shared" si="8"/>
-        <v>46344</v>
+        <v>46346</v>
       </c>
       <c r="Z12" s="8">
-        <v>89302</v>
+        <v>89304</v>
       </c>
       <c r="AA12" s="10">
         <f t="shared" si="9"/>
-        <v>0.73906530608866927</v>
+        <v>0.73908185813243288</v>
       </c>
       <c r="AB12" s="5">
         <v>318929</v>
@@ -1619,14 +1619,14 @@
       </c>
       <c r="AD12" s="9">
         <f t="shared" si="10"/>
-        <v>87170</v>
+        <v>87172</v>
       </c>
       <c r="AE12" s="8">
-        <v>293218</v>
+        <v>293220</v>
       </c>
       <c r="AF12" s="10">
         <f t="shared" si="11"/>
-        <v>0.9193833110190669</v>
+        <v>0.9193895820072806</v>
       </c>
       <c r="AG12" s="5">
         <v>113974</v>
@@ -1636,14 +1636,14 @@
       </c>
       <c r="AI12" s="9">
         <f t="shared" si="12"/>
-        <v>42585</v>
+        <v>42587</v>
       </c>
       <c r="AJ12" s="8">
-        <v>89927</v>
+        <v>89929</v>
       </c>
       <c r="AK12" s="10">
         <f t="shared" si="13"/>
-        <v>0.78901328373137736</v>
+        <v>0.78903083159317033</v>
       </c>
       <c r="AL12" s="5">
         <v>111535</v>
@@ -1653,14 +1653,14 @@
       </c>
       <c r="AN12" s="9">
         <f t="shared" si="14"/>
-        <v>40536</v>
+        <v>40539</v>
       </c>
       <c r="AO12" s="8">
-        <v>90426</v>
+        <v>90429</v>
       </c>
       <c r="AP12" s="10">
         <f t="shared" si="15"/>
-        <v>0.81074102299726547</v>
+        <v>0.81076792038373602</v>
       </c>
       <c r="AQ12" s="22">
         <v>323550</v>
@@ -1670,14 +1670,14 @@
       </c>
       <c r="AS12" s="9">
         <f t="shared" si="16"/>
-        <v>38424</v>
+        <v>38426</v>
       </c>
       <c r="AT12" s="8">
-        <v>299678</v>
+        <v>299680</v>
       </c>
       <c r="AU12" s="10">
         <f t="shared" si="17"/>
-        <v>0.92621851336733119</v>
+        <v>0.92622469479214964</v>
       </c>
       <c r="AV12" s="22">
         <v>144846</v>
@@ -1687,14 +1687,14 @@
       </c>
       <c r="AX12" s="9">
         <f t="shared" si="18"/>
-        <v>44870</v>
+        <v>44872</v>
       </c>
       <c r="AY12" s="9">
-        <v>126336</v>
+        <v>126338</v>
       </c>
       <c r="AZ12" s="10">
         <f t="shared" si="19"/>
-        <v>0.87220910484238434</v>
+        <v>0.87222291261063478</v>
       </c>
       <c r="BA12" s="22">
         <v>144289</v>
@@ -1704,14 +1704,14 @@
       </c>
       <c r="BC12" s="9">
         <f t="shared" si="20"/>
-        <v>40162</v>
+        <v>40164</v>
       </c>
       <c r="BD12" s="8">
-        <v>129015</v>
+        <v>129017</v>
       </c>
       <c r="BE12" s="10">
         <f t="shared" si="21"/>
-        <v>0.89414300466425023</v>
+        <v>0.89415686573474074</v>
       </c>
       <c r="BF12" s="9">
         <v>318519</v>
@@ -1721,14 +1721,14 @@
       </c>
       <c r="BH12" s="9">
         <f t="shared" si="22"/>
-        <v>94436</v>
+        <v>94440</v>
       </c>
       <c r="BI12" s="6">
-        <v>304166</v>
+        <v>304170</v>
       </c>
       <c r="BJ12" s="10">
         <f t="shared" si="23"/>
-        <v>0.95493832393044054</v>
+        <v>0.95495088205099221</v>
       </c>
     </row>
     <row r="13" spans="1:62" x14ac:dyDescent="0.3">
@@ -1958,14 +1958,14 @@
       </c>
       <c r="E14" s="9">
         <f t="shared" si="0"/>
-        <v>11301</v>
+        <v>11302</v>
       </c>
       <c r="F14" s="8">
-        <v>34686</v>
+        <v>34687</v>
       </c>
       <c r="G14" s="10">
         <f t="shared" si="1"/>
-        <v>0.26451612903225807</v>
+        <v>0.26452375505223824</v>
       </c>
       <c r="H14" s="5">
         <v>113453</v>
@@ -1975,14 +1975,14 @@
       </c>
       <c r="J14" s="9">
         <f t="shared" si="2"/>
-        <v>13244</v>
+        <v>13245</v>
       </c>
       <c r="K14" s="8">
-        <v>34873</v>
+        <v>34874</v>
       </c>
       <c r="L14" s="10">
         <f t="shared" si="3"/>
-        <v>0.30737838576326759</v>
+        <v>0.30738719998589725</v>
       </c>
       <c r="M14" s="5">
         <v>130093</v>
@@ -1992,14 +1992,14 @@
       </c>
       <c r="O14" s="9">
         <f t="shared" si="4"/>
-        <v>66697</v>
+        <v>66712</v>
       </c>
       <c r="P14" s="8">
-        <v>115510</v>
+        <v>115525</v>
       </c>
       <c r="Q14" s="10">
         <f t="shared" si="5"/>
-        <v>0.8879032691997264</v>
+        <v>0.88801857132974105</v>
       </c>
       <c r="R14" s="5">
         <v>63308</v>
@@ -2009,14 +2009,14 @@
       </c>
       <c r="T14" s="9">
         <f t="shared" si="6"/>
-        <v>27581</v>
+        <v>27582</v>
       </c>
       <c r="U14" s="8">
-        <v>35694</v>
+        <v>35695</v>
       </c>
       <c r="V14" s="10">
         <f t="shared" si="7"/>
-        <v>0.56381499968408411</v>
+        <v>0.56383079547608517</v>
       </c>
       <c r="W14" s="5">
         <v>61226</v>
@@ -2026,14 +2026,14 @@
       </c>
       <c r="Y14" s="9">
         <f t="shared" si="8"/>
-        <v>25501</v>
+        <v>25503</v>
       </c>
       <c r="Z14" s="8">
-        <v>36043</v>
+        <v>36045</v>
       </c>
       <c r="AA14" s="10">
         <f t="shared" si="9"/>
-        <v>0.58868781236729495</v>
+        <v>0.58872047822820373</v>
       </c>
       <c r="AB14" s="5">
         <v>138271</v>
@@ -2043,14 +2043,14 @@
       </c>
       <c r="AD14" s="9">
         <f t="shared" si="10"/>
-        <v>53053</v>
+        <v>53069</v>
       </c>
       <c r="AE14" s="8">
-        <v>120134</v>
+        <v>120150</v>
       </c>
       <c r="AF14" s="10">
         <f t="shared" si="11"/>
-        <v>0.86883005113147371</v>
+        <v>0.86894576592344019</v>
       </c>
       <c r="AG14" s="5">
         <v>55999</v>
@@ -2060,14 +2060,14 @@
       </c>
       <c r="AI14" s="9">
         <f t="shared" si="12"/>
-        <v>24996</v>
+        <v>24997</v>
       </c>
       <c r="AJ14" s="8">
-        <v>37046</v>
+        <v>37047</v>
       </c>
       <c r="AK14" s="10">
         <f t="shared" si="13"/>
-        <v>0.66154752763442204</v>
+        <v>0.66156538509616247</v>
       </c>
       <c r="AL14" s="5">
         <v>53588</v>
@@ -2077,14 +2077,14 @@
       </c>
       <c r="AN14" s="9">
         <f t="shared" si="14"/>
-        <v>24297</v>
+        <v>24298</v>
       </c>
       <c r="AO14" s="8">
-        <v>37512</v>
+        <v>37513</v>
       </c>
       <c r="AP14" s="10">
         <f t="shared" si="15"/>
-        <v>0.70000746435769201</v>
+        <v>0.70002612525192209</v>
       </c>
       <c r="AQ14" s="22">
         <v>140248</v>
@@ -2094,14 +2094,14 @@
       </c>
       <c r="AS14" s="9">
         <f t="shared" si="16"/>
-        <v>35419</v>
+        <v>35431</v>
       </c>
       <c r="AT14" s="8">
-        <v>125113</v>
+        <v>125125</v>
       </c>
       <c r="AU14" s="10">
         <f t="shared" si="17"/>
-        <v>0.89208402258855746</v>
+        <v>0.8921695853060293</v>
       </c>
       <c r="AV14" s="22">
         <v>71286</v>
@@ -2111,14 +2111,14 @@
       </c>
       <c r="AX14" s="9">
         <f t="shared" si="18"/>
-        <v>35667</v>
+        <v>35673</v>
       </c>
       <c r="AY14" s="9">
-        <v>59674</v>
+        <v>59680</v>
       </c>
       <c r="AZ14" s="10">
         <f t="shared" si="19"/>
-        <v>0.83710686530314504</v>
+        <v>0.83719103330247169</v>
       </c>
       <c r="BA14" s="22">
         <v>69175</v>
@@ -2128,14 +2128,14 @@
       </c>
       <c r="BC14" s="9">
         <f t="shared" si="20"/>
-        <v>34345</v>
+        <v>34348</v>
       </c>
       <c r="BD14" s="8">
-        <v>61422</v>
+        <v>61425</v>
       </c>
       <c r="BE14" s="10">
         <f t="shared" si="21"/>
-        <v>0.88792193711601008</v>
+        <v>0.88796530538489338</v>
       </c>
       <c r="BF14" s="9">
         <v>138667</v>
@@ -2145,14 +2145,14 @@
       </c>
       <c r="BH14" s="9">
         <f t="shared" si="22"/>
-        <v>69995</v>
+        <v>70012</v>
       </c>
       <c r="BI14" s="6">
-        <v>129503</v>
+        <v>129520</v>
       </c>
       <c r="BJ14" s="10">
         <f t="shared" si="23"/>
-        <v>0.93391362039995096</v>
+        <v>0.9340362162590955</v>
       </c>
     </row>
     <row r="15" spans="1:62" x14ac:dyDescent="0.3">
@@ -2187,14 +2187,14 @@
       </c>
       <c r="J15" s="9">
         <f t="shared" si="2"/>
-        <v>38311</v>
+        <v>38312</v>
       </c>
       <c r="K15" s="8">
-        <v>138262</v>
+        <v>138263</v>
       </c>
       <c r="L15" s="10">
         <f t="shared" si="3"/>
-        <v>0.35980149529110816</v>
+        <v>0.35980409760769039</v>
       </c>
       <c r="M15" s="5">
         <v>424733</v>
@@ -2221,14 +2221,14 @@
       </c>
       <c r="T15" s="9">
         <f t="shared" si="6"/>
-        <v>90713</v>
+        <v>90714</v>
       </c>
       <c r="U15" s="8">
-        <v>141011</v>
+        <v>141012</v>
       </c>
       <c r="V15" s="10">
         <f t="shared" si="7"/>
-        <v>0.65221574168721064</v>
+        <v>0.65222036696993102</v>
       </c>
       <c r="W15" s="5">
         <v>208829</v>
@@ -2238,14 +2238,14 @@
       </c>
       <c r="Y15" s="9">
         <f t="shared" si="8"/>
-        <v>82558</v>
+        <v>82559</v>
       </c>
       <c r="Z15" s="8">
-        <v>142572</v>
+        <v>142573</v>
       </c>
       <c r="AA15" s="10">
         <f t="shared" si="9"/>
-        <v>0.68272126955547363</v>
+        <v>0.68272605816241994</v>
       </c>
       <c r="AB15" s="5">
         <v>444211</v>
@@ -2255,14 +2255,14 @@
       </c>
       <c r="AD15" s="9">
         <f t="shared" si="10"/>
-        <v>126160</v>
+        <v>126161</v>
       </c>
       <c r="AE15" s="8">
-        <v>399114</v>
+        <v>399115</v>
       </c>
       <c r="AF15" s="10">
         <f t="shared" si="11"/>
-        <v>0.89847842579314785</v>
+        <v>0.89848067697558143</v>
       </c>
       <c r="AG15" s="5">
         <v>197957</v>
@@ -2357,14 +2357,14 @@
       </c>
       <c r="BH15" s="9">
         <f t="shared" si="22"/>
-        <v>156651</v>
+        <v>156652</v>
       </c>
       <c r="BI15" s="6">
-        <v>417711</v>
+        <v>417712</v>
       </c>
       <c r="BJ15" s="10">
         <f t="shared" si="23"/>
-        <v>0.95329284741097775</v>
+        <v>0.95329512959374862</v>
       </c>
     </row>
     <row r="16" spans="1:62" x14ac:dyDescent="0.3">
@@ -2382,14 +2382,14 @@
       </c>
       <c r="E16" s="9">
         <f t="shared" si="0"/>
-        <v>60756</v>
+        <v>60757</v>
       </c>
       <c r="F16" s="8">
-        <v>204018</v>
+        <v>204019</v>
       </c>
       <c r="G16" s="10">
         <f t="shared" si="1"/>
-        <v>0.27232755444735735</v>
+        <v>0.27232888926857135</v>
       </c>
       <c r="H16" s="5">
         <v>684312</v>
@@ -2416,14 +2416,14 @@
       </c>
       <c r="O16" s="9">
         <f t="shared" si="4"/>
-        <v>326398</v>
+        <v>326401</v>
       </c>
       <c r="P16" s="8">
-        <v>630723</v>
+        <v>630726</v>
       </c>
       <c r="Q16" s="10">
         <f t="shared" si="5"/>
-        <v>0.85728673952046974</v>
+        <v>0.8572908171587017</v>
       </c>
       <c r="R16" s="5">
         <v>377107</v>
@@ -2433,14 +2433,14 @@
       </c>
       <c r="T16" s="9">
         <f t="shared" si="6"/>
-        <v>145096</v>
+        <v>145097</v>
       </c>
       <c r="U16" s="8">
-        <v>208419</v>
+        <v>208420</v>
       </c>
       <c r="V16" s="10">
         <f t="shared" si="7"/>
-        <v>0.55267868270809084</v>
+        <v>0.55268133447536105</v>
       </c>
       <c r="W16" s="5">
         <v>358920</v>
@@ -2467,14 +2467,14 @@
       </c>
       <c r="AD16" s="9">
         <f t="shared" si="10"/>
-        <v>218530</v>
+        <v>218533</v>
       </c>
       <c r="AE16" s="8">
-        <v>649878</v>
+        <v>649881</v>
       </c>
       <c r="AF16" s="10">
         <f t="shared" si="11"/>
-        <v>0.85043419544291077</v>
+        <v>0.85043812126065854</v>
       </c>
       <c r="AG16" s="5">
         <v>333237</v>
@@ -2501,14 +2501,14 @@
       </c>
       <c r="AN16" s="9">
         <f t="shared" si="14"/>
-        <v>116994</v>
+        <v>116995</v>
       </c>
       <c r="AO16" s="8">
-        <v>217707</v>
+        <v>217708</v>
       </c>
       <c r="AP16" s="10">
         <f t="shared" si="15"/>
-        <v>0.67387986937613176</v>
+        <v>0.67388296472846021</v>
       </c>
       <c r="AQ16" s="22">
         <v>767321</v>
@@ -2518,14 +2518,14 @@
       </c>
       <c r="AS16" s="9">
         <f t="shared" si="16"/>
-        <v>111996</v>
+        <v>112000</v>
       </c>
       <c r="AT16" s="8">
-        <v>671252</v>
+        <v>671256</v>
       </c>
       <c r="AU16" s="10">
         <f t="shared" si="17"/>
-        <v>0.87479946463083902</v>
+        <v>0.8748046775730105</v>
       </c>
       <c r="AV16" s="22">
         <v>376806</v>
@@ -2535,14 +2535,14 @@
       </c>
       <c r="AX16" s="9">
         <f t="shared" si="18"/>
-        <v>148955</v>
+        <v>148958</v>
       </c>
       <c r="AY16" s="9">
-        <v>307750</v>
+        <v>307753</v>
       </c>
       <c r="AZ16" s="10">
         <f t="shared" si="19"/>
-        <v>0.81673327919406802</v>
+        <v>0.81674124085072952</v>
       </c>
       <c r="BA16" s="22">
         <v>362361</v>
@@ -2552,14 +2552,14 @@
       </c>
       <c r="BC16" s="9">
         <f t="shared" si="20"/>
-        <v>130506</v>
+        <v>130509</v>
       </c>
       <c r="BD16" s="8">
-        <v>312752</v>
+        <v>312755</v>
       </c>
       <c r="BE16" s="10">
         <f t="shared" si="21"/>
-        <v>0.86309509025529785</v>
+        <v>0.8631033692919492</v>
       </c>
       <c r="BF16" s="9">
         <v>717401</v>
@@ -2569,14 +2569,14 @@
       </c>
       <c r="BH16" s="9">
         <f t="shared" si="22"/>
-        <v>223690</v>
+        <v>223696</v>
       </c>
       <c r="BI16" s="6">
-        <v>675480</v>
+        <v>675486</v>
       </c>
       <c r="BJ16" s="10">
         <f t="shared" si="23"/>
-        <v>0.94156545641837686</v>
+        <v>0.94157381994170619</v>
       </c>
     </row>
     <row r="17" spans="1:62" x14ac:dyDescent="0.3">
@@ -2594,14 +2594,14 @@
       </c>
       <c r="E17" s="9">
         <f t="shared" si="0"/>
-        <v>33421</v>
+        <v>33424</v>
       </c>
       <c r="F17" s="8">
-        <v>138322</v>
+        <v>138325</v>
       </c>
       <c r="G17" s="10">
         <f t="shared" si="1"/>
-        <v>0.25131451287623047</v>
+        <v>0.25131996351704416</v>
       </c>
       <c r="H17" s="5">
         <v>502451</v>
@@ -2611,14 +2611,14 @@
       </c>
       <c r="J17" s="9">
         <f t="shared" si="2"/>
-        <v>39842</v>
+        <v>39845</v>
       </c>
       <c r="K17" s="8">
-        <v>138715</v>
+        <v>138718</v>
       </c>
       <c r="L17" s="10">
         <f t="shared" si="3"/>
-        <v>0.2760766721531055</v>
+        <v>0.27608264288457979</v>
       </c>
       <c r="M17" s="5">
         <v>556868</v>
@@ -2628,14 +2628,14 @@
       </c>
       <c r="O17" s="9">
         <f t="shared" si="4"/>
-        <v>259014</v>
+        <v>259023</v>
       </c>
       <c r="P17" s="8">
-        <v>514361</v>
+        <v>514370</v>
       </c>
       <c r="Q17" s="10">
         <f t="shared" si="5"/>
-        <v>0.92366772736088265</v>
+        <v>0.92368388918020072</v>
       </c>
       <c r="R17" s="5">
         <v>233458</v>
@@ -2645,14 +2645,14 @@
       </c>
       <c r="T17" s="9">
         <f t="shared" si="6"/>
-        <v>96607</v>
+        <v>96610</v>
       </c>
       <c r="U17" s="8">
-        <v>141762</v>
+        <v>141765</v>
       </c>
       <c r="V17" s="10">
         <f t="shared" si="7"/>
-        <v>0.60722699586221074</v>
+        <v>0.60723984613934845</v>
       </c>
       <c r="W17" s="5">
         <v>221561</v>
@@ -2662,14 +2662,14 @@
       </c>
       <c r="Y17" s="9">
         <f t="shared" si="8"/>
-        <v>86582</v>
+        <v>86585</v>
       </c>
       <c r="Z17" s="8">
-        <v>142723</v>
+        <v>142726</v>
       </c>
       <c r="AA17" s="10">
         <f t="shared" si="9"/>
-        <v>0.64417022851494621</v>
+        <v>0.64418376880407657</v>
       </c>
       <c r="AB17" s="5">
         <v>582052</v>
@@ -2679,14 +2679,14 @@
       </c>
       <c r="AD17" s="9">
         <f t="shared" si="10"/>
-        <v>196936</v>
+        <v>196948</v>
       </c>
       <c r="AE17" s="8">
-        <v>535845</v>
+        <v>535857</v>
       </c>
       <c r="AF17" s="10">
         <f t="shared" si="11"/>
-        <v>0.92061362215059828</v>
+        <v>0.92063423886525597</v>
       </c>
       <c r="AG17" s="5">
         <v>198905</v>
@@ -2696,14 +2696,14 @@
       </c>
       <c r="AI17" s="9">
         <f t="shared" si="12"/>
-        <v>84775</v>
+        <v>84778</v>
       </c>
       <c r="AJ17" s="8">
-        <v>144559</v>
+        <v>144562</v>
       </c>
       <c r="AK17" s="10">
         <f t="shared" si="13"/>
-        <v>0.72677408813252553</v>
+        <v>0.72678917070963522</v>
       </c>
       <c r="AL17" s="5">
         <v>191155</v>
@@ -2713,14 +2713,14 @@
       </c>
       <c r="AN17" s="9">
         <f t="shared" si="14"/>
-        <v>82764</v>
+        <v>82767</v>
       </c>
       <c r="AO17" s="8">
-        <v>145996</v>
+        <v>145999</v>
       </c>
       <c r="AP17" s="10">
         <f t="shared" si="15"/>
-        <v>0.76375716041955477</v>
+        <v>0.76377285448981191</v>
       </c>
       <c r="AQ17" s="22">
         <v>594970</v>
@@ -2730,14 +2730,14 @@
       </c>
       <c r="AS17" s="9">
         <f t="shared" si="16"/>
-        <v>115069</v>
+        <v>115076</v>
       </c>
       <c r="AT17" s="8">
-        <v>556248</v>
+        <v>556255</v>
       </c>
       <c r="AU17" s="10">
         <f t="shared" si="17"/>
-        <v>0.93491772694421571</v>
+        <v>0.93492949224330635</v>
       </c>
       <c r="AV17" s="22">
         <v>254447</v>
@@ -2747,14 +2747,14 @@
       </c>
       <c r="AX17" s="9">
         <f t="shared" si="18"/>
-        <v>115478</v>
+        <v>115485</v>
       </c>
       <c r="AY17" s="9">
-        <v>224977</v>
+        <v>224984</v>
       </c>
       <c r="AZ17" s="10">
         <f t="shared" si="19"/>
-        <v>0.88418020255691754</v>
+        <v>0.88420771319764035</v>
       </c>
       <c r="BA17" s="22">
         <v>254024</v>
@@ -2764,14 +2764,14 @@
       </c>
       <c r="BC17" s="9">
         <f t="shared" si="20"/>
-        <v>106316</v>
+        <v>106326</v>
       </c>
       <c r="BD17" s="8">
-        <v>234295</v>
+        <v>234305</v>
       </c>
       <c r="BE17" s="10">
         <f t="shared" si="21"/>
-        <v>0.9223341101628193</v>
+        <v>0.92237347652190349</v>
       </c>
       <c r="BF17" s="9">
         <v>590776</v>
@@ -2781,14 +2781,14 @@
       </c>
       <c r="BH17" s="9">
         <f t="shared" si="22"/>
-        <v>261166</v>
+        <v>261174</v>
       </c>
       <c r="BI17" s="6">
-        <v>572574</v>
+        <v>572582</v>
       </c>
       <c r="BJ17" s="10">
         <f t="shared" si="23"/>
-        <v>0.96918967595162975</v>
+        <v>0.9692032174631332</v>
       </c>
     </row>
     <row r="18" spans="1:62" x14ac:dyDescent="0.3">
@@ -2806,14 +2806,14 @@
       </c>
       <c r="E18" s="9">
         <f t="shared" si="0"/>
-        <v>117491</v>
+        <v>117501</v>
       </c>
       <c r="F18" s="8">
-        <v>332211</v>
+        <v>332221</v>
       </c>
       <c r="G18" s="10">
         <f t="shared" si="1"/>
-        <v>0.28890827248661605</v>
+        <v>0.28891696901600511</v>
       </c>
       <c r="H18" s="5">
         <v>1037981</v>
@@ -2823,14 +2823,14 @@
       </c>
       <c r="J18" s="9">
         <f t="shared" si="2"/>
-        <v>131817</v>
+        <v>131827</v>
       </c>
       <c r="K18" s="8">
-        <v>332126</v>
+        <v>332136</v>
       </c>
       <c r="L18" s="10">
         <f t="shared" si="3"/>
-        <v>0.31997310162710108</v>
+        <v>0.31998273571481561</v>
       </c>
       <c r="M18" s="5">
         <v>1134575</v>
@@ -2840,14 +2840,14 @@
       </c>
       <c r="O18" s="9">
         <f t="shared" si="4"/>
-        <v>604391</v>
+        <v>604405</v>
       </c>
       <c r="P18" s="8">
-        <v>1000737</v>
+        <v>1000751</v>
       </c>
       <c r="Q18" s="10">
         <f t="shared" si="5"/>
-        <v>0.88203688605865638</v>
+        <v>0.88204922548090692</v>
       </c>
       <c r="R18" s="5">
         <v>560923</v>
@@ -2857,14 +2857,14 @@
       </c>
       <c r="T18" s="9">
         <f t="shared" si="6"/>
-        <v>280935</v>
+        <v>280944</v>
       </c>
       <c r="U18" s="8">
-        <v>340398</v>
+        <v>340407</v>
       </c>
       <c r="V18" s="10">
         <f t="shared" si="7"/>
-        <v>0.60685334707259286</v>
+        <v>0.60686939205559409</v>
       </c>
       <c r="W18" s="5">
         <v>535952</v>
@@ -2874,14 +2874,14 @@
       </c>
       <c r="Y18" s="9">
         <f t="shared" si="8"/>
-        <v>262463</v>
+        <v>262473</v>
       </c>
       <c r="Z18" s="8">
-        <v>344116</v>
+        <v>344126</v>
       </c>
       <c r="AA18" s="10">
         <f t="shared" si="9"/>
-        <v>0.6420649610412873</v>
+        <v>0.64208361942860559</v>
       </c>
       <c r="AB18" s="5">
         <v>1210642</v>
@@ -2891,14 +2891,14 @@
       </c>
       <c r="AD18" s="9">
         <f t="shared" si="10"/>
-        <v>486241</v>
+        <v>486257</v>
       </c>
       <c r="AE18" s="8">
-        <v>1048093</v>
+        <v>1048109</v>
       </c>
       <c r="AF18" s="10">
         <f t="shared" si="11"/>
-        <v>0.86573322253812435</v>
+        <v>0.86574643866642653</v>
       </c>
       <c r="AG18" s="5">
         <v>495943</v>
@@ -2908,14 +2908,14 @@
       </c>
       <c r="AI18" s="9">
         <f t="shared" si="12"/>
-        <v>257036</v>
+        <v>257043</v>
       </c>
       <c r="AJ18" s="8">
-        <v>353141</v>
+        <v>353148</v>
       </c>
       <c r="AK18" s="10">
         <f t="shared" si="13"/>
-        <v>0.7120596520164616</v>
+        <v>0.7120737665417195</v>
       </c>
       <c r="AL18" s="5">
         <v>477702</v>
@@ -2925,14 +2925,14 @@
       </c>
       <c r="AN18" s="9">
         <f t="shared" si="14"/>
-        <v>255780</v>
+        <v>255788</v>
       </c>
       <c r="AO18" s="8">
-        <v>358361</v>
+        <v>358369</v>
       </c>
       <c r="AP18" s="10">
         <f t="shared" si="15"/>
-        <v>0.75017688852045838</v>
+        <v>0.75019363536263195</v>
       </c>
       <c r="AQ18" s="22">
         <v>1231355</v>
@@ -2942,14 +2942,14 @@
       </c>
       <c r="AS18" s="9">
         <f t="shared" si="16"/>
-        <v>296444</v>
+        <v>296459</v>
       </c>
       <c r="AT18" s="8">
-        <v>1092304</v>
+        <v>1092319</v>
       </c>
       <c r="AU18" s="10">
         <f t="shared" si="17"/>
-        <v>0.88707480783364667</v>
+        <v>0.8870869895359178</v>
       </c>
       <c r="AV18" s="22">
         <v>676361</v>
@@ -2959,14 +2959,14 @@
       </c>
       <c r="AX18" s="9">
         <f t="shared" si="18"/>
-        <v>330618</v>
+        <v>330631</v>
       </c>
       <c r="AY18" s="9">
-        <v>573192</v>
+        <v>573205</v>
       </c>
       <c r="AZ18" s="10">
         <f t="shared" si="19"/>
-        <v>0.84746459361199122</v>
+        <v>0.84748381411701734</v>
       </c>
       <c r="BA18" s="22">
         <v>652080</v>
@@ -2976,14 +2976,14 @@
       </c>
       <c r="BC18" s="9">
         <f t="shared" si="20"/>
-        <v>316126</v>
+        <v>316138</v>
       </c>
       <c r="BD18" s="8">
-        <v>587337</v>
+        <v>587349</v>
       </c>
       <c r="BE18" s="10">
         <f t="shared" si="21"/>
-        <v>0.90071310268678695</v>
+        <v>0.90073150533676849</v>
       </c>
       <c r="BF18" s="9">
         <v>1203078</v>
@@ -2993,14 +2993,14 @@
       </c>
       <c r="BH18" s="9">
         <f t="shared" si="22"/>
-        <v>595053</v>
+        <v>595065</v>
       </c>
       <c r="BI18" s="6">
-        <v>1125676</v>
+        <v>1125688</v>
       </c>
       <c r="BJ18" s="10">
         <f t="shared" si="23"/>
-        <v>0.9356633568230821</v>
+        <v>0.93567333123870611</v>
       </c>
     </row>
     <row r="19" spans="1:62" x14ac:dyDescent="0.3">
@@ -3018,14 +3018,14 @@
       </c>
       <c r="E19" s="9">
         <f t="shared" si="0"/>
-        <v>44336</v>
+        <v>44337</v>
       </c>
       <c r="F19" s="8">
-        <v>92382</v>
+        <v>92383</v>
       </c>
       <c r="G19" s="10">
         <f t="shared" si="1"/>
-        <v>0.29012898180687591</v>
+        <v>0.29013212234271413</v>
       </c>
       <c r="H19" s="5">
         <v>290976</v>
@@ -3052,14 +3052,14 @@
       </c>
       <c r="O19" s="9">
         <f t="shared" si="4"/>
-        <v>210392</v>
+        <v>210398</v>
       </c>
       <c r="P19" s="8">
-        <v>278105</v>
+        <v>278111</v>
       </c>
       <c r="Q19" s="10">
         <f t="shared" si="5"/>
-        <v>0.85100751235484018</v>
+        <v>0.85102587248886918</v>
       </c>
       <c r="R19" s="5">
         <v>182406</v>
@@ -3069,14 +3069,14 @@
       </c>
       <c r="T19" s="9">
         <f t="shared" si="6"/>
-        <v>85573</v>
+        <v>85574</v>
       </c>
       <c r="U19" s="8">
-        <v>95491</v>
+        <v>95492</v>
       </c>
       <c r="V19" s="10">
         <f t="shared" si="7"/>
-        <v>0.52350799864039566</v>
+        <v>0.52351348091619798</v>
       </c>
       <c r="W19" s="5">
         <v>174793</v>
@@ -3103,14 +3103,14 @@
       </c>
       <c r="AD19" s="9">
         <f t="shared" si="10"/>
-        <v>164262</v>
+        <v>164269</v>
       </c>
       <c r="AE19" s="8">
-        <v>291734</v>
+        <v>291741</v>
       </c>
       <c r="AF19" s="10">
         <f t="shared" si="11"/>
-        <v>0.82090026816139205</v>
+        <v>0.82091996522062116</v>
       </c>
       <c r="AG19" s="5">
         <v>163328</v>
@@ -3137,14 +3137,14 @@
       </c>
       <c r="AN19" s="9">
         <f t="shared" si="14"/>
-        <v>83149</v>
+        <v>83152</v>
       </c>
       <c r="AO19" s="8">
-        <v>100620</v>
+        <v>100623</v>
       </c>
       <c r="AP19" s="10">
         <f t="shared" si="15"/>
-        <v>0.62698229719035659</v>
+        <v>0.62700099075914584</v>
       </c>
       <c r="AQ19" s="22">
         <v>372999</v>
@@ -3154,14 +3154,14 @@
       </c>
       <c r="AS19" s="9">
         <f t="shared" si="16"/>
-        <v>120077</v>
+        <v>120087</v>
       </c>
       <c r="AT19" s="8">
-        <v>306813</v>
+        <v>306823</v>
       </c>
       <c r="AU19" s="10">
         <f t="shared" si="17"/>
-        <v>0.822557165032614</v>
+        <v>0.82258397475596445</v>
       </c>
       <c r="AV19" s="22">
         <v>223136</v>
@@ -3171,14 +3171,14 @@
       </c>
       <c r="AX19" s="9">
         <f t="shared" si="18"/>
-        <v>120765</v>
+        <v>120771</v>
       </c>
       <c r="AY19" s="9">
-        <v>165122</v>
+        <v>165128</v>
       </c>
       <c r="AZ19" s="10">
         <f t="shared" si="19"/>
-        <v>0.74000609493761649</v>
+        <v>0.74003298436827769</v>
       </c>
       <c r="BA19" s="22">
         <v>218799</v>
@@ -3188,14 +3188,14 @@
       </c>
       <c r="BC19" s="9">
         <f t="shared" si="20"/>
-        <v>118601</v>
+        <v>118607</v>
       </c>
       <c r="BD19" s="8">
-        <v>171492</v>
+        <v>171498</v>
       </c>
       <c r="BE19" s="10">
         <f t="shared" si="21"/>
-        <v>0.78378786009076828</v>
+        <v>0.78381528251957278</v>
       </c>
       <c r="BF19" s="9">
         <v>376756</v>
@@ -3205,14 +3205,14 @@
       </c>
       <c r="BH19" s="9">
         <f t="shared" si="22"/>
-        <v>221991</v>
+        <v>222000</v>
       </c>
       <c r="BI19" s="6">
-        <v>323345</v>
+        <v>323354</v>
       </c>
       <c r="BJ19" s="10">
         <f t="shared" si="23"/>
-        <v>0.85823450721421823</v>
+        <v>0.85825839535402226</v>
       </c>
     </row>
     <row r="20" spans="1:62" x14ac:dyDescent="0.3">
@@ -3264,14 +3264,14 @@
       </c>
       <c r="O20" s="9">
         <f t="shared" si="4"/>
-        <v>3842</v>
+        <v>3843</v>
       </c>
       <c r="P20" s="8">
-        <v>6373</v>
+        <v>6374</v>
       </c>
       <c r="Q20" s="10">
         <f t="shared" si="5"/>
-        <v>0.84143121204119353</v>
+        <v>0.84156324267229998</v>
       </c>
       <c r="R20" s="5">
         <v>4791</v>
@@ -3315,14 +3315,14 @@
       </c>
       <c r="AD20" s="9">
         <f t="shared" si="10"/>
-        <v>2702</v>
+        <v>2703</v>
       </c>
       <c r="AE20" s="8">
-        <v>6410</v>
+        <v>6411</v>
       </c>
       <c r="AF20" s="10">
         <f t="shared" si="11"/>
-        <v>0.83181936153646507</v>
+        <v>0.8319491305476252</v>
       </c>
       <c r="AG20" s="5">
         <v>4195</v>
@@ -3366,14 +3366,14 @@
       </c>
       <c r="AS20" s="9">
         <f t="shared" si="16"/>
-        <v>1863</v>
+        <v>1865</v>
       </c>
       <c r="AT20" s="8">
-        <v>6605</v>
+        <v>6607</v>
       </c>
       <c r="AU20" s="10">
         <f t="shared" si="17"/>
-        <v>0.83681743316863044</v>
+        <v>0.83707082224756113</v>
       </c>
       <c r="AV20" s="22">
         <v>5263</v>
@@ -3417,14 +3417,14 @@
       </c>
       <c r="BH20" s="9">
         <f t="shared" si="22"/>
-        <v>4535</v>
+        <v>4538</v>
       </c>
       <c r="BI20" s="6">
-        <v>6934</v>
+        <v>6937</v>
       </c>
       <c r="BJ20" s="10">
         <f t="shared" si="23"/>
-        <v>0.87939124920735579</v>
+        <v>0.87977171845275837</v>
       </c>
     </row>
     <row r="21" spans="1:62" x14ac:dyDescent="0.3">
@@ -3442,14 +3442,14 @@
       </c>
       <c r="E21" s="9">
         <f t="shared" si="0"/>
-        <v>2151</v>
+        <v>2152</v>
       </c>
       <c r="F21" s="8">
-        <v>3860</v>
+        <v>3861</v>
       </c>
       <c r="G21" s="10">
         <f t="shared" si="1"/>
-        <v>0.31081407520734361</v>
+        <v>0.31089459698848537</v>
       </c>
       <c r="H21" s="5">
         <v>10801</v>
@@ -3459,14 +3459,14 @@
       </c>
       <c r="J21" s="9">
         <f t="shared" si="2"/>
-        <v>2326</v>
+        <v>2327</v>
       </c>
       <c r="K21" s="8">
-        <v>3819</v>
+        <v>3820</v>
       </c>
       <c r="L21" s="10">
         <f t="shared" si="3"/>
-        <v>0.35357837237292844</v>
+        <v>0.35367095639292656</v>
       </c>
       <c r="M21" s="5">
         <v>12071</v>
@@ -3476,14 +3476,14 @@
       </c>
       <c r="O21" s="9">
         <f t="shared" si="4"/>
-        <v>6466</v>
+        <v>6467</v>
       </c>
       <c r="P21" s="8">
-        <v>8743</v>
+        <v>8744</v>
       </c>
       <c r="Q21" s="10">
         <f t="shared" si="5"/>
-        <v>0.72429790406760008</v>
+        <v>0.72438074724546431</v>
       </c>
       <c r="R21" s="5">
         <v>8791</v>
@@ -3595,14 +3595,14 @@
       </c>
       <c r="AX21" s="9">
         <f t="shared" si="18"/>
-        <v>4666</v>
+        <v>4667</v>
       </c>
       <c r="AY21" s="9">
-        <v>6068</v>
+        <v>6069</v>
       </c>
       <c r="AZ21" s="10">
         <f t="shared" si="19"/>
-        <v>0.640489761452396</v>
+        <v>0.64059531348955034</v>
       </c>
       <c r="BA21" s="22">
         <v>9339</v>
@@ -3612,14 +3612,14 @@
       </c>
       <c r="BC21" s="9">
         <f t="shared" si="20"/>
-        <v>4608</v>
+        <v>4609</v>
       </c>
       <c r="BD21" s="8">
-        <v>6187</v>
+        <v>6188</v>
       </c>
       <c r="BE21" s="10">
         <f t="shared" si="21"/>
-        <v>0.66249063068851055</v>
+        <v>0.66259770853410427</v>
       </c>
       <c r="BF21" s="9">
         <v>12705</v>
@@ -3629,14 +3629,14 @@
       </c>
       <c r="BH21" s="9">
         <f t="shared" si="22"/>
-        <v>7291</v>
+        <v>7292</v>
       </c>
       <c r="BI21" s="6">
-        <v>9737</v>
+        <v>9738</v>
       </c>
       <c r="BJ21" s="10">
         <f t="shared" si="23"/>
-        <v>0.7663911845730027</v>
+        <v>0.76646989374262098</v>
       </c>
     </row>
     <row r="22" spans="1:62" x14ac:dyDescent="0.3">
@@ -3654,14 +3654,14 @@
       </c>
       <c r="E22" s="9">
         <f t="shared" si="0"/>
-        <v>1601</v>
+        <v>1604</v>
       </c>
       <c r="F22" s="8">
-        <v>3677</v>
+        <v>3680</v>
       </c>
       <c r="G22" s="10">
         <f t="shared" si="1"/>
-        <v>0.54954416380212223</v>
+        <v>0.54999252727544468</v>
       </c>
       <c r="H22" s="5">
         <v>6403</v>
@@ -3671,14 +3671,14 @@
       </c>
       <c r="J22" s="9">
         <f t="shared" si="2"/>
-        <v>1809</v>
+        <v>1812</v>
       </c>
       <c r="K22" s="8">
-        <v>3692</v>
+        <v>3695</v>
       </c>
       <c r="L22" s="10">
         <f t="shared" si="3"/>
-        <v>0.57660471653912226</v>
+        <v>0.57707324691550832</v>
       </c>
       <c r="M22" s="5">
         <v>6636</v>
@@ -3688,14 +3688,14 @@
       </c>
       <c r="O22" s="9">
         <f t="shared" si="4"/>
-        <v>3454</v>
+        <v>3458</v>
       </c>
       <c r="P22" s="8">
-        <v>5236</v>
+        <v>5240</v>
       </c>
       <c r="Q22" s="10">
         <f t="shared" si="5"/>
-        <v>0.78902953586497893</v>
+        <v>0.78963230861965039</v>
       </c>
       <c r="R22" s="5">
         <v>5537</v>
@@ -3705,14 +3705,14 @@
       </c>
       <c r="T22" s="9">
         <f t="shared" si="6"/>
-        <v>3232</v>
+        <v>3234</v>
       </c>
       <c r="U22" s="8">
-        <v>3724</v>
+        <v>3726</v>
       </c>
       <c r="V22" s="10">
         <f t="shared" si="7"/>
-        <v>0.67256637168141598</v>
+        <v>0.67292757811089032</v>
       </c>
       <c r="W22" s="5">
         <v>5469</v>
@@ -3722,14 +3722,14 @@
       </c>
       <c r="Y22" s="9">
         <f t="shared" si="8"/>
-        <v>3036</v>
+        <v>3038</v>
       </c>
       <c r="Z22" s="8">
-        <v>3780</v>
+        <v>3782</v>
       </c>
       <c r="AA22" s="10">
         <f t="shared" si="9"/>
-        <v>0.69116840373011523</v>
+        <v>0.69153410129822634</v>
       </c>
       <c r="AB22" s="5">
         <v>6814</v>
@@ -3739,14 +3739,14 @@
       </c>
       <c r="AD22" s="9">
         <f t="shared" si="10"/>
-        <v>2736</v>
+        <v>2738</v>
       </c>
       <c r="AE22" s="8">
-        <v>5393</v>
+        <v>5395</v>
       </c>
       <c r="AF22" s="10">
         <f t="shared" si="11"/>
-        <v>0.79145876137364246</v>
+        <v>0.79175227472850018</v>
       </c>
       <c r="AG22" s="5">
         <v>5399</v>
@@ -3756,14 +3756,14 @@
       </c>
       <c r="AI22" s="9">
         <f t="shared" si="12"/>
-        <v>3052</v>
+        <v>3054</v>
       </c>
       <c r="AJ22" s="8">
-        <v>3849</v>
+        <v>3851</v>
       </c>
       <c r="AK22" s="10">
         <f t="shared" si="13"/>
-        <v>0.71290979811076127</v>
+        <v>0.7132802370809409</v>
       </c>
       <c r="AL22" s="5">
         <v>5432</v>
@@ -3773,14 +3773,14 @@
       </c>
       <c r="AN22" s="9">
         <f t="shared" si="14"/>
-        <v>2997</v>
+        <v>2999</v>
       </c>
       <c r="AO22" s="8">
-        <v>3935</v>
+        <v>3937</v>
       </c>
       <c r="AP22" s="10">
         <f t="shared" si="15"/>
-        <v>0.72441089837997052</v>
+        <v>0.72477908689248893</v>
       </c>
       <c r="AQ22" s="22">
         <v>7088</v>
@@ -3790,14 +3790,14 @@
       </c>
       <c r="AS22" s="9">
         <f t="shared" si="16"/>
-        <v>2099</v>
+        <v>2101</v>
       </c>
       <c r="AT22" s="8">
-        <v>5595</v>
+        <v>5597</v>
       </c>
       <c r="AU22" s="10">
         <f t="shared" si="17"/>
-        <v>0.78936230248306993</v>
+        <v>0.78964446952595935</v>
       </c>
       <c r="AV22" s="22">
         <v>5686</v>
@@ -3807,14 +3807,14 @@
       </c>
       <c r="AX22" s="9">
         <f t="shared" si="18"/>
-        <v>3235</v>
+        <v>3237</v>
       </c>
       <c r="AY22" s="9">
-        <v>4390</v>
+        <v>4392</v>
       </c>
       <c r="AZ22" s="10">
         <f t="shared" si="19"/>
-        <v>0.7720717551881815</v>
+        <v>0.77242349630671825</v>
       </c>
       <c r="BA22" s="22">
         <v>5622</v>
@@ -3824,14 +3824,14 @@
       </c>
       <c r="BC22" s="9">
         <f t="shared" si="20"/>
-        <v>3147</v>
+        <v>3150</v>
       </c>
       <c r="BD22" s="8">
-        <v>4470</v>
+        <v>4473</v>
       </c>
       <c r="BE22" s="10">
         <f t="shared" si="21"/>
-        <v>0.79509071504802564</v>
+        <v>0.79562433297758806</v>
       </c>
       <c r="BF22" s="9">
         <v>6948</v>
@@ -3841,14 +3841,14 @@
       </c>
       <c r="BH22" s="9">
         <f t="shared" si="22"/>
-        <v>4136</v>
+        <v>4138</v>
       </c>
       <c r="BI22" s="6">
-        <v>5829</v>
+        <v>5831</v>
       </c>
       <c r="BJ22" s="10">
         <f t="shared" si="23"/>
-        <v>0.83894645941278068</v>
+        <v>0.83923431203223953</v>
       </c>
     </row>
     <row r="23" spans="1:62" x14ac:dyDescent="0.3">
@@ -4163,14 +4163,14 @@
       </c>
       <c r="AD24" s="9">
         <f t="shared" si="10"/>
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="AE24" s="8">
-        <v>4642</v>
+        <v>4643</v>
       </c>
       <c r="AF24" s="10">
         <f t="shared" si="11"/>
-        <v>0.69668317574666061</v>
+        <v>0.69683325829206066</v>
       </c>
       <c r="AG24" s="5">
         <v>5175</v>
@@ -4214,14 +4214,14 @@
       </c>
       <c r="AS24" s="9">
         <f t="shared" si="16"/>
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="AT24" s="8">
-        <v>4992</v>
+        <v>4993</v>
       </c>
       <c r="AU24" s="10">
         <f t="shared" si="17"/>
-        <v>0.73132141810723705</v>
+        <v>0.7314679167887489</v>
       </c>
       <c r="AV24" s="22">
         <v>5390</v>
@@ -4231,14 +4231,14 @@
       </c>
       <c r="AX24" s="9">
         <f t="shared" si="18"/>
-        <v>2756</v>
+        <v>2758</v>
       </c>
       <c r="AY24" s="9">
-        <v>3735</v>
+        <v>3737</v>
       </c>
       <c r="AZ24" s="10">
         <f t="shared" si="19"/>
-        <v>0.69294990723562155</v>
+        <v>0.69332096474953619</v>
       </c>
       <c r="BA24" s="22">
         <v>5125</v>
@@ -4426,14 +4426,14 @@
       </c>
       <c r="AS25" s="9">
         <f t="shared" si="16"/>
-        <v>6762</v>
+        <v>6763</v>
       </c>
       <c r="AT25" s="8">
-        <v>21746</v>
+        <v>21747</v>
       </c>
       <c r="AU25" s="10">
         <f t="shared" si="17"/>
-        <v>0.84159603699833585</v>
+        <v>0.84163473818646228</v>
       </c>
       <c r="AV25" s="22">
         <v>15840</v>
@@ -4502,14 +4502,14 @@
       </c>
       <c r="E26" s="9">
         <f t="shared" si="0"/>
-        <v>3522</v>
+        <v>3526</v>
       </c>
       <c r="F26" s="8">
-        <v>7621</v>
+        <v>7625</v>
       </c>
       <c r="G26" s="10">
         <f t="shared" si="1"/>
-        <v>0.28702169328110877</v>
+        <v>0.28717234106658635</v>
       </c>
       <c r="H26" s="5">
         <v>23466</v>
@@ -4519,14 +4519,14 @@
       </c>
       <c r="J26" s="9">
         <f t="shared" si="2"/>
-        <v>3882</v>
+        <v>3886</v>
       </c>
       <c r="K26" s="8">
-        <v>7641</v>
+        <v>7645</v>
       </c>
       <c r="L26" s="10">
         <f t="shared" si="3"/>
-        <v>0.32562004602403477</v>
+        <v>0.3257905054120856</v>
       </c>
       <c r="M26" s="5">
         <v>25760</v>
@@ -4536,14 +4536,14 @@
       </c>
       <c r="O26" s="9">
         <f t="shared" si="4"/>
-        <v>10439</v>
+        <v>10445</v>
       </c>
       <c r="P26" s="8">
-        <v>17310</v>
+        <v>17316</v>
       </c>
       <c r="Q26" s="10">
         <f t="shared" si="5"/>
-        <v>0.67197204968944102</v>
+        <v>0.67220496894409942</v>
       </c>
       <c r="R26" s="5">
         <v>16534</v>
@@ -4553,14 +4553,14 @@
       </c>
       <c r="T26" s="9">
         <f t="shared" si="6"/>
-        <v>6347</v>
+        <v>6351</v>
       </c>
       <c r="U26" s="8">
-        <v>7694</v>
+        <v>7698</v>
       </c>
       <c r="V26" s="10">
         <f t="shared" si="7"/>
-        <v>0.46534413934921981</v>
+        <v>0.46558606507802103</v>
       </c>
       <c r="W26" s="5">
         <v>16064</v>
@@ -4570,14 +4570,14 @@
       </c>
       <c r="Y26" s="9">
         <f t="shared" si="8"/>
-        <v>6282</v>
+        <v>6286</v>
       </c>
       <c r="Z26" s="8">
-        <v>7758</v>
+        <v>7762</v>
       </c>
       <c r="AA26" s="10">
         <f t="shared" si="9"/>
-        <v>0.48294322709163345</v>
+        <v>0.4831922310756972</v>
       </c>
       <c r="AB26" s="5">
         <v>25659</v>
@@ -4587,14 +4587,14 @@
       </c>
       <c r="AD26" s="9">
         <f t="shared" si="10"/>
-        <v>9211</v>
+        <v>9218</v>
       </c>
       <c r="AE26" s="8">
-        <v>17579</v>
+        <v>17586</v>
       </c>
       <c r="AF26" s="10">
         <f t="shared" si="11"/>
-        <v>0.68510074437819091</v>
+        <v>0.68537355313924941</v>
       </c>
       <c r="AG26" s="5">
         <v>15065</v>
@@ -4604,14 +4604,14 @@
       </c>
       <c r="AI26" s="9">
         <f t="shared" si="12"/>
-        <v>6164</v>
+        <v>6168</v>
       </c>
       <c r="AJ26" s="8">
-        <v>7940</v>
+        <v>7944</v>
       </c>
       <c r="AK26" s="10">
         <f t="shared" si="13"/>
-        <v>0.52704945237305012</v>
+        <v>0.52731496846996351</v>
       </c>
       <c r="AL26" s="5">
         <v>14868</v>
@@ -4621,14 +4621,14 @@
       </c>
       <c r="AN26" s="9">
         <f t="shared" si="14"/>
-        <v>6207</v>
+        <v>6211</v>
       </c>
       <c r="AO26" s="8">
-        <v>7976</v>
+        <v>7980</v>
       </c>
       <c r="AP26" s="10">
         <f t="shared" si="15"/>
-        <v>0.5364541296744687</v>
+        <v>0.53672316384180796</v>
       </c>
       <c r="AQ26" s="22">
         <v>26317</v>
@@ -4638,14 +4638,14 @@
       </c>
       <c r="AS26" s="9">
         <f t="shared" si="16"/>
-        <v>7554</v>
+        <v>7562</v>
       </c>
       <c r="AT26" s="8">
-        <v>18124</v>
+        <v>18132</v>
       </c>
       <c r="AU26" s="10">
         <f t="shared" si="17"/>
-        <v>0.68868032070524754</v>
+        <v>0.68898430672189082</v>
       </c>
       <c r="AV26" s="22">
         <v>16878</v>
@@ -4655,14 +4655,14 @@
       </c>
       <c r="AX26" s="9">
         <f t="shared" si="18"/>
-        <v>7675</v>
+        <v>7678</v>
       </c>
       <c r="AY26" s="9">
-        <v>10296</v>
+        <v>10299</v>
       </c>
       <c r="AZ26" s="10">
         <f t="shared" si="19"/>
-        <v>0.61002488446498404</v>
+        <v>0.61020263064344116</v>
       </c>
       <c r="BA26" s="22">
         <v>16511</v>
@@ -4672,14 +4672,14 @@
       </c>
       <c r="BC26" s="9">
         <f t="shared" si="20"/>
-        <v>7369</v>
+        <v>7373</v>
       </c>
       <c r="BD26" s="8">
-        <v>10286</v>
+        <v>10290</v>
       </c>
       <c r="BE26" s="10">
         <f t="shared" si="21"/>
-        <v>0.62297862031373019</v>
+        <v>0.62322088304766521</v>
       </c>
       <c r="BF26" s="9">
         <v>25358</v>
@@ -4689,14 +4689,14 @@
       </c>
       <c r="BH26" s="9">
         <f t="shared" si="22"/>
-        <v>12723</v>
+        <v>12731</v>
       </c>
       <c r="BI26" s="6">
-        <v>18470</v>
+        <v>18478</v>
       </c>
       <c r="BJ26" s="10">
         <f t="shared" si="23"/>
-        <v>0.72836974524804798</v>
+        <v>0.72868522754160425</v>
       </c>
     </row>
     <row r="27" spans="1:62" x14ac:dyDescent="0.3">
@@ -4714,14 +4714,14 @@
       </c>
       <c r="E27" s="9">
         <f t="shared" si="0"/>
-        <v>27156</v>
+        <v>27159</v>
       </c>
       <c r="F27" s="8">
-        <v>53275</v>
+        <v>53278</v>
       </c>
       <c r="G27" s="10">
         <f t="shared" si="1"/>
-        <v>0.36640554611792381</v>
+        <v>0.3664261789971045</v>
       </c>
       <c r="H27" s="5">
         <v>133004</v>
@@ -4731,14 +4731,14 @@
       </c>
       <c r="J27" s="9">
         <f t="shared" si="2"/>
-        <v>30762</v>
+        <v>30765</v>
       </c>
       <c r="K27" s="8">
-        <v>53260</v>
+        <v>53263</v>
       </c>
       <c r="L27" s="10">
         <f t="shared" si="3"/>
-        <v>0.40043908453881089</v>
+        <v>0.400461640251421</v>
       </c>
       <c r="M27" s="5">
         <v>146684</v>
@@ -4748,14 +4748,14 @@
       </c>
       <c r="O27" s="9">
         <f t="shared" si="4"/>
-        <v>89621</v>
+        <v>89628</v>
       </c>
       <c r="P27" s="8">
-        <v>121219</v>
+        <v>121226</v>
       </c>
       <c r="Q27" s="10">
         <f t="shared" si="5"/>
-        <v>0.82639551689345803</v>
+        <v>0.82644323852635593</v>
       </c>
       <c r="R27" s="5">
         <v>100364</v>
@@ -4765,14 +4765,14 @@
       </c>
       <c r="T27" s="9">
         <f t="shared" si="6"/>
-        <v>48151</v>
+        <v>48154</v>
       </c>
       <c r="U27" s="8">
-        <v>54582</v>
+        <v>54585</v>
       </c>
       <c r="V27" s="10">
         <f t="shared" si="7"/>
-        <v>0.5438404208680403</v>
+        <v>0.54387031206408676</v>
       </c>
       <c r="W27" s="5">
         <v>96252</v>
@@ -4782,14 +4782,14 @@
       </c>
       <c r="Y27" s="9">
         <f t="shared" si="8"/>
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="Z27" s="8">
-        <v>55292</v>
+        <v>55295</v>
       </c>
       <c r="AA27" s="10">
         <f t="shared" si="9"/>
-        <v>0.57445040103062794</v>
+        <v>0.57448156921414617</v>
       </c>
       <c r="AB27" s="5">
         <v>156081</v>
@@ -4799,14 +4799,14 @@
       </c>
       <c r="AD27" s="9">
         <f t="shared" si="10"/>
-        <v>70845</v>
+        <v>70850</v>
       </c>
       <c r="AE27" s="8">
-        <v>125723</v>
+        <v>125728</v>
       </c>
       <c r="AF27" s="10">
         <f t="shared" si="11"/>
-        <v>0.80549842709874997</v>
+        <v>0.80553046174742604</v>
       </c>
       <c r="AG27" s="5">
         <v>90207</v>
@@ -4816,14 +4816,14 @@
       </c>
       <c r="AI27" s="9">
         <f t="shared" si="12"/>
-        <v>43205</v>
+        <v>43209</v>
       </c>
       <c r="AJ27" s="8">
-        <v>56359</v>
+        <v>56363</v>
       </c>
       <c r="AK27" s="10">
         <f t="shared" si="13"/>
-        <v>0.62477413061070652</v>
+        <v>0.62481847306750027</v>
       </c>
       <c r="AL27" s="5">
         <v>89207</v>
@@ -4833,14 +4833,14 @@
       </c>
       <c r="AN27" s="9">
         <f t="shared" si="14"/>
-        <v>43643</v>
+        <v>43647</v>
       </c>
       <c r="AO27" s="8">
-        <v>57096</v>
+        <v>57100</v>
       </c>
       <c r="AP27" s="10">
         <f t="shared" si="15"/>
-        <v>0.64003945878686652</v>
+        <v>0.64008429831739666</v>
       </c>
       <c r="AQ27" s="22">
         <v>161396</v>
@@ -4850,14 +4850,14 @@
       </c>
       <c r="AS27" s="9">
         <f t="shared" si="16"/>
-        <v>52372</v>
+        <v>52383</v>
       </c>
       <c r="AT27" s="8">
-        <v>131350</v>
+        <v>131361</v>
       </c>
       <c r="AU27" s="10">
         <f t="shared" si="17"/>
-        <v>0.81383677414557987</v>
+        <v>0.81390492949019799</v>
       </c>
       <c r="AV27" s="22">
         <v>108391</v>
@@ -4867,14 +4867,14 @@
       </c>
       <c r="AX27" s="9">
         <f t="shared" si="18"/>
-        <v>57642</v>
+        <v>57652</v>
       </c>
       <c r="AY27" s="9">
-        <v>81710</v>
+        <v>81720</v>
       </c>
       <c r="AZ27" s="10">
         <f t="shared" si="19"/>
-        <v>0.75384487641962894</v>
+        <v>0.75393713500198356</v>
       </c>
       <c r="BA27" s="22">
         <v>101826</v>
@@ -4884,14 +4884,14 @@
       </c>
       <c r="BC27" s="9">
         <f t="shared" si="20"/>
-        <v>56623</v>
+        <v>56633</v>
       </c>
       <c r="BD27" s="8">
-        <v>83623</v>
+        <v>83633</v>
       </c>
       <c r="BE27" s="10">
         <f t="shared" si="21"/>
-        <v>0.82123426236913954</v>
+        <v>0.82133246911397872</v>
       </c>
       <c r="BF27" s="9">
         <v>155251</v>
@@ -4901,14 +4901,14 @@
       </c>
       <c r="BH27" s="9">
         <f t="shared" si="22"/>
-        <v>92672</v>
+        <v>92683</v>
       </c>
       <c r="BI27" s="6">
-        <v>135895</v>
+        <v>135906</v>
       </c>
       <c r="BJ27" s="10">
         <f t="shared" si="23"/>
-        <v>0.87532447456055029</v>
+        <v>0.8753953275663281</v>
       </c>
     </row>
     <row r="28" spans="1:62" x14ac:dyDescent="0.3">
@@ -4926,14 +4926,14 @@
       </c>
       <c r="E28" s="9">
         <f t="shared" si="0"/>
-        <v>71296</v>
+        <v>71299</v>
       </c>
       <c r="F28" s="8">
-        <v>190569</v>
+        <v>190572</v>
       </c>
       <c r="G28" s="10">
         <f t="shared" si="1"/>
-        <v>0.31246044420542451</v>
+        <v>0.31246536306070849</v>
       </c>
       <c r="H28" s="5">
         <v>562058</v>
@@ -4943,14 +4943,14 @@
       </c>
       <c r="J28" s="9">
         <f t="shared" si="2"/>
-        <v>80700</v>
+        <v>80702</v>
       </c>
       <c r="K28" s="8">
-        <v>190258</v>
+        <v>190260</v>
       </c>
       <c r="L28" s="10">
         <f t="shared" si="3"/>
-        <v>0.33850243213333853</v>
+        <v>0.33850599048496777</v>
       </c>
       <c r="M28" s="5">
         <v>606073</v>
@@ -4960,14 +4960,14 @@
       </c>
       <c r="O28" s="9">
         <f t="shared" si="4"/>
-        <v>317128</v>
+        <v>317136</v>
       </c>
       <c r="P28" s="8">
-        <v>515627</v>
+        <v>515635</v>
       </c>
       <c r="Q28" s="10">
         <f t="shared" si="5"/>
-        <v>0.85076715181174545</v>
+        <v>0.85078035154181098</v>
       </c>
       <c r="R28" s="5">
         <v>322040</v>
@@ -4977,14 +4977,14 @@
       </c>
       <c r="T28" s="9">
         <f t="shared" si="6"/>
-        <v>155942</v>
+        <v>155944</v>
       </c>
       <c r="U28" s="8">
-        <v>192531</v>
+        <v>192533</v>
       </c>
       <c r="V28" s="10">
         <f t="shared" si="7"/>
-        <v>0.59784809340454603</v>
+        <v>0.59785430381319093</v>
       </c>
       <c r="W28" s="5">
         <v>307068</v>
@@ -4994,14 +4994,14 @@
       </c>
       <c r="Y28" s="9">
         <f t="shared" si="8"/>
-        <v>148998</v>
+        <v>149001</v>
       </c>
       <c r="Z28" s="8">
-        <v>193172</v>
+        <v>193175</v>
       </c>
       <c r="AA28" s="10">
         <f t="shared" si="9"/>
-        <v>0.62908541430562614</v>
+        <v>0.62909518412859688</v>
       </c>
       <c r="AB28" s="5">
         <v>616763</v>
@@ -5011,14 +5011,14 @@
       </c>
       <c r="AD28" s="9">
         <f t="shared" si="10"/>
-        <v>237483</v>
+        <v>237488</v>
       </c>
       <c r="AE28" s="8">
-        <v>521353</v>
+        <v>521358</v>
       </c>
       <c r="AF28" s="10">
         <f t="shared" si="11"/>
-        <v>0.84530524691007725</v>
+        <v>0.84531335375176531</v>
       </c>
       <c r="AG28" s="5">
         <v>279354</v>
@@ -5028,14 +5028,14 @@
       </c>
       <c r="AI28" s="9">
         <f t="shared" si="12"/>
-        <v>132094</v>
+        <v>132097</v>
       </c>
       <c r="AJ28" s="8">
-        <v>194997</v>
+        <v>195000</v>
       </c>
       <c r="AK28" s="10">
         <f t="shared" si="13"/>
-        <v>0.69802830816813077</v>
+        <v>0.69803904723039589</v>
       </c>
       <c r="AL28" s="5">
         <v>276143</v>
@@ -5045,14 +5045,14 @@
       </c>
       <c r="AN28" s="9">
         <f t="shared" si="14"/>
-        <v>129664</v>
+        <v>129667</v>
       </c>
       <c r="AO28" s="8">
-        <v>196862</v>
+        <v>196865</v>
       </c>
       <c r="AP28" s="10">
         <f t="shared" si="15"/>
-        <v>0.71289875173370321</v>
+        <v>0.71290961567014188</v>
       </c>
       <c r="AQ28" s="22">
         <v>625592</v>
@@ -5062,14 +5062,14 @@
       </c>
       <c r="AS28" s="9">
         <f t="shared" si="16"/>
-        <v>155350</v>
+        <v>155356</v>
       </c>
       <c r="AT28" s="8">
-        <v>532662</v>
+        <v>532668</v>
       </c>
       <c r="AU28" s="10">
         <f t="shared" si="17"/>
-        <v>0.85145270399877238</v>
+        <v>0.85146229491425718</v>
       </c>
       <c r="AV28" s="22">
         <v>329857</v>
@@ -5079,14 +5079,14 @@
       </c>
       <c r="AX28" s="9">
         <f t="shared" si="18"/>
-        <v>153800</v>
+        <v>153805</v>
       </c>
       <c r="AY28" s="9">
-        <v>254203</v>
+        <v>254208</v>
       </c>
       <c r="AZ28" s="10">
         <f t="shared" si="19"/>
-        <v>0.77064606784151923</v>
+        <v>0.77066122592517361</v>
       </c>
       <c r="BA28" s="22">
         <v>323426</v>
@@ -5096,14 +5096,14 @@
       </c>
       <c r="BC28" s="9">
         <f t="shared" si="20"/>
-        <v>140105</v>
+        <v>140111</v>
       </c>
       <c r="BD28" s="8">
-        <v>257977</v>
+        <v>257983</v>
       </c>
       <c r="BE28" s="10">
         <f t="shared" si="21"/>
-        <v>0.79763840878593562</v>
+        <v>0.79765696017017806</v>
       </c>
       <c r="BF28" s="9">
         <v>619161</v>
@@ -5113,14 +5113,14 @@
       </c>
       <c r="BH28" s="9">
         <f t="shared" si="22"/>
-        <v>279104</v>
+        <v>279109</v>
       </c>
       <c r="BI28" s="6">
-        <v>545816</v>
+        <v>545821</v>
       </c>
       <c r="BJ28" s="10">
         <f t="shared" si="23"/>
-        <v>0.88154131154901549</v>
+        <v>0.88154938699304386</v>
       </c>
     </row>
     <row r="29" spans="1:62" x14ac:dyDescent="0.3">
@@ -5172,14 +5172,14 @@
       </c>
       <c r="O29" s="9">
         <f t="shared" si="4"/>
-        <v>79875</v>
+        <v>79876</v>
       </c>
       <c r="P29" s="8">
-        <v>129715</v>
+        <v>129716</v>
       </c>
       <c r="Q29" s="10">
         <f t="shared" si="5"/>
-        <v>0.89720356626572695</v>
+        <v>0.89721048299522055</v>
       </c>
       <c r="R29" s="5">
         <v>86442</v>
@@ -5274,14 +5274,14 @@
       </c>
       <c r="AS29" s="9">
         <f t="shared" si="16"/>
-        <v>41577</v>
+        <v>41578</v>
       </c>
       <c r="AT29" s="8">
-        <v>138702</v>
+        <v>138703</v>
       </c>
       <c r="AU29" s="10">
         <f t="shared" si="17"/>
-        <v>0.89185383324438505</v>
+        <v>0.8918602632441921</v>
       </c>
       <c r="AV29" s="22">
         <v>96040</v>
@@ -5291,14 +5291,14 @@
       </c>
       <c r="AX29" s="9">
         <f t="shared" si="18"/>
-        <v>51816</v>
+        <v>51817</v>
       </c>
       <c r="AY29" s="9">
-        <v>83588</v>
+        <v>83589</v>
       </c>
       <c r="AZ29" s="10">
         <f t="shared" si="19"/>
-        <v>0.87034568929612666</v>
+        <v>0.8703561016243232</v>
       </c>
       <c r="BA29" s="22">
         <v>92820</v>
@@ -5350,14 +5350,14 @@
       </c>
       <c r="E30" s="9">
         <f t="shared" si="0"/>
-        <v>30453</v>
+        <v>30456</v>
       </c>
       <c r="F30" s="8">
-        <v>77351</v>
+        <v>77354</v>
       </c>
       <c r="G30" s="10">
         <f t="shared" si="1"/>
-        <v>0.3478888569064153</v>
+        <v>0.34790234951246718</v>
       </c>
       <c r="H30" s="5">
         <v>196739</v>
@@ -5367,14 +5367,14 @@
       </c>
       <c r="J30" s="9">
         <f t="shared" si="2"/>
-        <v>35383</v>
+        <v>35386</v>
       </c>
       <c r="K30" s="8">
-        <v>77589</v>
+        <v>77592</v>
       </c>
       <c r="L30" s="10">
         <f t="shared" si="3"/>
-        <v>0.39437528908858943</v>
+        <v>0.39439053771748356</v>
       </c>
       <c r="M30" s="5">
         <v>227236</v>
@@ -5384,14 +5384,14 @@
       </c>
       <c r="O30" s="9">
         <f t="shared" si="4"/>
-        <v>132027</v>
+        <v>132034</v>
       </c>
       <c r="P30" s="8">
-        <v>197256</v>
+        <v>197263</v>
       </c>
       <c r="Q30" s="10">
         <f t="shared" si="5"/>
-        <v>0.86806667957541939</v>
+        <v>0.86809748455350388</v>
       </c>
       <c r="R30" s="5">
         <v>127114</v>
@@ -5401,14 +5401,14 @@
       </c>
       <c r="T30" s="9">
         <f t="shared" si="6"/>
-        <v>67308</v>
+        <v>67309</v>
       </c>
       <c r="U30" s="8">
-        <v>79307</v>
+        <v>79308</v>
       </c>
       <c r="V30" s="10">
         <f t="shared" si="7"/>
-        <v>0.62390452664537344</v>
+        <v>0.62391239359944617</v>
       </c>
       <c r="W30" s="5">
         <v>123894</v>
@@ -5418,14 +5418,14 @@
       </c>
       <c r="Y30" s="9">
         <f t="shared" si="8"/>
-        <v>64460</v>
+        <v>64461</v>
       </c>
       <c r="Z30" s="8">
-        <v>79902</v>
+        <v>79903</v>
       </c>
       <c r="AA30" s="10">
         <f t="shared" si="9"/>
-        <v>0.64492227226500076</v>
+        <v>0.64493034368088853</v>
       </c>
       <c r="AB30" s="5">
         <v>242455</v>
@@ -5435,14 +5435,14 @@
       </c>
       <c r="AD30" s="9">
         <f t="shared" si="10"/>
-        <v>99278</v>
+        <v>99286</v>
       </c>
       <c r="AE30" s="8">
-        <v>203357</v>
+        <v>203365</v>
       </c>
       <c r="AF30" s="10">
         <f t="shared" si="11"/>
-        <v>0.83874120970901822</v>
+        <v>0.83877420552267434</v>
       </c>
       <c r="AG30" s="5">
         <v>117700</v>
@@ -5452,14 +5452,14 @@
       </c>
       <c r="AI30" s="9">
         <f t="shared" si="12"/>
-        <v>61295</v>
+        <v>61298</v>
       </c>
       <c r="AJ30" s="8">
-        <v>81933</v>
+        <v>81936</v>
       </c>
       <c r="AK30" s="10">
         <f t="shared" si="13"/>
-        <v>0.69611724723874258</v>
+        <v>0.69614273576890395</v>
       </c>
       <c r="AL30" s="5">
         <v>115490</v>
@@ -5469,14 +5469,14 @@
       </c>
       <c r="AN30" s="9">
         <f t="shared" si="14"/>
-        <v>62020</v>
+        <v>62026</v>
       </c>
       <c r="AO30" s="8">
-        <v>83080</v>
+        <v>83086</v>
       </c>
       <c r="AP30" s="10">
         <f t="shared" si="15"/>
-        <v>0.71936964239328083</v>
+        <v>0.71942159494328517</v>
       </c>
       <c r="AQ30" s="22">
         <v>248265</v>
@@ -5486,14 +5486,14 @@
       </c>
       <c r="AS30" s="9">
         <f t="shared" si="16"/>
-        <v>74356</v>
+        <v>74370</v>
       </c>
       <c r="AT30" s="8">
-        <v>212345</v>
+        <v>212359</v>
       </c>
       <c r="AU30" s="10">
         <f t="shared" si="17"/>
-        <v>0.85531589229251004</v>
+        <v>0.85537228364852069</v>
       </c>
       <c r="AV30" s="22">
         <v>136681</v>
@@ -5503,14 +5503,14 @@
       </c>
       <c r="AX30" s="9">
         <f t="shared" si="18"/>
-        <v>78439</v>
+        <v>78444</v>
       </c>
       <c r="AY30" s="9">
-        <v>110626</v>
+        <v>110631</v>
       </c>
       <c r="AZ30" s="10">
         <f t="shared" si="19"/>
-        <v>0.8093736510561087</v>
+        <v>0.80941023258536304</v>
       </c>
       <c r="BA30" s="22">
         <v>130520</v>
@@ -5520,14 +5520,14 @@
       </c>
       <c r="BC30" s="9">
         <f t="shared" si="20"/>
-        <v>76621</v>
+        <v>76627</v>
       </c>
       <c r="BD30" s="8">
-        <v>113432</v>
+        <v>113438</v>
       </c>
       <c r="BE30" s="10">
         <f t="shared" si="21"/>
-        <v>0.86907753600980697</v>
+        <v>0.86912350597609567</v>
       </c>
       <c r="BF30" s="9">
         <v>245647</v>
@@ -5537,14 +5537,14 @@
       </c>
       <c r="BH30" s="9">
         <f t="shared" si="22"/>
-        <v>141105</v>
+        <v>141116</v>
       </c>
       <c r="BI30" s="6">
-        <v>221798</v>
+        <v>221809</v>
       </c>
       <c r="BJ30" s="10">
         <f t="shared" si="23"/>
-        <v>0.90291353039117106</v>
+        <v>0.90295831009538075</v>
       </c>
     </row>
     <row r="31" spans="1:62" x14ac:dyDescent="0.3">
@@ -5562,14 +5562,14 @@
       </c>
       <c r="E31" s="9">
         <f t="shared" si="0"/>
-        <v>16304</v>
+        <v>16308</v>
       </c>
       <c r="F31" s="8">
-        <v>41818</v>
+        <v>41822</v>
       </c>
       <c r="G31" s="10">
         <f t="shared" si="1"/>
-        <v>0.39205722696717699</v>
+        <v>0.39209472825628383</v>
       </c>
       <c r="H31" s="5">
         <v>97781</v>
@@ -5579,14 +5579,14 @@
       </c>
       <c r="J31" s="9">
         <f t="shared" si="2"/>
-        <v>18550</v>
+        <v>18553</v>
       </c>
       <c r="K31" s="8">
-        <v>41898</v>
+        <v>41901</v>
       </c>
       <c r="L31" s="10">
         <f t="shared" si="3"/>
-        <v>0.42848815209498781</v>
+        <v>0.42851883290209752</v>
       </c>
       <c r="M31" s="5">
         <v>107995</v>
@@ -5596,14 +5596,14 @@
       </c>
       <c r="O31" s="9">
         <f t="shared" si="4"/>
-        <v>64552</v>
+        <v>64556</v>
       </c>
       <c r="P31" s="8">
-        <v>98081</v>
+        <v>98085</v>
       </c>
       <c r="Q31" s="10">
         <f t="shared" si="5"/>
-        <v>0.90819945367841104</v>
+        <v>0.9082364924302051</v>
       </c>
       <c r="R31" s="5">
         <v>65023</v>
@@ -5613,14 +5613,14 @@
       </c>
       <c r="T31" s="9">
         <f t="shared" si="6"/>
-        <v>35236</v>
+        <v>35239</v>
       </c>
       <c r="U31" s="8">
-        <v>42837</v>
+        <v>42840</v>
       </c>
       <c r="V31" s="10">
         <f t="shared" si="7"/>
-        <v>0.65879765621395503</v>
+        <v>0.65884379373452473</v>
       </c>
       <c r="W31" s="5">
         <v>62560</v>
@@ -5630,14 +5630,14 @@
       </c>
       <c r="Y31" s="9">
         <f t="shared" si="8"/>
-        <v>33332</v>
+        <v>33335</v>
       </c>
       <c r="Z31" s="8">
-        <v>43148</v>
+        <v>43151</v>
       </c>
       <c r="AA31" s="10">
         <f t="shared" si="9"/>
-        <v>0.68970588235294117</v>
+        <v>0.6897538363171356</v>
       </c>
       <c r="AB31" s="5">
         <v>113499</v>
@@ -5647,14 +5647,14 @@
       </c>
       <c r="AD31" s="9">
         <f t="shared" si="10"/>
-        <v>52957</v>
+        <v>52962</v>
       </c>
       <c r="AE31" s="8">
-        <v>101289</v>
+        <v>101294</v>
       </c>
       <c r="AF31" s="10">
         <f t="shared" si="11"/>
-        <v>0.89242195966484283</v>
+        <v>0.89246601291641336</v>
       </c>
       <c r="AG31" s="5">
         <v>58990</v>
@@ -5664,14 +5664,14 @@
       </c>
       <c r="AI31" s="9">
         <f t="shared" si="12"/>
-        <v>31524</v>
+        <v>31526</v>
       </c>
       <c r="AJ31" s="8">
-        <v>43725</v>
+        <v>43727</v>
       </c>
       <c r="AK31" s="10">
         <f t="shared" si="13"/>
-        <v>0.74122732666553648</v>
+        <v>0.74126123071707073</v>
       </c>
       <c r="AL31" s="5">
         <v>57896</v>
@@ -5681,14 +5681,14 @@
       </c>
       <c r="AN31" s="9">
         <f t="shared" si="14"/>
-        <v>30987</v>
+        <v>30990</v>
       </c>
       <c r="AO31" s="8">
-        <v>44039</v>
+        <v>44042</v>
       </c>
       <c r="AP31" s="10">
         <f t="shared" si="15"/>
-        <v>0.76065704021003178</v>
+        <v>0.76070885726129611</v>
       </c>
       <c r="AQ31" s="22">
         <v>115872</v>
@@ -5698,14 +5698,14 @@
       </c>
       <c r="AS31" s="9">
         <f t="shared" si="16"/>
-        <v>37955</v>
+        <v>37961</v>
       </c>
       <c r="AT31" s="8">
-        <v>104650</v>
+        <v>104656</v>
       </c>
       <c r="AU31" s="10">
         <f t="shared" si="17"/>
-        <v>0.90315175365921019</v>
+        <v>0.90320353493510075</v>
       </c>
       <c r="AV31" s="22">
         <v>66185</v>
@@ -5715,14 +5715,14 @@
       </c>
       <c r="AX31" s="9">
         <f t="shared" si="18"/>
-        <v>37449</v>
+        <v>37457</v>
       </c>
       <c r="AY31" s="9">
-        <v>57171</v>
+        <v>57179</v>
       </c>
       <c r="AZ31" s="10">
         <f t="shared" si="19"/>
-        <v>0.86380599833799199</v>
+        <v>0.86392687164765425</v>
       </c>
       <c r="BA31" s="22">
         <v>65739</v>
@@ -5732,14 +5732,14 @@
       </c>
       <c r="BC31" s="9">
         <f t="shared" si="20"/>
-        <v>36881</v>
+        <v>36888</v>
       </c>
       <c r="BD31" s="8">
-        <v>59450</v>
+        <v>59457</v>
       </c>
       <c r="BE31" s="10">
         <f t="shared" si="21"/>
-        <v>0.9043338048951155</v>
+        <v>0.90444028658787023</v>
       </c>
       <c r="BF31" s="9">
         <v>116311</v>
@@ -5749,14 +5749,14 @@
       </c>
       <c r="BH31" s="9">
         <f t="shared" si="22"/>
-        <v>76432</v>
+        <v>76439</v>
       </c>
       <c r="BI31" s="6">
-        <v>109212</v>
+        <v>109219</v>
       </c>
       <c r="BJ31" s="10">
         <f t="shared" si="23"/>
-        <v>0.93896536011211318</v>
+        <v>0.93902554358573131</v>
       </c>
     </row>
     <row r="32" spans="1:62" x14ac:dyDescent="0.3">
@@ -5808,14 +5808,14 @@
       </c>
       <c r="O32" s="9">
         <f t="shared" si="4"/>
-        <v>199311</v>
+        <v>199314</v>
       </c>
       <c r="P32" s="8">
-        <v>329565</v>
+        <v>329568</v>
       </c>
       <c r="Q32" s="10">
         <f t="shared" si="5"/>
-        <v>0.93330784588590121</v>
+        <v>0.93331634170171196</v>
       </c>
       <c r="R32" s="5">
         <v>166950</v>
@@ -5825,14 +5825,14 @@
       </c>
       <c r="T32" s="9">
         <f t="shared" si="6"/>
-        <v>90908</v>
+        <v>90909</v>
       </c>
       <c r="U32" s="8">
-        <v>114750</v>
+        <v>114751</v>
       </c>
       <c r="V32" s="10">
         <f t="shared" si="7"/>
-        <v>0.68733153638814015</v>
+        <v>0.68733752620545074</v>
       </c>
       <c r="W32" s="5">
         <v>161498</v>
@@ -5859,14 +5859,14 @@
       </c>
       <c r="AD32" s="9">
         <f t="shared" si="10"/>
-        <v>160703</v>
+        <v>160706</v>
       </c>
       <c r="AE32" s="8">
-        <v>338746</v>
+        <v>338749</v>
       </c>
       <c r="AF32" s="10">
         <f t="shared" si="11"/>
-        <v>0.90494916196043018</v>
+        <v>0.90495717636498663</v>
       </c>
       <c r="AG32" s="5">
         <v>155463</v>
@@ -5910,14 +5910,14 @@
       </c>
       <c r="AS32" s="9">
         <f t="shared" si="16"/>
-        <v>111942</v>
+        <v>111944</v>
       </c>
       <c r="AT32" s="8">
-        <v>348806</v>
+        <v>348808</v>
       </c>
       <c r="AU32" s="10">
         <f t="shared" si="17"/>
-        <v>0.92068955505169547</v>
+        <v>0.9206948341441139</v>
       </c>
       <c r="AV32" s="22">
         <v>171744</v>
@@ -5927,14 +5927,14 @@
       </c>
       <c r="AX32" s="9">
         <f t="shared" si="18"/>
-        <v>96171</v>
+        <v>96174</v>
       </c>
       <c r="AY32" s="9">
-        <v>152306</v>
+        <v>152309</v>
       </c>
       <c r="AZ32" s="10">
         <f t="shared" si="19"/>
-        <v>0.88681991801751447</v>
+        <v>0.88683738587665362</v>
       </c>
       <c r="BA32" s="22">
         <v>169380</v>
@@ -5944,14 +5944,14 @@
       </c>
       <c r="BC32" s="9">
         <f t="shared" si="20"/>
-        <v>93097</v>
+        <v>93103</v>
       </c>
       <c r="BD32" s="8">
-        <v>156559</v>
+        <v>156565</v>
       </c>
       <c r="BE32" s="10">
         <f t="shared" si="21"/>
-        <v>0.92430629354115013</v>
+        <v>0.92434171684968713</v>
       </c>
       <c r="BF32" s="9">
         <v>378386</v>
@@ -5961,14 +5961,14 @@
       </c>
       <c r="BH32" s="9">
         <f t="shared" si="22"/>
-        <v>248533</v>
+        <v>248542</v>
       </c>
       <c r="BI32" s="6">
-        <v>358211</v>
+        <v>358220</v>
       </c>
       <c r="BJ32" s="10">
         <f t="shared" si="23"/>
-        <v>0.94668143113117298</v>
+        <v>0.94670521636635607</v>
       </c>
     </row>
     <row r="33" spans="1:63" x14ac:dyDescent="0.3">
@@ -5986,14 +5986,14 @@
       </c>
       <c r="E33" s="9">
         <f t="shared" si="0"/>
-        <v>57415</v>
+        <v>57417</v>
       </c>
       <c r="F33" s="8">
-        <v>294973</v>
+        <v>294975</v>
       </c>
       <c r="G33" s="10">
         <f t="shared" si="1"/>
-        <v>0.33093542129691439</v>
+        <v>0.33093766513225725</v>
       </c>
       <c r="H33" s="5">
         <v>840037</v>
@@ -6003,14 +6003,14 @@
       </c>
       <c r="J33" s="9">
         <f t="shared" si="2"/>
-        <v>65400</v>
+        <v>65403</v>
       </c>
       <c r="K33" s="8">
-        <v>295271</v>
+        <v>295274</v>
       </c>
       <c r="L33" s="10">
         <f t="shared" si="3"/>
-        <v>0.35149761260515905</v>
+        <v>0.35150118387642448</v>
       </c>
       <c r="M33" s="5">
         <v>888717</v>
@@ -6020,14 +6020,14 @@
       </c>
       <c r="O33" s="9">
         <f t="shared" si="4"/>
-        <v>331345</v>
+        <v>331358</v>
       </c>
       <c r="P33" s="8">
-        <v>837819</v>
+        <v>837832</v>
       </c>
       <c r="Q33" s="10">
         <f t="shared" si="5"/>
-        <v>0.94272867515755854</v>
+        <v>0.942743302986215</v>
       </c>
       <c r="R33" s="5">
         <v>410545</v>
@@ -6037,14 +6037,14 @@
       </c>
       <c r="T33" s="9">
         <f t="shared" si="6"/>
-        <v>191541</v>
+        <v>191546</v>
       </c>
       <c r="U33" s="8">
-        <v>299397</v>
+        <v>299402</v>
       </c>
       <c r="V33" s="10">
         <f t="shared" si="7"/>
-        <v>0.72926719360849601</v>
+        <v>0.72927937254137798</v>
       </c>
       <c r="W33" s="5">
         <v>395753</v>
@@ -6054,14 +6054,14 @@
       </c>
       <c r="Y33" s="9">
         <f t="shared" si="8"/>
-        <v>163283</v>
+        <v>163286</v>
       </c>
       <c r="Z33" s="8">
-        <v>301314</v>
+        <v>301317</v>
       </c>
       <c r="AA33" s="10">
         <f t="shared" si="9"/>
-        <v>0.76136883359064866</v>
+        <v>0.76137641407645673</v>
       </c>
       <c r="AB33" s="5">
         <v>919225</v>
@@ -6071,14 +6071,14 @@
       </c>
       <c r="AD33" s="9">
         <f t="shared" si="10"/>
-        <v>217510</v>
+        <v>217523</v>
       </c>
       <c r="AE33" s="8">
-        <v>863381</v>
+        <v>863394</v>
       </c>
       <c r="AF33" s="10">
         <f t="shared" si="11"/>
-        <v>0.93924882373738749</v>
+        <v>0.93926296608556126</v>
       </c>
       <c r="AG33" s="5">
         <v>374721</v>
@@ -6088,14 +6088,14 @@
       </c>
       <c r="AI33" s="9">
         <f t="shared" si="12"/>
-        <v>140246</v>
+        <v>140252</v>
       </c>
       <c r="AJ33" s="8">
-        <v>305398</v>
+        <v>305404</v>
       </c>
       <c r="AK33" s="10">
         <f t="shared" si="13"/>
-        <v>0.81500102743107539</v>
+        <v>0.81501703934393854</v>
       </c>
       <c r="AL33" s="5">
         <v>367134</v>
@@ -6105,14 +6105,14 @@
       </c>
       <c r="AN33" s="9">
         <f t="shared" si="14"/>
-        <v>142082</v>
+        <v>142090</v>
       </c>
       <c r="AO33" s="8">
-        <v>307663</v>
+        <v>307671</v>
       </c>
       <c r="AP33" s="10">
         <f t="shared" si="15"/>
-        <v>0.83801282365566798</v>
+        <v>0.83803461406461943</v>
       </c>
       <c r="AQ33" s="22">
         <v>933808</v>
@@ -6122,14 +6122,14 @@
       </c>
       <c r="AS33" s="9">
         <f t="shared" si="16"/>
-        <v>111333</v>
+        <v>111349</v>
       </c>
       <c r="AT33" s="8">
-        <v>891158</v>
+        <v>891174</v>
       </c>
       <c r="AU33" s="10">
         <f t="shared" si="17"/>
-        <v>0.95432679951339028</v>
+        <v>0.95434393365659753</v>
       </c>
       <c r="AV33" s="22">
         <v>471208</v>
@@ -6139,14 +6139,14 @@
       </c>
       <c r="AX33" s="9">
         <f t="shared" si="18"/>
-        <v>148143</v>
+        <v>148147</v>
       </c>
       <c r="AY33" s="9">
-        <v>435384</v>
+        <v>435388</v>
       </c>
       <c r="AZ33" s="10">
         <f t="shared" si="19"/>
-        <v>0.92397412607595797</v>
+        <v>0.92398261489618172</v>
       </c>
       <c r="BA33" s="22">
         <v>469534</v>
@@ -6156,14 +6156,14 @@
       </c>
       <c r="BC33" s="9">
         <f t="shared" si="20"/>
-        <v>133504</v>
+        <v>133508</v>
       </c>
       <c r="BD33" s="8">
-        <v>447359</v>
+        <v>447363</v>
       </c>
       <c r="BE33" s="10">
         <f t="shared" si="21"/>
-        <v>0.95277232319704219</v>
+        <v>0.95278084228192206</v>
       </c>
       <c r="BF33" s="9">
         <v>935950</v>
@@ -6173,14 +6173,14 @@
       </c>
       <c r="BH33" s="9">
         <f t="shared" si="22"/>
-        <v>270358</v>
+        <v>270368</v>
       </c>
       <c r="BI33" s="6">
-        <v>916101</v>
+        <v>916111</v>
       </c>
       <c r="BJ33" s="10">
         <f t="shared" si="23"/>
-        <v>0.97879267054864039</v>
+        <v>0.97880335488006842</v>
       </c>
     </row>
     <row r="34" spans="1:63" x14ac:dyDescent="0.3">
@@ -6478,14 +6478,14 @@
       </c>
       <c r="AD35" s="9">
         <f t="shared" si="10"/>
-        <v>4176</v>
+        <v>4177</v>
       </c>
       <c r="AE35" s="8">
-        <v>13003</v>
+        <v>13004</v>
       </c>
       <c r="AF35" s="10">
         <f t="shared" si="11"/>
-        <v>0.90524923419660264</v>
+        <v>0.90531885268727375</v>
       </c>
       <c r="AG35" s="5">
         <v>9452</v>
@@ -6529,14 +6529,14 @@
       </c>
       <c r="AS35" s="9">
         <f t="shared" si="16"/>
-        <v>2433</v>
+        <v>2434</v>
       </c>
       <c r="AT35" s="8">
-        <v>13247</v>
+        <v>13248</v>
       </c>
       <c r="AU35" s="10">
         <f t="shared" si="17"/>
-        <v>0.91503764592111625</v>
+        <v>0.9151067210057332</v>
       </c>
       <c r="AV35" s="22">
         <v>10244</v>
@@ -6563,14 +6563,14 @@
       </c>
       <c r="BC35" s="9">
         <f t="shared" si="20"/>
-        <v>3159</v>
+        <v>3160</v>
       </c>
       <c r="BD35" s="8">
-        <v>9140</v>
+        <v>9141</v>
       </c>
       <c r="BE35" s="10">
         <f t="shared" si="21"/>
-        <v>0.89441236911635191</v>
+        <v>0.89451022604951558</v>
       </c>
       <c r="BF35" s="9">
         <v>13967</v>
@@ -6580,14 +6580,14 @@
       </c>
       <c r="BH35" s="9">
         <f t="shared" si="22"/>
-        <v>4550</v>
+        <v>4551</v>
       </c>
       <c r="BI35" s="6">
-        <v>13388</v>
+        <v>13389</v>
       </c>
       <c r="BJ35" s="10">
         <f t="shared" si="23"/>
-        <v>0.95854514212071307</v>
+        <v>0.9586167394572922</v>
       </c>
     </row>
     <row r="36" spans="1:63" x14ac:dyDescent="0.3">
@@ -6605,14 +6605,14 @@
       </c>
       <c r="E36" s="9">
         <f t="shared" si="0"/>
-        <v>160248</v>
+        <v>160260</v>
       </c>
       <c r="F36" s="8">
-        <v>403998</v>
+        <v>404010</v>
       </c>
       <c r="G36" s="10">
         <f t="shared" si="1"/>
-        <v>0.29321941267280255</v>
+        <v>0.29322812220342415</v>
       </c>
       <c r="H36" s="5">
         <v>1292614</v>
@@ -6622,14 +6622,14 @@
       </c>
       <c r="J36" s="9">
         <f t="shared" si="2"/>
-        <v>174065</v>
+        <v>174079</v>
       </c>
       <c r="K36" s="8">
-        <v>404197</v>
+        <v>404211</v>
       </c>
       <c r="L36" s="10">
         <f t="shared" si="3"/>
-        <v>0.31269737137304715</v>
+        <v>0.31270820213923106</v>
       </c>
       <c r="M36" s="5">
         <v>1376699</v>
@@ -6639,14 +6639,14 @@
       </c>
       <c r="O36" s="9">
         <f t="shared" si="4"/>
-        <v>743372</v>
+        <v>743393</v>
       </c>
       <c r="P36" s="8">
-        <v>1226706</v>
+        <v>1226727</v>
       </c>
       <c r="Q36" s="10">
         <f t="shared" si="5"/>
-        <v>0.89104880587550361</v>
+        <v>0.89106405975452874</v>
       </c>
       <c r="R36" s="5">
         <v>745641</v>
@@ -6656,14 +6656,14 @@
       </c>
       <c r="T36" s="9">
         <f t="shared" si="6"/>
-        <v>301868</v>
+        <v>301879</v>
       </c>
       <c r="U36" s="8">
-        <v>409686</v>
+        <v>409697</v>
       </c>
       <c r="V36" s="10">
         <f t="shared" si="7"/>
-        <v>0.54944135314447573</v>
+        <v>0.54945610555213564</v>
       </c>
       <c r="W36" s="5">
         <v>686690</v>
@@ -6673,14 +6673,14 @@
       </c>
       <c r="Y36" s="9">
         <f t="shared" si="8"/>
-        <v>276499</v>
+        <v>276515</v>
       </c>
       <c r="Z36" s="8">
-        <v>412160</v>
+        <v>412176</v>
       </c>
       <c r="AA36" s="10">
         <f t="shared" si="9"/>
-        <v>0.60021261413447113</v>
+        <v>0.60023591431359125</v>
       </c>
       <c r="AB36" s="5">
         <v>1408098</v>
@@ -6690,14 +6690,14 @@
       </c>
       <c r="AD36" s="9">
         <f t="shared" si="10"/>
-        <v>511449</v>
+        <v>511488</v>
       </c>
       <c r="AE36" s="8">
-        <v>1248515</v>
+        <v>1248554</v>
       </c>
       <c r="AF36" s="10">
         <f t="shared" si="11"/>
-        <v>0.88666768932276019</v>
+        <v>0.88669538625862687</v>
       </c>
       <c r="AG36" s="5">
         <v>587071</v>
@@ -6707,14 +6707,14 @@
       </c>
       <c r="AI36" s="9">
         <f t="shared" si="12"/>
-        <v>248182</v>
+        <v>248195</v>
       </c>
       <c r="AJ36" s="8">
-        <v>417489</v>
+        <v>417502</v>
       </c>
       <c r="AK36" s="10">
         <f t="shared" si="13"/>
-        <v>0.71113885713993708</v>
+        <v>0.71116100096921842</v>
       </c>
       <c r="AL36" s="5">
         <v>562582</v>
@@ -6724,14 +6724,14 @@
       </c>
       <c r="AN36" s="9">
         <f t="shared" si="14"/>
-        <v>238159</v>
+        <v>238174</v>
       </c>
       <c r="AO36" s="8">
-        <v>421178</v>
+        <v>421193</v>
       </c>
       <c r="AP36" s="10">
         <f t="shared" si="15"/>
-        <v>0.74865175210013835</v>
+        <v>0.74867841487996412</v>
       </c>
       <c r="AQ36" s="22">
         <v>1406326</v>
@@ -6741,14 +6741,14 @@
       </c>
       <c r="AS36" s="9">
         <f t="shared" si="16"/>
-        <v>335724</v>
+        <v>335752</v>
       </c>
       <c r="AT36" s="8">
-        <v>1284212</v>
+        <v>1284240</v>
       </c>
       <c r="AU36" s="10">
         <f t="shared" si="17"/>
-        <v>0.91316807056116434</v>
+        <v>0.91318798059624862</v>
       </c>
       <c r="AV36" s="22">
         <v>685313</v>
@@ -6758,14 +6758,14 @@
       </c>
       <c r="AX36" s="9">
         <f t="shared" si="18"/>
-        <v>333867</v>
+        <v>333889</v>
       </c>
       <c r="AY36" s="9">
-        <v>603375</v>
+        <v>603397</v>
       </c>
       <c r="AZ36" s="10">
         <f t="shared" si="19"/>
-        <v>0.88043711413616843</v>
+        <v>0.88046921625592978</v>
       </c>
       <c r="BA36" s="22">
         <v>667446</v>
@@ -6775,14 +6775,14 @@
       </c>
       <c r="BC36" s="9">
         <f t="shared" si="20"/>
-        <v>306815</v>
+        <v>306846</v>
       </c>
       <c r="BD36" s="8">
-        <v>617005</v>
+        <v>617036</v>
       </c>
       <c r="BE36" s="10">
         <f t="shared" si="21"/>
-        <v>0.92442684501817374</v>
+        <v>0.92447329072314466</v>
       </c>
       <c r="BF36" s="9">
         <v>1363993</v>
@@ -6792,14 +6792,14 @@
       </c>
       <c r="BH36" s="9">
         <f t="shared" si="22"/>
-        <v>656276</v>
+        <v>656300</v>
       </c>
       <c r="BI36" s="6">
-        <v>1309741</v>
+        <v>1309765</v>
       </c>
       <c r="BJ36" s="10">
         <f t="shared" si="23"/>
-        <v>0.96022560233080378</v>
+        <v>0.96024319772902056</v>
       </c>
     </row>
     <row r="37" spans="1:63" x14ac:dyDescent="0.3">
@@ -6817,14 +6817,14 @@
       </c>
       <c r="E37" s="9">
         <f t="shared" si="0"/>
-        <v>126082</v>
+        <v>126093</v>
       </c>
       <c r="F37" s="8">
-        <v>409785</v>
+        <v>409796</v>
       </c>
       <c r="G37" s="10">
         <f t="shared" si="1"/>
-        <v>0.5592227365525072</v>
+        <v>0.55923774796117776</v>
       </c>
       <c r="H37" s="5">
         <v>674591</v>
@@ -6834,14 +6834,14 @@
       </c>
       <c r="J37" s="9">
         <f t="shared" si="2"/>
-        <v>147497</v>
+        <v>147506</v>
       </c>
       <c r="K37" s="8">
-        <v>413295</v>
+        <v>413304</v>
       </c>
       <c r="L37" s="10">
         <f t="shared" si="3"/>
-        <v>0.61266011553667332</v>
+        <v>0.61267345695391728</v>
       </c>
       <c r="M37" s="5">
         <v>737436</v>
@@ -6851,14 +6851,14 @@
       </c>
       <c r="O37" s="9">
         <f t="shared" si="4"/>
-        <v>346080</v>
+        <v>346095</v>
       </c>
       <c r="P37" s="8">
-        <v>645231</v>
+        <v>645246</v>
       </c>
       <c r="Q37" s="10">
         <f t="shared" si="5"/>
-        <v>0.87496542072803607</v>
+        <v>0.87498576147625018</v>
       </c>
       <c r="R37" s="5">
         <v>540612</v>
@@ -6868,14 +6868,14 @@
       </c>
       <c r="T37" s="9">
         <f t="shared" si="6"/>
-        <v>330366</v>
+        <v>330376</v>
       </c>
       <c r="U37" s="8">
-        <v>420059</v>
+        <v>420069</v>
       </c>
       <c r="V37" s="10">
         <f t="shared" si="7"/>
-        <v>0.77700642974998702</v>
+        <v>0.77702492730461037</v>
       </c>
       <c r="W37" s="5">
         <v>536259</v>
@@ -6885,14 +6885,14 @@
       </c>
       <c r="Y37" s="9">
         <f t="shared" si="8"/>
-        <v>307320</v>
+        <v>307335</v>
       </c>
       <c r="Z37" s="8">
-        <v>423749</v>
+        <v>423764</v>
       </c>
       <c r="AA37" s="10">
         <f t="shared" si="9"/>
-        <v>0.79019466339958866</v>
+        <v>0.79022263495810796</v>
       </c>
       <c r="AB37" s="5">
         <v>768520</v>
@@ -6902,14 +6902,14 @@
       </c>
       <c r="AD37" s="9">
         <f t="shared" si="10"/>
-        <v>226245</v>
+        <v>226265</v>
       </c>
       <c r="AE37" s="8">
-        <v>661183</v>
+        <v>661203</v>
       </c>
       <c r="AF37" s="10">
         <f t="shared" si="11"/>
-        <v>0.86033284755113726</v>
+        <v>0.86035887159735591</v>
       </c>
       <c r="AG37" s="5">
         <v>524373</v>
@@ -6919,14 +6919,14 @@
       </c>
       <c r="AI37" s="9">
         <f t="shared" si="12"/>
-        <v>282793</v>
+        <v>282804</v>
       </c>
       <c r="AJ37" s="8">
-        <v>431766</v>
+        <v>431777</v>
       </c>
       <c r="AK37" s="10">
         <f t="shared" si="13"/>
-        <v>0.82339479721495956</v>
+        <v>0.82341577464896176</v>
       </c>
       <c r="AL37" s="5">
         <v>516478</v>
@@ -6936,14 +6936,14 @@
       </c>
       <c r="AN37" s="9">
         <f t="shared" si="14"/>
-        <v>277981</v>
+        <v>277991</v>
       </c>
       <c r="AO37" s="8">
-        <v>437354</v>
+        <v>437364</v>
       </c>
       <c r="AP37" s="10">
         <f t="shared" si="15"/>
-        <v>0.84680083178760757</v>
+        <v>0.84682019369653694</v>
       </c>
       <c r="AQ37" s="22">
         <v>769503</v>
@@ -6953,14 +6953,14 @@
       </c>
       <c r="AS37" s="9">
         <f t="shared" si="16"/>
-        <v>145886</v>
+        <v>145902</v>
       </c>
       <c r="AT37" s="8">
-        <v>682693</v>
+        <v>682709</v>
       </c>
       <c r="AU37" s="10">
         <f t="shared" si="17"/>
-        <v>0.88718692454740267</v>
+        <v>0.8872077171888868</v>
       </c>
       <c r="AV37" s="22">
         <v>526610</v>
@@ -6970,14 +6970,14 @@
       </c>
       <c r="AX37" s="9">
         <f t="shared" si="18"/>
-        <v>255379</v>
+        <v>255392</v>
       </c>
       <c r="AY37" s="9">
-        <v>463234</v>
+        <v>463247</v>
       </c>
       <c r="AZ37" s="10">
         <f t="shared" si="19"/>
-        <v>0.87965287404340975</v>
+        <v>0.87967756024382371</v>
       </c>
       <c r="BA37" s="22">
         <v>525208</v>
@@ -6987,14 +6987,14 @@
       </c>
       <c r="BC37" s="9">
         <f t="shared" si="20"/>
-        <v>248154</v>
+        <v>248168</v>
       </c>
       <c r="BD37" s="8">
-        <v>471673</v>
+        <v>471687</v>
       </c>
       <c r="BE37" s="10">
         <f t="shared" si="21"/>
-        <v>0.89806895553761557</v>
+        <v>0.89809561164338703</v>
       </c>
       <c r="BF37" s="9">
         <v>765317</v>
@@ -7004,14 +7004,14 @@
       </c>
       <c r="BH37" s="9">
         <f t="shared" si="22"/>
-        <v>359903</v>
+        <v>359919</v>
       </c>
       <c r="BI37" s="6">
-        <v>707072</v>
+        <v>707088</v>
       </c>
       <c r="BJ37" s="10">
         <f t="shared" si="23"/>
-        <v>0.92389428171594257</v>
+        <v>0.92391518808546003</v>
       </c>
     </row>
     <row r="38" spans="1:63" x14ac:dyDescent="0.3">
@@ -7029,14 +7029,14 @@
       </c>
       <c r="E38" s="9">
         <f t="shared" si="0"/>
-        <v>4235</v>
+        <v>4236</v>
       </c>
       <c r="F38" s="8">
-        <v>12949</v>
+        <v>12950</v>
       </c>
       <c r="G38" s="10">
         <f t="shared" si="1"/>
-        <v>0.35998443190347779</v>
+        <v>0.36001223207583888</v>
       </c>
       <c r="H38" s="5">
         <v>32261</v>
@@ -7046,14 +7046,14 @@
       </c>
       <c r="J38" s="9">
         <f t="shared" si="2"/>
-        <v>4848</v>
+        <v>4849</v>
       </c>
       <c r="K38" s="8">
-        <v>12998</v>
+        <v>12999</v>
       </c>
       <c r="L38" s="10">
         <f t="shared" si="3"/>
-        <v>0.40290133597842598</v>
+        <v>0.40293233315768268</v>
       </c>
       <c r="M38" s="5">
         <v>35630</v>
@@ -7063,14 +7063,14 @@
       </c>
       <c r="O38" s="9">
         <f t="shared" si="4"/>
-        <v>15618</v>
+        <v>15619</v>
       </c>
       <c r="P38" s="8">
-        <v>29604</v>
+        <v>29605</v>
       </c>
       <c r="Q38" s="10">
         <f t="shared" si="5"/>
-        <v>0.83087285994948079</v>
+        <v>0.83090092618579847</v>
       </c>
       <c r="R38" s="5">
         <v>23074</v>
@@ -7080,14 +7080,14 @@
       </c>
       <c r="T38" s="9">
         <f t="shared" si="6"/>
-        <v>9006</v>
+        <v>9007</v>
       </c>
       <c r="U38" s="8">
-        <v>13124</v>
+        <v>13125</v>
       </c>
       <c r="V38" s="10">
         <f t="shared" si="7"/>
-        <v>0.56877871197018293</v>
+        <v>0.56882205079310044</v>
       </c>
       <c r="W38" s="5">
         <v>22269</v>
@@ -7097,14 +7097,14 @@
       </c>
       <c r="Y38" s="9">
         <f t="shared" si="8"/>
-        <v>8391</v>
+        <v>8392</v>
       </c>
       <c r="Z38" s="8">
-        <v>13146</v>
+        <v>13147</v>
       </c>
       <c r="AA38" s="10">
         <f t="shared" si="9"/>
-        <v>0.59032736090529436</v>
+        <v>0.59037226637927165</v>
       </c>
       <c r="AB38" s="5">
         <v>36289</v>
@@ -7114,14 +7114,14 @@
       </c>
       <c r="AD38" s="9">
         <f t="shared" si="10"/>
-        <v>11182</v>
+        <v>11183</v>
       </c>
       <c r="AE38" s="8">
-        <v>29884</v>
+        <v>29885</v>
       </c>
       <c r="AF38" s="10">
         <f t="shared" si="11"/>
-        <v>0.82350023423075869</v>
+        <v>0.82352779079059768</v>
       </c>
       <c r="AG38" s="5">
         <v>20568</v>
@@ -7131,14 +7131,14 @@
       </c>
       <c r="AI38" s="9">
         <f t="shared" si="12"/>
-        <v>7651</v>
+        <v>7652</v>
       </c>
       <c r="AJ38" s="8">
-        <v>13342</v>
+        <v>13343</v>
       </c>
       <c r="AK38" s="10">
         <f t="shared" si="13"/>
-        <v>0.6486775573706729</v>
+        <v>0.64872617658498644</v>
       </c>
       <c r="AL38" s="5">
         <v>20258</v>
@@ -7148,14 +7148,14 @@
       </c>
       <c r="AN38" s="9">
         <f t="shared" si="14"/>
-        <v>7387</v>
+        <v>7388</v>
       </c>
       <c r="AO38" s="8">
-        <v>13439</v>
+        <v>13440</v>
       </c>
       <c r="AP38" s="10">
         <f t="shared" si="15"/>
-        <v>0.6633922401026755</v>
+        <v>0.66344160331720803</v>
       </c>
       <c r="AQ38" s="22">
         <v>36918</v>
@@ -7165,14 +7165,14 @@
       </c>
       <c r="AS38" s="9">
         <f t="shared" si="16"/>
-        <v>8118</v>
+        <v>8120</v>
       </c>
       <c r="AT38" s="8">
-        <v>30639</v>
+        <v>30641</v>
       </c>
       <c r="AU38" s="10">
         <f t="shared" si="17"/>
-        <v>0.82992036405005687</v>
+        <v>0.82997453816566447</v>
       </c>
       <c r="AV38" s="22">
         <v>23527</v>
@@ -7182,14 +7182,14 @@
       </c>
       <c r="AX38" s="9">
         <f t="shared" si="18"/>
-        <v>10175</v>
+        <v>10178</v>
       </c>
       <c r="AY38" s="9">
-        <v>17569</v>
+        <v>17572</v>
       </c>
       <c r="AZ38" s="10">
         <f t="shared" si="19"/>
-        <v>0.74675904280188721</v>
+        <v>0.74688655587197683</v>
       </c>
       <c r="BA38" s="22">
         <v>22628</v>
@@ -7199,14 +7199,14 @@
       </c>
       <c r="BC38" s="9">
         <f t="shared" si="20"/>
-        <v>9746</v>
+        <v>9748</v>
       </c>
       <c r="BD38" s="8">
-        <v>17751</v>
+        <v>17753</v>
       </c>
       <c r="BE38" s="10">
         <f t="shared" si="21"/>
-        <v>0.78447056743857169</v>
+        <v>0.78455895350892702</v>
       </c>
       <c r="BF38" s="9">
         <v>35459</v>
@@ -7216,14 +7216,14 @@
       </c>
       <c r="BH38" s="9">
         <f t="shared" si="22"/>
-        <v>16719</v>
+        <v>16720</v>
       </c>
       <c r="BI38" s="6">
-        <v>31044</v>
+        <v>31045</v>
       </c>
       <c r="BJ38" s="10">
         <f t="shared" si="23"/>
-        <v>0.87549000253814269</v>
+        <v>0.87551820412307169</v>
       </c>
     </row>
     <row r="39" spans="1:63" x14ac:dyDescent="0.3">
@@ -7453,14 +7453,14 @@
       </c>
       <c r="E40" s="9">
         <f t="shared" si="0"/>
-        <v>58075</v>
+        <v>58084</v>
       </c>
       <c r="F40" s="8">
-        <v>173996</v>
+        <v>174005</v>
       </c>
       <c r="G40" s="10">
         <f t="shared" si="1"/>
-        <v>0.5736119261276349</v>
+        <v>0.57364159639209589</v>
       </c>
       <c r="H40" s="5">
         <v>287028</v>
@@ -7470,14 +7470,14 @@
       </c>
       <c r="J40" s="9">
         <f t="shared" si="2"/>
-        <v>72957</v>
+        <v>72964</v>
       </c>
       <c r="K40" s="8">
-        <v>174649</v>
+        <v>174656</v>
       </c>
       <c r="L40" s="10">
         <f t="shared" si="3"/>
-        <v>0.60847373775380798</v>
+        <v>0.60849812561840655</v>
       </c>
       <c r="M40" s="5">
         <v>303033</v>
@@ -7487,14 +7487,14 @@
       </c>
       <c r="O40" s="9">
         <f t="shared" si="4"/>
-        <v>166271</v>
+        <v>166278</v>
       </c>
       <c r="P40" s="8">
-        <v>273157</v>
+        <v>273164</v>
       </c>
       <c r="Q40" s="10">
         <f t="shared" si="5"/>
-        <v>0.90141007745031065</v>
+        <v>0.90143317724472249</v>
       </c>
       <c r="R40" s="5">
         <v>226941</v>
@@ -7504,14 +7504,14 @@
       </c>
       <c r="T40" s="9">
         <f t="shared" si="6"/>
-        <v>150767</v>
+        <v>150770</v>
       </c>
       <c r="U40" s="8">
-        <v>177629</v>
+        <v>177632</v>
       </c>
       <c r="V40" s="10">
         <f t="shared" si="7"/>
-        <v>0.78271004357960883</v>
+        <v>0.78272326287449157</v>
       </c>
       <c r="W40" s="5">
         <v>224663</v>
@@ -7521,14 +7521,14 @@
       </c>
       <c r="Y40" s="9">
         <f t="shared" si="8"/>
-        <v>132195</v>
+        <v>132198</v>
       </c>
       <c r="Z40" s="8">
-        <v>179920</v>
+        <v>179923</v>
       </c>
       <c r="AA40" s="10">
         <f t="shared" si="9"/>
-        <v>0.80084393068729609</v>
+        <v>0.8008572840209558</v>
       </c>
       <c r="AB40" s="5">
         <v>313197</v>
@@ -7538,14 +7538,14 @@
       </c>
       <c r="AD40" s="9">
         <f t="shared" si="10"/>
-        <v>87357</v>
+        <v>87364</v>
       </c>
       <c r="AE40" s="8">
-        <v>280643</v>
+        <v>280650</v>
       </c>
       <c r="AF40" s="10">
         <f t="shared" si="11"/>
-        <v>0.89605902993962272</v>
+        <v>0.89608138008984761</v>
       </c>
       <c r="AG40" s="5">
         <v>217708</v>
@@ -7555,14 +7555,14 @@
       </c>
       <c r="AI40" s="9">
         <f t="shared" si="12"/>
-        <v>92081</v>
+        <v>92085</v>
       </c>
       <c r="AJ40" s="8">
-        <v>184504</v>
+        <v>184508</v>
       </c>
       <c r="AK40" s="10">
         <f t="shared" si="13"/>
-        <v>0.84748378562110716</v>
+        <v>0.84750215885498004</v>
       </c>
       <c r="AL40" s="5">
         <v>217966</v>
@@ -7572,14 +7572,14 @@
       </c>
       <c r="AN40" s="9">
         <f t="shared" si="14"/>
-        <v>88616</v>
+        <v>88620</v>
       </c>
       <c r="AO40" s="8">
-        <v>187509</v>
+        <v>187513</v>
       </c>
       <c r="AP40" s="10">
         <f t="shared" si="15"/>
-        <v>0.86026719763632864</v>
+        <v>0.86028554912234023</v>
       </c>
       <c r="AQ40" s="22">
         <v>320883</v>
@@ -7589,14 +7589,14 @@
       </c>
       <c r="AS40" s="9">
         <f t="shared" si="16"/>
-        <v>54254</v>
+        <v>54259</v>
       </c>
       <c r="AT40" s="8">
-        <v>291066</v>
+        <v>291071</v>
       </c>
       <c r="AU40" s="10">
         <f t="shared" si="17"/>
-        <v>0.90707828086872788</v>
+        <v>0.90709386287213722</v>
       </c>
       <c r="AV40" s="22">
         <v>237287</v>
@@ -7606,14 +7606,14 @@
       </c>
       <c r="AX40" s="9">
         <f t="shared" si="18"/>
-        <v>104130</v>
+        <v>104137</v>
       </c>
       <c r="AY40" s="9">
-        <v>212760</v>
+        <v>212767</v>
       </c>
       <c r="AZ40" s="10">
         <f t="shared" si="19"/>
-        <v>0.89663571961380106</v>
+        <v>0.89666521975498026</v>
       </c>
       <c r="BA40" s="22">
         <v>231690</v>
@@ -7623,14 +7623,14 @@
       </c>
       <c r="BC40" s="9">
         <f t="shared" si="20"/>
-        <v>100489</v>
+        <v>100492</v>
       </c>
       <c r="BD40" s="8">
-        <v>215371</v>
+        <v>215374</v>
       </c>
       <c r="BE40" s="10">
         <f t="shared" si="21"/>
-        <v>0.92956536751694074</v>
+        <v>0.9295783158530796</v>
       </c>
       <c r="BF40" s="9">
         <v>314391</v>
@@ -7640,14 +7640,14 @@
       </c>
       <c r="BH40" s="9">
         <f t="shared" si="22"/>
-        <v>147474</v>
+        <v>147479</v>
       </c>
       <c r="BI40" s="6">
-        <v>298962</v>
+        <v>298967</v>
       </c>
       <c r="BJ40" s="10">
         <f t="shared" si="23"/>
-        <v>0.95092416767655563</v>
+        <v>0.95094007143970405</v>
       </c>
     </row>
     <row r="41" spans="1:63" x14ac:dyDescent="0.3">
@@ -7665,14 +7665,14 @@
       </c>
       <c r="E41" s="9">
         <f t="shared" si="0"/>
-        <v>174686</v>
+        <v>174727</v>
       </c>
       <c r="F41" s="8">
-        <v>589377</v>
+        <v>589418</v>
       </c>
       <c r="G41" s="10">
         <f t="shared" si="1"/>
-        <v>0.6734590338330958</v>
+        <v>0.67350588299820946</v>
       </c>
       <c r="H41" s="5">
         <v>834053</v>
@@ -7682,14 +7682,14 @@
       </c>
       <c r="J41" s="9">
         <f t="shared" si="2"/>
-        <v>211993</v>
+        <v>212026</v>
       </c>
       <c r="K41" s="8">
-        <v>593074</v>
+        <v>593107</v>
       </c>
       <c r="L41" s="10">
         <f t="shared" si="3"/>
-        <v>0.71107471587537008</v>
+        <v>0.71111428170631841</v>
       </c>
       <c r="M41" s="5">
         <v>879453</v>
@@ -7699,14 +7699,14 @@
       </c>
       <c r="O41" s="9">
         <f t="shared" si="4"/>
-        <v>392288</v>
+        <v>392345</v>
       </c>
       <c r="P41" s="8">
-        <v>788372</v>
+        <v>788429</v>
       </c>
       <c r="Q41" s="10">
         <f t="shared" si="5"/>
-        <v>0.8964344882557681</v>
+        <v>0.89649930127022137</v>
       </c>
       <c r="R41" s="5">
         <v>738453</v>
@@ -7716,14 +7716,14 @@
       </c>
       <c r="T41" s="9">
         <f t="shared" si="6"/>
-        <v>486226</v>
+        <v>486265</v>
       </c>
       <c r="U41" s="8">
-        <v>605594</v>
+        <v>605633</v>
       </c>
       <c r="V41" s="10">
         <f t="shared" si="7"/>
-        <v>0.82008469056256794</v>
+        <v>0.82013750367321958</v>
       </c>
       <c r="W41" s="5">
         <v>740008</v>
@@ -7733,14 +7733,14 @@
       </c>
       <c r="Y41" s="9">
         <f t="shared" si="8"/>
-        <v>428108</v>
+        <v>428149</v>
       </c>
       <c r="Z41" s="8">
-        <v>611225</v>
+        <v>611266</v>
       </c>
       <c r="AA41" s="10">
         <f t="shared" si="9"/>
-        <v>0.82597080031567227</v>
+        <v>0.82602620512210678</v>
       </c>
       <c r="AB41" s="5">
         <v>928683</v>
@@ -7750,14 +7750,14 @@
       </c>
       <c r="AD41" s="9">
         <f t="shared" si="10"/>
-        <v>220607</v>
+        <v>220678</v>
       </c>
       <c r="AE41" s="8">
-        <v>813125</v>
+        <v>813196</v>
       </c>
       <c r="AF41" s="10">
         <f t="shared" si="11"/>
-        <v>0.87556787407543801</v>
+        <v>0.87564432642785539</v>
       </c>
       <c r="AG41" s="5">
         <v>734303</v>
@@ -7767,14 +7767,14 @@
       </c>
       <c r="AI41" s="9">
         <f t="shared" si="12"/>
-        <v>376509</v>
+        <v>376553</v>
       </c>
       <c r="AJ41" s="8">
-        <v>623668</v>
+        <v>623712</v>
       </c>
       <c r="AK41" s="10">
         <f t="shared" si="13"/>
-        <v>0.84933331335974382</v>
+        <v>0.84939323412814605</v>
       </c>
       <c r="AL41" s="5">
         <v>728636</v>
@@ -7784,14 +7784,14 @@
       </c>
       <c r="AN41" s="9">
         <f t="shared" si="14"/>
-        <v>357909</v>
+        <v>357945</v>
       </c>
       <c r="AO41" s="8">
-        <v>631330</v>
+        <v>631366</v>
       </c>
       <c r="AP41" s="10">
         <f t="shared" si="15"/>
-        <v>0.86645458088812521</v>
+        <v>0.86650398827398045</v>
       </c>
       <c r="AQ41" s="22">
         <v>923873</v>
@@ -7801,14 +7801,14 @@
       </c>
       <c r="AS41" s="9">
         <f t="shared" si="16"/>
-        <v>140457</v>
+        <v>140512</v>
       </c>
       <c r="AT41" s="8">
-        <v>842064</v>
+        <v>842119</v>
       </c>
       <c r="AU41" s="10">
         <f t="shared" si="17"/>
-        <v>0.91144995037196674</v>
+        <v>0.91150948236391793</v>
       </c>
       <c r="AV41" s="22">
         <v>726271</v>
@@ -7818,14 +7818,14 @@
       </c>
       <c r="AX41" s="9">
         <f t="shared" si="18"/>
-        <v>325919</v>
+        <v>325958</v>
       </c>
       <c r="AY41" s="9">
-        <v>662916</v>
+        <v>662955</v>
       </c>
       <c r="AZ41" s="10">
         <f t="shared" si="19"/>
-        <v>0.9127667220638026</v>
+        <v>0.91282042102741268</v>
       </c>
       <c r="BA41" s="22">
         <v>715104</v>
@@ -7835,14 +7835,14 @@
       </c>
       <c r="BC41" s="9">
         <f t="shared" si="20"/>
-        <v>312267</v>
+        <v>312305</v>
       </c>
       <c r="BD41" s="8">
-        <v>671025</v>
+        <v>671063</v>
       </c>
       <c r="BE41" s="10">
         <f t="shared" si="21"/>
-        <v>0.93836001476708286</v>
+        <v>0.93841315389090263</v>
       </c>
       <c r="BF41" s="9">
         <v>910875</v>
@@ -7852,14 +7852,14 @@
       </c>
       <c r="BH41" s="9">
         <f t="shared" si="22"/>
-        <v>397935</v>
+        <v>397977</v>
       </c>
       <c r="BI41" s="6">
-        <v>867146</v>
+        <v>867188</v>
       </c>
       <c r="BJ41" s="10">
         <f t="shared" si="23"/>
-        <v>0.95199231508165227</v>
+        <v>0.95203842459173871</v>
       </c>
     </row>
     <row r="42" spans="1:63" x14ac:dyDescent="0.3">
@@ -7877,14 +7877,14 @@
       </c>
       <c r="E42" s="9">
         <f t="shared" si="0"/>
-        <v>3409</v>
+        <v>3410</v>
       </c>
       <c r="F42" s="8">
-        <v>12435</v>
+        <v>12436</v>
       </c>
       <c r="G42" s="10">
         <f t="shared" si="1"/>
-        <v>0.63311440354360771</v>
+        <v>0.63316531744819515</v>
       </c>
       <c r="H42" s="5">
         <v>18257</v>
@@ -7894,14 +7894,14 @@
       </c>
       <c r="J42" s="9">
         <f t="shared" si="2"/>
-        <v>4249</v>
+        <v>4250</v>
       </c>
       <c r="K42" s="8">
-        <v>12413</v>
+        <v>12414</v>
       </c>
       <c r="L42" s="10">
         <f t="shared" si="3"/>
-        <v>0.67990359861970751</v>
+        <v>0.67995837213123733</v>
       </c>
       <c r="M42" s="5">
         <v>19399</v>
@@ -7911,14 +7911,14 @@
       </c>
       <c r="O42" s="9">
         <f t="shared" si="4"/>
-        <v>8205</v>
+        <v>8206</v>
       </c>
       <c r="P42" s="8">
-        <v>17005</v>
+        <v>17006</v>
       </c>
       <c r="Q42" s="10">
         <f t="shared" si="5"/>
-        <v>0.87659157688540645</v>
+        <v>0.87664312593432647</v>
       </c>
       <c r="R42" s="5">
         <v>15746</v>
@@ -7928,14 +7928,14 @@
       </c>
       <c r="T42" s="9">
         <f t="shared" si="6"/>
-        <v>9614</v>
+        <v>9615</v>
       </c>
       <c r="U42" s="8">
-        <v>12678</v>
+        <v>12679</v>
       </c>
       <c r="V42" s="10">
         <f t="shared" si="7"/>
-        <v>0.80515686523561536</v>
+        <v>0.80522037342817221</v>
       </c>
       <c r="W42" s="5">
         <v>15724</v>
@@ -7945,14 +7945,14 @@
       </c>
       <c r="Y42" s="9">
         <f t="shared" si="8"/>
-        <v>8909</v>
+        <v>8910</v>
       </c>
       <c r="Z42" s="8">
-        <v>12785</v>
+        <v>12786</v>
       </c>
       <c r="AA42" s="10">
         <f t="shared" si="9"/>
-        <v>0.81308827270414652</v>
+        <v>0.81315186975324349</v>
       </c>
       <c r="AB42" s="5">
         <v>20172</v>
@@ -8064,14 +8064,14 @@
       </c>
       <c r="BH42" s="9">
         <f t="shared" si="22"/>
-        <v>8845</v>
+        <v>8846</v>
       </c>
       <c r="BI42" s="6">
-        <v>18138</v>
+        <v>18139</v>
       </c>
       <c r="BJ42" s="10">
         <f t="shared" si="23"/>
-        <v>0.9196369720630736</v>
+        <v>0.9196876742889013</v>
       </c>
     </row>
     <row r="43" spans="1:63" x14ac:dyDescent="0.3">
@@ -8301,14 +8301,14 @@
       </c>
       <c r="E44" s="9">
         <f t="shared" si="0"/>
-        <v>61743</v>
+        <v>61746</v>
       </c>
       <c r="F44" s="8">
-        <v>191697</v>
+        <v>191700</v>
       </c>
       <c r="G44" s="10">
         <f t="shared" si="1"/>
-        <v>0.53711382956665976</v>
+        <v>0.53712223523544278</v>
       </c>
       <c r="H44" s="5">
         <v>334097</v>
@@ -8318,14 +8318,14 @@
       </c>
       <c r="J44" s="9">
         <f t="shared" si="2"/>
-        <v>70944</v>
+        <v>70948</v>
       </c>
       <c r="K44" s="8">
-        <v>192795</v>
+        <v>192799</v>
       </c>
       <c r="L44" s="10">
         <f t="shared" si="3"/>
-        <v>0.57706294878433506</v>
+        <v>0.57707492135517524</v>
       </c>
       <c r="M44" s="5">
         <v>358237</v>
@@ -8335,14 +8335,14 @@
       </c>
       <c r="O44" s="9">
         <f t="shared" si="4"/>
-        <v>149466</v>
+        <v>149476</v>
       </c>
       <c r="P44" s="8">
-        <v>285563</v>
+        <v>285573</v>
       </c>
       <c r="Q44" s="10">
         <f t="shared" si="5"/>
-        <v>0.79713429936047919</v>
+        <v>0.79716221384167463</v>
       </c>
       <c r="R44" s="5">
         <v>284869</v>
@@ -8352,14 +8352,14 @@
       </c>
       <c r="T44" s="9">
         <f t="shared" si="6"/>
-        <v>159506</v>
+        <v>159514</v>
       </c>
       <c r="U44" s="8">
-        <v>196730</v>
+        <v>196738</v>
       </c>
       <c r="V44" s="10">
         <f t="shared" si="7"/>
-        <v>0.69059813458115837</v>
+        <v>0.69062621766496179</v>
       </c>
       <c r="W44" s="5">
         <v>281986</v>
@@ -8369,14 +8369,14 @@
       </c>
       <c r="Y44" s="9">
         <f t="shared" si="8"/>
-        <v>150391</v>
+        <v>150399</v>
       </c>
       <c r="Z44" s="8">
-        <v>198483</v>
+        <v>198491</v>
       </c>
       <c r="AA44" s="10">
         <f t="shared" si="9"/>
-        <v>0.70387536969920494</v>
+        <v>0.70390373990198096</v>
       </c>
       <c r="AB44" s="5">
         <v>371659</v>
@@ -8386,14 +8386,14 @@
       </c>
       <c r="AD44" s="9">
         <f t="shared" si="10"/>
-        <v>117171</v>
+        <v>117182</v>
       </c>
       <c r="AE44" s="8">
-        <v>293338</v>
+        <v>293349</v>
       </c>
       <c r="AF44" s="10">
         <f t="shared" si="11"/>
-        <v>0.7892665050489831</v>
+        <v>0.78929610207206069</v>
       </c>
       <c r="AG44" s="5">
         <v>277254</v>
@@ -8403,14 +8403,14 @@
       </c>
       <c r="AI44" s="9">
         <f t="shared" si="12"/>
-        <v>144598</v>
+        <v>144604</v>
       </c>
       <c r="AJ44" s="8">
-        <v>202637</v>
+        <v>202643</v>
       </c>
       <c r="AK44" s="10">
         <f t="shared" si="13"/>
-        <v>0.7308713309816991</v>
+        <v>0.73089297178760271</v>
       </c>
       <c r="AL44" s="5">
         <v>276584</v>
@@ -8420,14 +8420,14 @@
       </c>
       <c r="AN44" s="9">
         <f t="shared" si="14"/>
-        <v>143867</v>
+        <v>143872</v>
       </c>
       <c r="AO44" s="8">
-        <v>205759</v>
+        <v>205764</v>
       </c>
       <c r="AP44" s="10">
         <f t="shared" si="15"/>
-        <v>0.74392951146848696</v>
+        <v>0.74394758915917047</v>
       </c>
       <c r="AQ44" s="22">
         <v>381213</v>
@@ -8437,14 +8437,14 @@
       </c>
       <c r="AS44" s="9">
         <f t="shared" si="16"/>
-        <v>79468</v>
+        <v>79475</v>
       </c>
       <c r="AT44" s="8">
-        <v>306653</v>
+        <v>306660</v>
       </c>
       <c r="AU44" s="10">
         <f t="shared" si="17"/>
-        <v>0.80441380540537699</v>
+        <v>0.80443216784317428</v>
       </c>
       <c r="AV44" s="22">
         <v>286200</v>
@@ -8454,14 +8454,14 @@
       </c>
       <c r="AX44" s="9">
         <f t="shared" si="18"/>
-        <v>140919</v>
+        <v>140924</v>
       </c>
       <c r="AY44" s="9">
-        <v>225295</v>
+        <v>225300</v>
       </c>
       <c r="AZ44" s="10">
         <f t="shared" si="19"/>
-        <v>0.78719426974143958</v>
+        <v>0.78721174004192873</v>
       </c>
       <c r="BA44" s="22">
         <v>282748</v>
@@ -8471,14 +8471,14 @@
       </c>
       <c r="BC44" s="9">
         <f t="shared" si="20"/>
-        <v>139538</v>
+        <v>139542</v>
       </c>
       <c r="BD44" s="8">
-        <v>229337</v>
+        <v>229341</v>
       </c>
       <c r="BE44" s="10">
         <f t="shared" si="21"/>
-        <v>0.81110034376900986</v>
+        <v>0.8111144906418436</v>
       </c>
       <c r="BF44" s="9">
         <v>372165</v>
@@ -8488,14 +8488,14 @@
       </c>
       <c r="BH44" s="9">
         <f t="shared" si="22"/>
-        <v>189926</v>
+        <v>189929</v>
       </c>
       <c r="BI44" s="6">
-        <v>317814</v>
+        <v>317817</v>
       </c>
       <c r="BJ44" s="10">
         <f t="shared" si="23"/>
-        <v>0.85395993712466245</v>
+        <v>0.85396799806537427</v>
       </c>
     </row>
     <row r="45" spans="1:63" x14ac:dyDescent="0.3">
@@ -8513,14 +8513,14 @@
       </c>
       <c r="E45" s="9">
         <f t="shared" si="0"/>
-        <v>49626</v>
+        <v>49629</v>
       </c>
       <c r="F45" s="8">
-        <v>167507</v>
+        <v>167510</v>
       </c>
       <c r="G45" s="10">
         <f t="shared" si="1"/>
-        <v>0.5934493020619287</v>
+        <v>0.59345993056047619</v>
       </c>
       <c r="H45" s="5">
         <v>264867</v>
@@ -8530,14 +8530,14 @@
       </c>
       <c r="J45" s="9">
         <f t="shared" si="2"/>
-        <v>59039</v>
+        <v>59042</v>
       </c>
       <c r="K45" s="8">
-        <v>167749</v>
+        <v>167752</v>
       </c>
       <c r="L45" s="10">
         <f t="shared" si="3"/>
-        <v>0.63333295578535642</v>
+        <v>0.63334428222466366</v>
       </c>
       <c r="M45" s="5">
         <v>281786</v>
@@ -8547,14 +8547,14 @@
       </c>
       <c r="O45" s="9">
         <f t="shared" si="4"/>
-        <v>129920</v>
+        <v>129923</v>
       </c>
       <c r="P45" s="8">
-        <v>241333</v>
+        <v>241336</v>
       </c>
       <c r="Q45" s="10">
         <f t="shared" si="5"/>
-        <v>0.85644070322869126</v>
+        <v>0.85645134960572922</v>
       </c>
       <c r="R45" s="5">
         <v>221339</v>
@@ -8564,14 +8564,14 @@
       </c>
       <c r="T45" s="9">
         <f t="shared" si="6"/>
-        <v>140341</v>
+        <v>140345</v>
       </c>
       <c r="U45" s="8">
-        <v>170632</v>
+        <v>170636</v>
       </c>
       <c r="V45" s="10">
         <f t="shared" si="7"/>
-        <v>0.77090797374163611</v>
+        <v>0.77092604556811051</v>
       </c>
       <c r="W45" s="5">
         <v>220187</v>
@@ -8581,14 +8581,14 @@
       </c>
       <c r="Y45" s="9">
         <f t="shared" si="8"/>
-        <v>128831</v>
+        <v>128836</v>
       </c>
       <c r="Z45" s="8">
-        <v>171548</v>
+        <v>171553</v>
       </c>
       <c r="AA45" s="10">
         <f t="shared" si="9"/>
-        <v>0.77910140017348894</v>
+        <v>0.77912410814444089</v>
       </c>
       <c r="AB45" s="5">
         <v>291802</v>
@@ -8598,14 +8598,14 @@
       </c>
       <c r="AD45" s="9">
         <f t="shared" si="10"/>
-        <v>84794</v>
+        <v>84797</v>
       </c>
       <c r="AE45" s="8">
-        <v>245742</v>
+        <v>245745</v>
       </c>
       <c r="AF45" s="10">
         <f t="shared" si="11"/>
-        <v>0.84215324089622412</v>
+        <v>0.84216352184015186</v>
       </c>
       <c r="AG45" s="5">
         <v>216277</v>
@@ -8615,14 +8615,14 @@
       </c>
       <c r="AI45" s="9">
         <f t="shared" si="12"/>
-        <v>119861</v>
+        <v>119864</v>
       </c>
       <c r="AJ45" s="8">
-        <v>174763</v>
+        <v>174766</v>
       </c>
       <c r="AK45" s="10">
         <f t="shared" si="13"/>
-        <v>0.80805171146261512</v>
+        <v>0.8080655825631019</v>
       </c>
       <c r="AL45" s="5">
         <v>214950</v>
@@ -8632,14 +8632,14 @@
       </c>
       <c r="AN45" s="9">
         <f t="shared" si="14"/>
-        <v>115739</v>
+        <v>115741</v>
       </c>
       <c r="AO45" s="8">
-        <v>176813</v>
+        <v>176815</v>
       </c>
       <c r="AP45" s="10">
         <f t="shared" si="15"/>
-        <v>0.82257734356827172</v>
+        <v>0.82258664805768789</v>
       </c>
       <c r="AQ45" s="22">
         <v>297340</v>
@@ -8649,14 +8649,14 @@
       </c>
       <c r="AS45" s="9">
         <f t="shared" si="16"/>
-        <v>52917</v>
+        <v>52919</v>
       </c>
       <c r="AT45" s="8">
-        <v>255703</v>
+        <v>255705</v>
       </c>
       <c r="AU45" s="10">
         <f t="shared" si="17"/>
-        <v>0.85996838635905026</v>
+        <v>0.85997511266563531</v>
       </c>
       <c r="AV45" s="22">
         <v>215263</v>
@@ -8666,14 +8666,14 @@
       </c>
       <c r="AX45" s="9">
         <f t="shared" si="18"/>
-        <v>99765</v>
+        <v>99766</v>
       </c>
       <c r="AY45" s="9">
-        <v>182756</v>
+        <v>182757</v>
       </c>
       <c r="AZ45" s="10">
         <f t="shared" si="19"/>
-        <v>0.8489893757868282</v>
+        <v>0.84899402126700829</v>
       </c>
       <c r="BA45" s="22">
         <v>211125</v>
@@ -8683,14 +8683,14 @@
       </c>
       <c r="BC45" s="9">
         <f t="shared" si="20"/>
-        <v>101665</v>
+        <v>101667</v>
       </c>
       <c r="BD45" s="8">
-        <v>185318</v>
+        <v>185320</v>
       </c>
       <c r="BE45" s="10">
         <f t="shared" si="21"/>
-        <v>0.87776435760805205</v>
+        <v>0.87777383066903492</v>
       </c>
       <c r="BF45" s="9">
         <v>290704</v>
@@ -8700,14 +8700,14 @@
       </c>
       <c r="BH45" s="9">
         <f t="shared" si="22"/>
-        <v>145213</v>
+        <v>145216</v>
       </c>
       <c r="BI45" s="6">
-        <v>262767</v>
+        <v>262770</v>
       </c>
       <c r="BJ45" s="10">
         <f t="shared" si="23"/>
-        <v>0.9038988111618691</v>
+        <v>0.90390913093731085</v>
       </c>
     </row>
     <row r="46" spans="1:63" x14ac:dyDescent="0.3">
@@ -8759,14 +8759,14 @@
       </c>
       <c r="O46" s="9">
         <f t="shared" si="4"/>
-        <v>1779</v>
+        <v>1780</v>
       </c>
       <c r="P46" s="8">
-        <v>2733</v>
+        <v>2734</v>
       </c>
       <c r="Q46" s="10">
         <f t="shared" si="5"/>
-        <v>0.87934362934362931</v>
+        <v>0.87966537966537972</v>
       </c>
       <c r="R46" s="5">
         <v>1509</v>
@@ -8810,14 +8810,14 @@
       </c>
       <c r="AD46" s="9">
         <f t="shared" si="10"/>
-        <v>1889</v>
+        <v>1891</v>
       </c>
       <c r="AE46" s="8">
-        <v>3069</v>
+        <v>3071</v>
       </c>
       <c r="AF46" s="10">
         <f t="shared" si="11"/>
-        <v>0.87237066515065376</v>
+        <v>0.87293916998294485</v>
       </c>
       <c r="AG46" s="5">
         <v>1259</v>
@@ -8861,14 +8861,14 @@
       </c>
       <c r="AS46" s="9">
         <f t="shared" si="16"/>
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="AT46" s="8">
-        <v>3302</v>
+        <v>3303</v>
       </c>
       <c r="AU46" s="10">
         <f t="shared" si="17"/>
-        <v>0.85944820406038525</v>
+        <v>0.85970848516397713</v>
       </c>
       <c r="AV46" s="22">
         <v>1986</v>
@@ -9135,10 +9135,10 @@
       </c>
     </row>
     <row r="48" spans="1:63" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="39" t="s">
+      <c r="A48" s="31" t="s">
         <v>41</v>
       </c>
-      <c r="B48" s="39"/>
+      <c r="B48" s="31"/>
       <c r="C48" s="20">
         <f>SUM(C10:C47)</f>
         <v>10396914</v>
@@ -9149,15 +9149,15 @@
       </c>
       <c r="E48" s="18">
         <f t="shared" si="0"/>
-        <v>1253579</v>
+        <v>1253701</v>
       </c>
       <c r="F48" s="20">
         <f>SUM(F10:F47)</f>
-        <v>3917736</v>
+        <v>3917858</v>
       </c>
       <c r="G48" s="19">
         <f t="shared" si="1"/>
-        <v>0.37681719787236867</v>
+        <v>0.37682893212351282</v>
       </c>
       <c r="H48" s="20">
         <f>SUM(H10:H47)</f>
@@ -9169,15 +9169,15 @@
       </c>
       <c r="J48" s="18">
         <f t="shared" si="2"/>
-        <v>1452418</v>
+        <v>1452529</v>
       </c>
       <c r="K48" s="20">
         <f>SUM(K10:K47)</f>
-        <v>3929194</v>
+        <v>3929305</v>
       </c>
       <c r="L48" s="19">
         <f t="shared" si="3"/>
-        <v>0.40920429888039356</v>
+        <v>0.40921585892990392</v>
       </c>
       <c r="M48" s="20">
         <f>SUM(M10:M47)</f>
@@ -9189,15 +9189,15 @@
       </c>
       <c r="O48" s="18">
         <f t="shared" si="4"/>
-        <v>5093821</v>
+        <v>5094041</v>
       </c>
       <c r="P48" s="20">
         <f>SUM(P10:P47)</f>
-        <v>9212140</v>
+        <v>9212360</v>
       </c>
       <c r="Q48" s="19">
         <f t="shared" si="5"/>
-        <v>0.8859446327641235</v>
+        <v>0.88596579047766322</v>
       </c>
       <c r="R48" s="20">
         <f>SUM(R10:R47)</f>
@@ -9209,15 +9209,15 @@
       </c>
       <c r="T48" s="18">
         <f t="shared" si="6"/>
-        <v>3084835</v>
+        <v>3084951</v>
       </c>
       <c r="U48" s="20">
         <f>SUM(U10:U47)</f>
-        <v>4004604</v>
+        <v>4004720</v>
       </c>
       <c r="V48" s="19">
         <f t="shared" si="7"/>
-        <v>0.66607022122204784</v>
+        <v>0.6660895150512659</v>
       </c>
       <c r="W48" s="20">
         <f>SUM(W10:W47)</f>
@@ -9229,15 +9229,15 @@
       </c>
       <c r="Y48" s="18">
         <f t="shared" si="8"/>
-        <v>2823211</v>
+        <v>2823338</v>
       </c>
       <c r="Z48" s="20">
         <f>SUM(Z10:Z47)</f>
-        <v>4036868</v>
+        <v>4036995</v>
       </c>
       <c r="AA48" s="19">
         <f t="shared" si="9"/>
-        <v>0.69474034929871442</v>
+        <v>0.69476220585294424</v>
       </c>
       <c r="AB48" s="20">
         <f>SUM(AB10:AB47)</f>
@@ -9249,15 +9249,15 @@
       </c>
       <c r="AD48" s="18">
         <f t="shared" si="10"/>
-        <v>3617897</v>
+        <v>3618164</v>
       </c>
       <c r="AE48" s="20">
         <f>SUM(AE10:AE47)</f>
-        <v>9488919</v>
+        <v>9489186</v>
       </c>
       <c r="AF48" s="19">
         <f t="shared" si="11"/>
-        <v>0.87447366631259815</v>
+        <v>0.87449827232608668</v>
       </c>
       <c r="AG48" s="20">
         <f>SUM(AG10:AG47)</f>
@@ -9269,15 +9269,15 @@
       </c>
       <c r="AI48" s="18">
         <f t="shared" si="12"/>
-        <v>2579975</v>
+        <v>2580094</v>
       </c>
       <c r="AJ48" s="20">
         <f>SUM(AJ10:AJ47)</f>
-        <v>4110207</v>
+        <v>4110326</v>
       </c>
       <c r="AK48" s="19">
         <f t="shared" si="13"/>
-        <v>0.75235882816587085</v>
+        <v>0.75238061069423301</v>
       </c>
       <c r="AL48" s="20">
         <f>SUM(AL10:AL47)</f>
@@ -9289,15 +9289,15 @@
       </c>
       <c r="AN48" s="18">
         <f t="shared" si="14"/>
-        <v>2523093</v>
+        <v>2523215</v>
       </c>
       <c r="AO48" s="20">
         <f>SUM(AO10:AO47)</f>
-        <v>4158963</v>
+        <v>4159085</v>
       </c>
       <c r="AP48" s="19">
         <f t="shared" si="15"/>
-        <v>0.77762859125877104</v>
+        <v>0.777651402398984</v>
       </c>
       <c r="AQ48" s="20">
         <f>SUM(AQ10:AQ47)</f>
@@ -9309,15 +9309,15 @@
       </c>
       <c r="AS48" s="18">
         <f t="shared" si="16"/>
-        <v>2270345</v>
+        <v>2270583</v>
       </c>
       <c r="AT48" s="20">
         <f>SUM(AT10:AT47)</f>
-        <v>9815417</v>
+        <v>9815655</v>
       </c>
       <c r="AU48" s="19">
         <f t="shared" si="17"/>
-        <v>0.89359302358821491</v>
+        <v>0.89361469104662383</v>
       </c>
       <c r="AV48" s="20">
         <f>SUM(AV10:AV47)</f>
@@ -9329,15 +9329,15 @@
       </c>
       <c r="AX48" s="18">
         <f t="shared" si="18"/>
-        <v>2882025</v>
+        <v>2882198</v>
       </c>
       <c r="AY48" s="20">
         <f>SUM(AY10:AY47)</f>
-        <v>5362298</v>
+        <v>5362471</v>
       </c>
       <c r="AZ48" s="19">
         <f t="shared" si="19"/>
-        <v>0.85626200608388092</v>
+        <v>0.8562896310549386</v>
       </c>
       <c r="BA48" s="20">
         <f>SUM(BA10:BA47)</f>
@@ -9349,15 +9349,15 @@
       </c>
       <c r="BC48" s="18">
         <f t="shared" si="20"/>
-        <v>2727943</v>
+        <v>2728123</v>
       </c>
       <c r="BD48" s="20">
         <f>SUM(BD10:BD47)</f>
-        <v>5477287</v>
+        <v>5477467</v>
       </c>
       <c r="BE48" s="19">
         <f t="shared" si="21"/>
-        <v>0.89254701188408803</v>
+        <v>0.89257634364306637</v>
       </c>
       <c r="BF48" s="20">
         <f>SUM(BF10:BF47)</f>
@@ -9369,15 +9369,15 @@
       </c>
       <c r="BH48" s="18">
         <f t="shared" si="22"/>
-        <v>4902200</v>
+        <v>4902422</v>
       </c>
       <c r="BI48" s="20">
         <f>SUM(BI10:BI47)</f>
-        <v>10081521</v>
+        <v>10081743</v>
       </c>
       <c r="BJ48" s="19">
         <f t="shared" si="23"/>
-        <v>0.93524220742119613</v>
+        <v>0.93526280190986977</v>
       </c>
       <c r="BK48"/>
     </row>
@@ -9392,22 +9392,17 @@
     <row r="57" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="58" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="40" t="s">
+      <c r="A59" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="B59" s="40"/>
-      <c r="C59" s="40"/>
-      <c r="D59" s="40"/>
-      <c r="E59" s="40"/>
+      <c r="B59" s="32"/>
+      <c r="C59" s="32"/>
+      <c r="D59" s="32"/>
+      <c r="E59" s="32"/>
       <c r="F59" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="A59:E59"/>
-    <mergeCell ref="M8:Q8"/>
-    <mergeCell ref="R8:V8"/>
-    <mergeCell ref="W8:AA8"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="BF8:BJ8"/>
     <mergeCell ref="A3:B3"/>
@@ -9422,6 +9417,11 @@
     <mergeCell ref="AB8:AF8"/>
     <mergeCell ref="AG8:AK8"/>
     <mergeCell ref="AL8:AP8"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="M8:Q8"/>
+    <mergeCell ref="R8:V8"/>
+    <mergeCell ref="W8:AA8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/gstdatabase/GSTR-1-2020-2021.xlsx
+++ b/gstdatabase/GSTR-1-2020-2021.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\May-26\GST Statistics Downloads 31st May 26\Downloads\GSTR 1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Jun-26\GST Statistics Downloads 31st May 26\Downloads\GSTR 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BA68264-70BB-4A83-9B15-3B879753E0DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BDB9475-65A5-450F-9287-46556B71A78B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -182,10 +182,10 @@
     <t>Andaman and Nicobar Islands</t>
   </si>
   <si>
-    <t>Data Considered upto 31st May 2026</t>
+    <t>Data Considered upto 30th Jun 2026</t>
   </si>
   <si>
-    <t>Filing %age as on 31st May 2026</t>
+    <t>Filing %age as on 30th Jun 2026</t>
   </si>
 </sst>
 </file>
@@ -1144,14 +1144,14 @@
       </c>
       <c r="O10" s="9">
         <f>P10-N10</f>
-        <v>53275</v>
+        <v>53276</v>
       </c>
       <c r="P10" s="8">
-        <v>73135</v>
+        <v>73136</v>
       </c>
       <c r="Q10" s="10">
         <f>P10/M10</f>
-        <v>0.87236834257768237</v>
+        <v>0.87238027076996483</v>
       </c>
       <c r="R10" s="5">
         <v>48665</v>
@@ -1356,14 +1356,14 @@
       </c>
       <c r="O11" s="9">
         <f t="shared" ref="O11:O48" si="4">P11-N11</f>
-        <v>40631</v>
+        <v>40632</v>
       </c>
       <c r="P11" s="8">
-        <v>78756</v>
+        <v>78757</v>
       </c>
       <c r="Q11" s="10">
         <f t="shared" ref="Q11:Q48" si="5">P11/M11</f>
-        <v>0.92322841568489533</v>
+        <v>0.92324013832717899</v>
       </c>
       <c r="R11" s="5">
         <v>34872</v>
@@ -1407,14 +1407,14 @@
       </c>
       <c r="AD11" s="9">
         <f t="shared" ref="AD11:AD48" si="10">AE11-AC11</f>
-        <v>27333</v>
+        <v>27334</v>
       </c>
       <c r="AE11" s="8">
-        <v>81752</v>
+        <v>81753</v>
       </c>
       <c r="AF11" s="10">
         <f t="shared" ref="AF11:AF48" si="11">AE11/AB11</f>
-        <v>0.91465652271201614</v>
+        <v>0.91466771089729249</v>
       </c>
       <c r="AG11" s="5">
         <v>29840</v>
@@ -1424,14 +1424,14 @@
       </c>
       <c r="AI11" s="9">
         <f t="shared" ref="AI11:AI48" si="12">AJ11-AH11</f>
-        <v>12812</v>
+        <v>12813</v>
       </c>
       <c r="AJ11" s="8">
-        <v>21564</v>
+        <v>21565</v>
       </c>
       <c r="AK11" s="10">
         <f t="shared" ref="AK11:AK48" si="13">AJ11/AG11</f>
-        <v>0.72265415549597856</v>
+        <v>0.72268766756032177</v>
       </c>
       <c r="AL11" s="5">
         <v>28848</v>
@@ -1958,14 +1958,14 @@
       </c>
       <c r="E14" s="9">
         <f t="shared" si="0"/>
-        <v>11302</v>
+        <v>11303</v>
       </c>
       <c r="F14" s="8">
-        <v>34687</v>
+        <v>34688</v>
       </c>
       <c r="G14" s="10">
         <f t="shared" si="1"/>
-        <v>0.26452375505223824</v>
+        <v>0.26453138107221841</v>
       </c>
       <c r="H14" s="5">
         <v>113453</v>
@@ -1975,14 +1975,14 @@
       </c>
       <c r="J14" s="9">
         <f t="shared" si="2"/>
-        <v>13245</v>
+        <v>13246</v>
       </c>
       <c r="K14" s="8">
-        <v>34874</v>
+        <v>34875</v>
       </c>
       <c r="L14" s="10">
         <f t="shared" si="3"/>
-        <v>0.30738719998589725</v>
+        <v>0.30739601420852686</v>
       </c>
       <c r="M14" s="5">
         <v>130093</v>
@@ -1992,14 +1992,14 @@
       </c>
       <c r="O14" s="9">
         <f t="shared" si="4"/>
-        <v>66712</v>
+        <v>66717</v>
       </c>
       <c r="P14" s="8">
-        <v>115525</v>
+        <v>115530</v>
       </c>
       <c r="Q14" s="10">
         <f t="shared" si="5"/>
-        <v>0.88801857132974105</v>
+        <v>0.8880570053730793</v>
       </c>
       <c r="R14" s="5">
         <v>63308</v>
@@ -2009,14 +2009,14 @@
       </c>
       <c r="T14" s="9">
         <f t="shared" si="6"/>
-        <v>27582</v>
+        <v>27583</v>
       </c>
       <c r="U14" s="8">
-        <v>35695</v>
+        <v>35696</v>
       </c>
       <c r="V14" s="10">
         <f t="shared" si="7"/>
-        <v>0.56383079547608517</v>
+        <v>0.56384659126808623</v>
       </c>
       <c r="W14" s="5">
         <v>61226</v>
@@ -2026,14 +2026,14 @@
       </c>
       <c r="Y14" s="9">
         <f t="shared" si="8"/>
-        <v>25503</v>
+        <v>25504</v>
       </c>
       <c r="Z14" s="8">
-        <v>36045</v>
+        <v>36046</v>
       </c>
       <c r="AA14" s="10">
         <f t="shared" si="9"/>
-        <v>0.58872047822820373</v>
+        <v>0.58873681115865806</v>
       </c>
       <c r="AB14" s="5">
         <v>138271</v>
@@ -2043,14 +2043,14 @@
       </c>
       <c r="AD14" s="9">
         <f t="shared" si="10"/>
-        <v>53069</v>
+        <v>53073</v>
       </c>
       <c r="AE14" s="8">
-        <v>120150</v>
+        <v>120154</v>
       </c>
       <c r="AF14" s="10">
         <f t="shared" si="11"/>
-        <v>0.86894576592344019</v>
+        <v>0.86897469462143184</v>
       </c>
       <c r="AG14" s="5">
         <v>55999</v>
@@ -2060,14 +2060,14 @@
       </c>
       <c r="AI14" s="9">
         <f t="shared" si="12"/>
-        <v>24997</v>
+        <v>24998</v>
       </c>
       <c r="AJ14" s="8">
-        <v>37047</v>
+        <v>37048</v>
       </c>
       <c r="AK14" s="10">
         <f t="shared" si="13"/>
-        <v>0.66156538509616247</v>
+        <v>0.6615832425579028</v>
       </c>
       <c r="AL14" s="5">
         <v>53588</v>
@@ -2077,14 +2077,14 @@
       </c>
       <c r="AN14" s="9">
         <f t="shared" si="14"/>
-        <v>24298</v>
+        <v>24300</v>
       </c>
       <c r="AO14" s="8">
-        <v>37513</v>
+        <v>37515</v>
       </c>
       <c r="AP14" s="10">
         <f t="shared" si="15"/>
-        <v>0.70002612525192209</v>
+        <v>0.70006344704038215</v>
       </c>
       <c r="AQ14" s="22">
         <v>140248</v>
@@ -2094,14 +2094,14 @@
       </c>
       <c r="AS14" s="9">
         <f t="shared" si="16"/>
-        <v>35431</v>
+        <v>35437</v>
       </c>
       <c r="AT14" s="8">
-        <v>125125</v>
+        <v>125131</v>
       </c>
       <c r="AU14" s="10">
         <f t="shared" si="17"/>
-        <v>0.8921695853060293</v>
+        <v>0.89221236666476522</v>
       </c>
       <c r="AV14" s="22">
         <v>71286</v>
@@ -2111,14 +2111,14 @@
       </c>
       <c r="AX14" s="9">
         <f t="shared" si="18"/>
-        <v>35673</v>
+        <v>35675</v>
       </c>
       <c r="AY14" s="9">
-        <v>59680</v>
+        <v>59682</v>
       </c>
       <c r="AZ14" s="10">
         <f t="shared" si="19"/>
-        <v>0.83719103330247169</v>
+        <v>0.83721908930224731</v>
       </c>
       <c r="BA14" s="22">
         <v>69175</v>
@@ -2128,14 +2128,14 @@
       </c>
       <c r="BC14" s="9">
         <f t="shared" si="20"/>
-        <v>34348</v>
+        <v>34349</v>
       </c>
       <c r="BD14" s="8">
-        <v>61425</v>
+        <v>61426</v>
       </c>
       <c r="BE14" s="10">
         <f t="shared" si="21"/>
-        <v>0.88796530538489338</v>
+        <v>0.88797976147452118</v>
       </c>
       <c r="BF14" s="9">
         <v>138667</v>
@@ -2145,14 +2145,14 @@
       </c>
       <c r="BH14" s="9">
         <f t="shared" si="22"/>
-        <v>70012</v>
+        <v>70015</v>
       </c>
       <c r="BI14" s="6">
-        <v>129520</v>
+        <v>129523</v>
       </c>
       <c r="BJ14" s="10">
         <f t="shared" si="23"/>
-        <v>0.9340362162590955</v>
+        <v>0.93405785082247395</v>
       </c>
     </row>
     <row r="15" spans="1:62" x14ac:dyDescent="0.3">
@@ -2255,14 +2255,14 @@
       </c>
       <c r="AD15" s="9">
         <f t="shared" si="10"/>
-        <v>126161</v>
+        <v>126162</v>
       </c>
       <c r="AE15" s="8">
-        <v>399115</v>
+        <v>399116</v>
       </c>
       <c r="AF15" s="10">
         <f t="shared" si="11"/>
-        <v>0.89848067697558143</v>
+        <v>0.898482928158015</v>
       </c>
       <c r="AG15" s="5">
         <v>197957</v>
@@ -2416,14 +2416,14 @@
       </c>
       <c r="O16" s="9">
         <f t="shared" si="4"/>
-        <v>326401</v>
+        <v>326402</v>
       </c>
       <c r="P16" s="8">
-        <v>630726</v>
+        <v>630727</v>
       </c>
       <c r="Q16" s="10">
         <f t="shared" si="5"/>
-        <v>0.8572908171587017</v>
+        <v>0.85729217637144561</v>
       </c>
       <c r="R16" s="5">
         <v>377107</v>
@@ -2433,14 +2433,14 @@
       </c>
       <c r="T16" s="9">
         <f t="shared" si="6"/>
-        <v>145097</v>
+        <v>145098</v>
       </c>
       <c r="U16" s="8">
-        <v>208420</v>
+        <v>208421</v>
       </c>
       <c r="V16" s="10">
         <f t="shared" si="7"/>
-        <v>0.55268133447536105</v>
+        <v>0.55268398624263138</v>
       </c>
       <c r="W16" s="5">
         <v>358920</v>
@@ -2467,14 +2467,14 @@
       </c>
       <c r="AD16" s="9">
         <f t="shared" si="10"/>
-        <v>218533</v>
+        <v>218536</v>
       </c>
       <c r="AE16" s="8">
-        <v>649881</v>
+        <v>649884</v>
       </c>
       <c r="AF16" s="10">
         <f t="shared" si="11"/>
-        <v>0.85043812126065854</v>
+        <v>0.85044204707840643</v>
       </c>
       <c r="AG16" s="5">
         <v>333237</v>
@@ -2594,14 +2594,14 @@
       </c>
       <c r="E17" s="9">
         <f t="shared" si="0"/>
-        <v>33424</v>
+        <v>33426</v>
       </c>
       <c r="F17" s="8">
-        <v>138325</v>
+        <v>138327</v>
       </c>
       <c r="G17" s="10">
         <f t="shared" si="1"/>
-        <v>0.25131996351704416</v>
+        <v>0.25132359727758657</v>
       </c>
       <c r="H17" s="5">
         <v>502451</v>
@@ -2611,14 +2611,14 @@
       </c>
       <c r="J17" s="9">
         <f t="shared" si="2"/>
-        <v>39845</v>
+        <v>39847</v>
       </c>
       <c r="K17" s="8">
-        <v>138718</v>
+        <v>138720</v>
       </c>
       <c r="L17" s="10">
         <f t="shared" si="3"/>
-        <v>0.27608264288457979</v>
+        <v>0.27608662337222933</v>
       </c>
       <c r="M17" s="5">
         <v>556868</v>
@@ -2628,14 +2628,14 @@
       </c>
       <c r="O17" s="9">
         <f t="shared" si="4"/>
-        <v>259023</v>
+        <v>259027</v>
       </c>
       <c r="P17" s="8">
-        <v>514370</v>
+        <v>514374</v>
       </c>
       <c r="Q17" s="10">
         <f t="shared" si="5"/>
-        <v>0.92368388918020072</v>
+        <v>0.92369107221100877</v>
       </c>
       <c r="R17" s="5">
         <v>233458</v>
@@ -2645,14 +2645,14 @@
       </c>
       <c r="T17" s="9">
         <f t="shared" si="6"/>
-        <v>96610</v>
+        <v>96612</v>
       </c>
       <c r="U17" s="8">
-        <v>141765</v>
+        <v>141767</v>
       </c>
       <c r="V17" s="10">
         <f t="shared" si="7"/>
-        <v>0.60723984613934845</v>
+        <v>0.60724841299077348</v>
       </c>
       <c r="W17" s="5">
         <v>221561</v>
@@ -2662,14 +2662,14 @@
       </c>
       <c r="Y17" s="9">
         <f t="shared" si="8"/>
-        <v>86585</v>
+        <v>86587</v>
       </c>
       <c r="Z17" s="8">
-        <v>142726</v>
+        <v>142728</v>
       </c>
       <c r="AA17" s="10">
         <f t="shared" si="9"/>
-        <v>0.64418376880407657</v>
+        <v>0.64419279566349674</v>
       </c>
       <c r="AB17" s="5">
         <v>582052</v>
@@ -2679,14 +2679,14 @@
       </c>
       <c r="AD17" s="9">
         <f t="shared" si="10"/>
-        <v>196948</v>
+        <v>196954</v>
       </c>
       <c r="AE17" s="8">
-        <v>535857</v>
+        <v>535863</v>
       </c>
       <c r="AF17" s="10">
         <f t="shared" si="11"/>
-        <v>0.92063423886525597</v>
+        <v>0.92064454722258493</v>
       </c>
       <c r="AG17" s="5">
         <v>198905</v>
@@ -2696,14 +2696,14 @@
       </c>
       <c r="AI17" s="9">
         <f t="shared" si="12"/>
-        <v>84778</v>
+        <v>84781</v>
       </c>
       <c r="AJ17" s="8">
-        <v>144562</v>
+        <v>144565</v>
       </c>
       <c r="AK17" s="10">
         <f t="shared" si="13"/>
-        <v>0.72678917070963522</v>
+        <v>0.72680425328674492</v>
       </c>
       <c r="AL17" s="5">
         <v>191155</v>
@@ -2713,14 +2713,14 @@
       </c>
       <c r="AN17" s="9">
         <f t="shared" si="14"/>
-        <v>82767</v>
+        <v>82769</v>
       </c>
       <c r="AO17" s="8">
-        <v>145999</v>
+        <v>146001</v>
       </c>
       <c r="AP17" s="10">
         <f t="shared" si="15"/>
-        <v>0.76377285448981191</v>
+        <v>0.76378331720331671</v>
       </c>
       <c r="AQ17" s="22">
         <v>594970</v>
@@ -2730,14 +2730,14 @@
       </c>
       <c r="AS17" s="9">
         <f t="shared" si="16"/>
-        <v>115076</v>
+        <v>115080</v>
       </c>
       <c r="AT17" s="8">
-        <v>556255</v>
+        <v>556259</v>
       </c>
       <c r="AU17" s="10">
         <f t="shared" si="17"/>
-        <v>0.93492949224330635</v>
+        <v>0.93493621527135817</v>
       </c>
       <c r="AV17" s="22">
         <v>254447</v>
@@ -2747,14 +2747,14 @@
       </c>
       <c r="AX17" s="9">
         <f t="shared" si="18"/>
-        <v>115485</v>
+        <v>115488</v>
       </c>
       <c r="AY17" s="9">
-        <v>224984</v>
+        <v>224987</v>
       </c>
       <c r="AZ17" s="10">
         <f t="shared" si="19"/>
-        <v>0.88420771319764035</v>
+        <v>0.88421950347223588</v>
       </c>
       <c r="BA17" s="22">
         <v>254024</v>
@@ -2764,14 +2764,14 @@
       </c>
       <c r="BC17" s="9">
         <f t="shared" si="20"/>
-        <v>106326</v>
+        <v>106327</v>
       </c>
       <c r="BD17" s="8">
-        <v>234305</v>
+        <v>234306</v>
       </c>
       <c r="BE17" s="10">
         <f t="shared" si="21"/>
-        <v>0.92237347652190349</v>
+        <v>0.92237741315781185</v>
       </c>
       <c r="BF17" s="9">
         <v>590776</v>
@@ -2781,14 +2781,14 @@
       </c>
       <c r="BH17" s="9">
         <f t="shared" si="22"/>
-        <v>261174</v>
+        <v>261177</v>
       </c>
       <c r="BI17" s="6">
-        <v>572582</v>
+        <v>572585</v>
       </c>
       <c r="BJ17" s="10">
         <f t="shared" si="23"/>
-        <v>0.9692032174631332</v>
+        <v>0.96920829552994703</v>
       </c>
     </row>
     <row r="18" spans="1:62" x14ac:dyDescent="0.3">
@@ -2823,14 +2823,14 @@
       </c>
       <c r="J18" s="9">
         <f t="shared" si="2"/>
-        <v>131827</v>
+        <v>131828</v>
       </c>
       <c r="K18" s="8">
-        <v>332136</v>
+        <v>332137</v>
       </c>
       <c r="L18" s="10">
         <f t="shared" si="3"/>
-        <v>0.31998273571481561</v>
+        <v>0.31998369912358704</v>
       </c>
       <c r="M18" s="5">
         <v>1134575</v>
@@ -2840,14 +2840,14 @@
       </c>
       <c r="O18" s="9">
         <f t="shared" si="4"/>
-        <v>604405</v>
+        <v>604410</v>
       </c>
       <c r="P18" s="8">
-        <v>1000751</v>
+        <v>1000756</v>
       </c>
       <c r="Q18" s="10">
         <f t="shared" si="5"/>
-        <v>0.88204922548090692</v>
+        <v>0.88205363241742507</v>
       </c>
       <c r="R18" s="5">
         <v>560923</v>
@@ -2857,14 +2857,14 @@
       </c>
       <c r="T18" s="9">
         <f t="shared" si="6"/>
-        <v>280944</v>
+        <v>280945</v>
       </c>
       <c r="U18" s="8">
-        <v>340407</v>
+        <v>340408</v>
       </c>
       <c r="V18" s="10">
         <f t="shared" si="7"/>
-        <v>0.60686939205559409</v>
+        <v>0.60687117483148312</v>
       </c>
       <c r="W18" s="5">
         <v>535952</v>
@@ -2874,14 +2874,14 @@
       </c>
       <c r="Y18" s="9">
         <f t="shared" si="8"/>
-        <v>262473</v>
+        <v>262474</v>
       </c>
       <c r="Z18" s="8">
-        <v>344126</v>
+        <v>344127</v>
       </c>
       <c r="AA18" s="10">
         <f t="shared" si="9"/>
-        <v>0.64208361942860559</v>
+        <v>0.64208548526733733</v>
       </c>
       <c r="AB18" s="5">
         <v>1210642</v>
@@ -2891,14 +2891,14 @@
       </c>
       <c r="AD18" s="9">
         <f t="shared" si="10"/>
-        <v>486257</v>
+        <v>486262</v>
       </c>
       <c r="AE18" s="8">
-        <v>1048109</v>
+        <v>1048114</v>
       </c>
       <c r="AF18" s="10">
         <f t="shared" si="11"/>
-        <v>0.86574643866642653</v>
+        <v>0.86575056870652101</v>
       </c>
       <c r="AG18" s="5">
         <v>495943</v>
@@ -2908,14 +2908,14 @@
       </c>
       <c r="AI18" s="9">
         <f t="shared" si="12"/>
-        <v>257043</v>
+        <v>257045</v>
       </c>
       <c r="AJ18" s="8">
-        <v>353148</v>
+        <v>353150</v>
       </c>
       <c r="AK18" s="10">
         <f t="shared" si="13"/>
-        <v>0.7120737665417195</v>
+        <v>0.71207779926322179</v>
       </c>
       <c r="AL18" s="5">
         <v>477702</v>
@@ -2925,14 +2925,14 @@
       </c>
       <c r="AN18" s="9">
         <f t="shared" si="14"/>
-        <v>255788</v>
+        <v>255789</v>
       </c>
       <c r="AO18" s="8">
-        <v>358369</v>
+        <v>358370</v>
       </c>
       <c r="AP18" s="10">
         <f t="shared" si="15"/>
-        <v>0.75019363536263195</v>
+        <v>0.75019572871790363</v>
       </c>
       <c r="AQ18" s="22">
         <v>1231355</v>
@@ -2942,14 +2942,14 @@
       </c>
       <c r="AS18" s="9">
         <f t="shared" si="16"/>
-        <v>296459</v>
+        <v>296465</v>
       </c>
       <c r="AT18" s="8">
-        <v>1092319</v>
+        <v>1092325</v>
       </c>
       <c r="AU18" s="10">
         <f t="shared" si="17"/>
-        <v>0.8870869895359178</v>
+        <v>0.88709186221682623</v>
       </c>
       <c r="AV18" s="22">
         <v>676361</v>
@@ -2959,14 +2959,14 @@
       </c>
       <c r="AX18" s="9">
         <f t="shared" si="18"/>
-        <v>330631</v>
+        <v>330637</v>
       </c>
       <c r="AY18" s="9">
-        <v>573205</v>
+        <v>573211</v>
       </c>
       <c r="AZ18" s="10">
         <f t="shared" si="19"/>
-        <v>0.84748381411701734</v>
+        <v>0.84749268511933717</v>
       </c>
       <c r="BA18" s="22">
         <v>652080</v>
@@ -2976,14 +2976,14 @@
       </c>
       <c r="BC18" s="9">
         <f t="shared" si="20"/>
-        <v>316138</v>
+        <v>316144</v>
       </c>
       <c r="BD18" s="8">
-        <v>587349</v>
+        <v>587355</v>
       </c>
       <c r="BE18" s="10">
         <f t="shared" si="21"/>
-        <v>0.90073150533676849</v>
+        <v>0.90074070666175932</v>
       </c>
       <c r="BF18" s="9">
         <v>1203078</v>
@@ -2993,14 +2993,14 @@
       </c>
       <c r="BH18" s="9">
         <f t="shared" si="22"/>
-        <v>595065</v>
+        <v>595070</v>
       </c>
       <c r="BI18" s="6">
-        <v>1125688</v>
+        <v>1125693</v>
       </c>
       <c r="BJ18" s="10">
         <f t="shared" si="23"/>
-        <v>0.93567333123870611</v>
+        <v>0.93567748724521604</v>
       </c>
     </row>
     <row r="19" spans="1:62" x14ac:dyDescent="0.3">
@@ -3052,14 +3052,14 @@
       </c>
       <c r="O19" s="9">
         <f t="shared" si="4"/>
-        <v>210398</v>
+        <v>210399</v>
       </c>
       <c r="P19" s="8">
-        <v>278111</v>
+        <v>278112</v>
       </c>
       <c r="Q19" s="10">
         <f t="shared" si="5"/>
-        <v>0.85102587248886918</v>
+        <v>0.85102893251120737</v>
       </c>
       <c r="R19" s="5">
         <v>182406</v>
@@ -3069,14 +3069,14 @@
       </c>
       <c r="T19" s="9">
         <f t="shared" si="6"/>
-        <v>85574</v>
+        <v>85575</v>
       </c>
       <c r="U19" s="8">
-        <v>95492</v>
+        <v>95493</v>
       </c>
       <c r="V19" s="10">
         <f t="shared" si="7"/>
-        <v>0.52351348091619798</v>
+        <v>0.52351896319200031</v>
       </c>
       <c r="W19" s="5">
         <v>174793</v>
@@ -3086,14 +3086,14 @@
       </c>
       <c r="Y19" s="9">
         <f t="shared" si="8"/>
-        <v>83339</v>
+        <v>83341</v>
       </c>
       <c r="Z19" s="8">
-        <v>96682</v>
+        <v>96684</v>
       </c>
       <c r="AA19" s="10">
         <f t="shared" si="9"/>
-        <v>0.55312283672687124</v>
+        <v>0.55313427883267641</v>
       </c>
       <c r="AB19" s="5">
         <v>355383</v>
@@ -3103,14 +3103,14 @@
       </c>
       <c r="AD19" s="9">
         <f t="shared" si="10"/>
-        <v>164269</v>
+        <v>164273</v>
       </c>
       <c r="AE19" s="8">
-        <v>291741</v>
+        <v>291745</v>
       </c>
       <c r="AF19" s="10">
         <f t="shared" si="11"/>
-        <v>0.82091996522062116</v>
+        <v>0.8209312206830377</v>
       </c>
       <c r="AG19" s="5">
         <v>163328</v>
@@ -3120,14 +3120,14 @@
       </c>
       <c r="AI19" s="9">
         <f t="shared" si="12"/>
-        <v>81717</v>
+        <v>81718</v>
       </c>
       <c r="AJ19" s="8">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="AK19" s="10">
         <f t="shared" si="13"/>
-        <v>0.60794842280564265</v>
+        <v>0.60795454545454541</v>
       </c>
       <c r="AL19" s="5">
         <v>160483</v>
@@ -3154,14 +3154,14 @@
       </c>
       <c r="AS19" s="9">
         <f t="shared" si="16"/>
-        <v>120087</v>
+        <v>120088</v>
       </c>
       <c r="AT19" s="8">
-        <v>306823</v>
+        <v>306824</v>
       </c>
       <c r="AU19" s="10">
         <f t="shared" si="17"/>
-        <v>0.82258397475596445</v>
+        <v>0.82258665572829959</v>
       </c>
       <c r="AV19" s="22">
         <v>223136</v>
@@ -3171,14 +3171,14 @@
       </c>
       <c r="AX19" s="9">
         <f t="shared" si="18"/>
-        <v>120771</v>
+        <v>120772</v>
       </c>
       <c r="AY19" s="9">
-        <v>165128</v>
+        <v>165129</v>
       </c>
       <c r="AZ19" s="10">
         <f t="shared" si="19"/>
-        <v>0.74003298436827769</v>
+        <v>0.74003746594005448</v>
       </c>
       <c r="BA19" s="22">
         <v>218799</v>
@@ -3188,14 +3188,14 @@
       </c>
       <c r="BC19" s="9">
         <f t="shared" si="20"/>
-        <v>118607</v>
+        <v>118608</v>
       </c>
       <c r="BD19" s="8">
-        <v>171498</v>
+        <v>171499</v>
       </c>
       <c r="BE19" s="10">
         <f t="shared" si="21"/>
-        <v>0.78381528251957278</v>
+        <v>0.78381985292437351</v>
       </c>
       <c r="BF19" s="9">
         <v>376756</v>
@@ -3205,14 +3205,14 @@
       </c>
       <c r="BH19" s="9">
         <f t="shared" si="22"/>
-        <v>222000</v>
+        <v>222001</v>
       </c>
       <c r="BI19" s="6">
-        <v>323354</v>
+        <v>323355</v>
       </c>
       <c r="BJ19" s="10">
         <f t="shared" si="23"/>
-        <v>0.85825839535402226</v>
+        <v>0.85826104959177818</v>
       </c>
     </row>
     <row r="20" spans="1:62" x14ac:dyDescent="0.3">
@@ -3417,14 +3417,14 @@
       </c>
       <c r="BH20" s="9">
         <f t="shared" si="22"/>
-        <v>4538</v>
+        <v>4539</v>
       </c>
       <c r="BI20" s="6">
-        <v>6937</v>
+        <v>6938</v>
       </c>
       <c r="BJ20" s="10">
         <f t="shared" si="23"/>
-        <v>0.87977171845275837</v>
+        <v>0.87989854153455926</v>
       </c>
     </row>
     <row r="21" spans="1:62" x14ac:dyDescent="0.3">
@@ -3476,14 +3476,14 @@
       </c>
       <c r="O21" s="9">
         <f t="shared" si="4"/>
-        <v>6467</v>
+        <v>6468</v>
       </c>
       <c r="P21" s="8">
-        <v>8744</v>
+        <v>8745</v>
       </c>
       <c r="Q21" s="10">
         <f t="shared" si="5"/>
-        <v>0.72438074724546431</v>
+        <v>0.72446359042332864</v>
       </c>
       <c r="R21" s="5">
         <v>8791</v>
@@ -3527,14 +3527,14 @@
       </c>
       <c r="AD21" s="9">
         <f t="shared" si="10"/>
-        <v>5216</v>
+        <v>5217</v>
       </c>
       <c r="AE21" s="8">
-        <v>8997</v>
+        <v>8998</v>
       </c>
       <c r="AF21" s="10">
         <f t="shared" si="11"/>
-        <v>0.71325511336610115</v>
+        <v>0.71333439035991753</v>
       </c>
       <c r="AG21" s="5">
         <v>7886</v>
@@ -3578,14 +3578,14 @@
       </c>
       <c r="AS21" s="9">
         <f t="shared" si="16"/>
-        <v>4040</v>
+        <v>4041</v>
       </c>
       <c r="AT21" s="8">
-        <v>9429</v>
+        <v>9430</v>
       </c>
       <c r="AU21" s="10">
         <f t="shared" si="17"/>
-        <v>0.71850948715994822</v>
+        <v>0.71858568924788535</v>
       </c>
       <c r="AV21" s="22">
         <v>9474</v>
@@ -3671,14 +3671,14 @@
       </c>
       <c r="J22" s="9">
         <f t="shared" si="2"/>
-        <v>1812</v>
+        <v>1813</v>
       </c>
       <c r="K22" s="8">
-        <v>3695</v>
+        <v>3696</v>
       </c>
       <c r="L22" s="10">
         <f t="shared" si="3"/>
-        <v>0.57707324691550832</v>
+        <v>0.57722942370763708</v>
       </c>
       <c r="M22" s="5">
         <v>6636</v>
@@ -3688,14 +3688,14 @@
       </c>
       <c r="O22" s="9">
         <f t="shared" si="4"/>
-        <v>3458</v>
+        <v>3459</v>
       </c>
       <c r="P22" s="8">
-        <v>5240</v>
+        <v>5241</v>
       </c>
       <c r="Q22" s="10">
         <f t="shared" si="5"/>
-        <v>0.78963230861965039</v>
+        <v>0.78978300180831829</v>
       </c>
       <c r="R22" s="5">
         <v>5537</v>
@@ -3705,14 +3705,14 @@
       </c>
       <c r="T22" s="9">
         <f t="shared" si="6"/>
-        <v>3234</v>
+        <v>3235</v>
       </c>
       <c r="U22" s="8">
-        <v>3726</v>
+        <v>3727</v>
       </c>
       <c r="V22" s="10">
         <f t="shared" si="7"/>
-        <v>0.67292757811089032</v>
+        <v>0.67310818132562755</v>
       </c>
       <c r="W22" s="5">
         <v>5469</v>
@@ -3790,14 +3790,14 @@
       </c>
       <c r="AS22" s="9">
         <f t="shared" si="16"/>
-        <v>2101</v>
+        <v>2102</v>
       </c>
       <c r="AT22" s="8">
-        <v>5597</v>
+        <v>5598</v>
       </c>
       <c r="AU22" s="10">
         <f t="shared" si="17"/>
-        <v>0.78964446952595935</v>
+        <v>0.78978555304740405</v>
       </c>
       <c r="AV22" s="22">
         <v>5686</v>
@@ -3807,14 +3807,14 @@
       </c>
       <c r="AX22" s="9">
         <f t="shared" si="18"/>
-        <v>3237</v>
+        <v>3238</v>
       </c>
       <c r="AY22" s="9">
-        <v>4392</v>
+        <v>4393</v>
       </c>
       <c r="AZ22" s="10">
         <f t="shared" si="19"/>
-        <v>0.77242349630671825</v>
+        <v>0.77259936686598663</v>
       </c>
       <c r="BA22" s="22">
         <v>5622</v>
@@ -3824,14 +3824,14 @@
       </c>
       <c r="BC22" s="9">
         <f t="shared" si="20"/>
-        <v>3150</v>
+        <v>3151</v>
       </c>
       <c r="BD22" s="8">
-        <v>4473</v>
+        <v>4474</v>
       </c>
       <c r="BE22" s="10">
         <f t="shared" si="21"/>
-        <v>0.79562433297758806</v>
+        <v>0.79580220562077553</v>
       </c>
       <c r="BF22" s="9">
         <v>6948</v>
@@ -3841,14 +3841,14 @@
       </c>
       <c r="BH22" s="9">
         <f t="shared" si="22"/>
-        <v>4138</v>
+        <v>4139</v>
       </c>
       <c r="BI22" s="6">
-        <v>5831</v>
+        <v>5832</v>
       </c>
       <c r="BJ22" s="10">
         <f t="shared" si="23"/>
-        <v>0.83923431203223953</v>
+        <v>0.8393782383419689</v>
       </c>
     </row>
     <row r="23" spans="1:62" x14ac:dyDescent="0.3">
@@ -4078,14 +4078,14 @@
       </c>
       <c r="E24" s="9">
         <f t="shared" si="0"/>
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="F24" s="8">
-        <v>2894</v>
+        <v>2895</v>
       </c>
       <c r="G24" s="10">
         <f t="shared" si="1"/>
-        <v>0.46557271557271557</v>
+        <v>0.46573359073359072</v>
       </c>
       <c r="H24" s="5">
         <v>5730</v>
@@ -4095,14 +4095,14 @@
       </c>
       <c r="J24" s="9">
         <f t="shared" si="2"/>
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="K24" s="8">
-        <v>2896</v>
+        <v>2897</v>
       </c>
       <c r="L24" s="10">
         <f t="shared" si="3"/>
-        <v>0.5054101221640489</v>
+        <v>0.50558464223385691</v>
       </c>
       <c r="M24" s="5">
         <v>6293</v>
@@ -4112,14 +4112,14 @@
       </c>
       <c r="O24" s="9">
         <f t="shared" si="4"/>
-        <v>2281</v>
+        <v>2282</v>
       </c>
       <c r="P24" s="8">
-        <v>4479</v>
+        <v>4480</v>
       </c>
       <c r="Q24" s="10">
         <f t="shared" si="5"/>
-        <v>0.71174320673764502</v>
+        <v>0.71190211345939935</v>
       </c>
       <c r="R24" s="5">
         <v>5052</v>
@@ -4129,14 +4129,14 @@
       </c>
       <c r="T24" s="9">
         <f t="shared" si="6"/>
-        <v>2404</v>
+        <v>2405</v>
       </c>
       <c r="U24" s="8">
-        <v>2980</v>
+        <v>2981</v>
       </c>
       <c r="V24" s="10">
         <f t="shared" si="7"/>
-        <v>0.58986539984164688</v>
+        <v>0.59006334125098969</v>
       </c>
       <c r="W24" s="5">
         <v>5122</v>
@@ -4146,14 +4146,14 @@
       </c>
       <c r="Y24" s="9">
         <f t="shared" si="8"/>
-        <v>2411</v>
+        <v>2412</v>
       </c>
       <c r="Z24" s="8">
-        <v>3022</v>
+        <v>3023</v>
       </c>
       <c r="AA24" s="10">
         <f t="shared" si="9"/>
-        <v>0.59000390472471687</v>
+        <v>0.59019914096056225</v>
       </c>
       <c r="AB24" s="5">
         <v>6663</v>
@@ -4163,14 +4163,14 @@
       </c>
       <c r="AD24" s="9">
         <f t="shared" si="10"/>
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="AE24" s="8">
-        <v>4643</v>
+        <v>4644</v>
       </c>
       <c r="AF24" s="10">
         <f t="shared" si="11"/>
-        <v>0.69683325829206066</v>
+        <v>0.69698334083746061</v>
       </c>
       <c r="AG24" s="5">
         <v>5175</v>
@@ -4180,14 +4180,14 @@
       </c>
       <c r="AI24" s="9">
         <f t="shared" si="12"/>
-        <v>2338</v>
+        <v>2339</v>
       </c>
       <c r="AJ24" s="8">
-        <v>3097</v>
+        <v>3098</v>
       </c>
       <c r="AK24" s="10">
         <f t="shared" si="13"/>
-        <v>0.59845410628019324</v>
+        <v>0.59864734299516909</v>
       </c>
       <c r="AL24" s="5">
         <v>5189</v>
@@ -4443,14 +4443,14 @@
       </c>
       <c r="AX25" s="9">
         <f t="shared" si="18"/>
-        <v>7292</v>
+        <v>7293</v>
       </c>
       <c r="AY25" s="9">
-        <v>12255</v>
+        <v>12256</v>
       </c>
       <c r="AZ25" s="10">
         <f t="shared" si="19"/>
-        <v>0.77367424242424243</v>
+        <v>0.77373737373737372</v>
       </c>
       <c r="BA25" s="22">
         <v>15498</v>
@@ -4460,14 +4460,14 @@
       </c>
       <c r="BC25" s="9">
         <f t="shared" si="20"/>
-        <v>6928</v>
+        <v>6929</v>
       </c>
       <c r="BD25" s="8">
-        <v>12418</v>
+        <v>12419</v>
       </c>
       <c r="BE25" s="10">
         <f t="shared" si="21"/>
-        <v>0.80126467931345979</v>
+        <v>0.80132920376822814</v>
       </c>
       <c r="BF25" s="9">
         <v>25465</v>
@@ -4502,14 +4502,14 @@
       </c>
       <c r="E26" s="9">
         <f t="shared" si="0"/>
-        <v>3526</v>
+        <v>3527</v>
       </c>
       <c r="F26" s="8">
-        <v>7625</v>
+        <v>7626</v>
       </c>
       <c r="G26" s="10">
         <f t="shared" si="1"/>
-        <v>0.28717234106658635</v>
+        <v>0.28721000301295568</v>
       </c>
       <c r="H26" s="5">
         <v>23466</v>
@@ -4519,14 +4519,14 @@
       </c>
       <c r="J26" s="9">
         <f t="shared" si="2"/>
-        <v>3886</v>
+        <v>3887</v>
       </c>
       <c r="K26" s="8">
-        <v>7645</v>
+        <v>7646</v>
       </c>
       <c r="L26" s="10">
         <f t="shared" si="3"/>
-        <v>0.3257905054120856</v>
+        <v>0.32583312025909827</v>
       </c>
       <c r="M26" s="5">
         <v>25760</v>
@@ -4536,14 +4536,14 @@
       </c>
       <c r="O26" s="9">
         <f t="shared" si="4"/>
-        <v>10445</v>
+        <v>10448</v>
       </c>
       <c r="P26" s="8">
-        <v>17316</v>
+        <v>17319</v>
       </c>
       <c r="Q26" s="10">
         <f t="shared" si="5"/>
-        <v>0.67220496894409942</v>
+        <v>0.67232142857142863</v>
       </c>
       <c r="R26" s="5">
         <v>16534</v>
@@ -4570,14 +4570,14 @@
       </c>
       <c r="Y26" s="9">
         <f t="shared" si="8"/>
-        <v>6286</v>
+        <v>6287</v>
       </c>
       <c r="Z26" s="8">
-        <v>7762</v>
+        <v>7763</v>
       </c>
       <c r="AA26" s="10">
         <f t="shared" si="9"/>
-        <v>0.4831922310756972</v>
+        <v>0.48325448207171312</v>
       </c>
       <c r="AB26" s="5">
         <v>25659</v>
@@ -4587,14 +4587,14 @@
       </c>
       <c r="AD26" s="9">
         <f t="shared" si="10"/>
-        <v>9218</v>
+        <v>9221</v>
       </c>
       <c r="AE26" s="8">
-        <v>17586</v>
+        <v>17589</v>
       </c>
       <c r="AF26" s="10">
         <f t="shared" si="11"/>
-        <v>0.68537355313924941</v>
+        <v>0.68549047117970308</v>
       </c>
       <c r="AG26" s="5">
         <v>15065</v>
@@ -4604,14 +4604,14 @@
       </c>
       <c r="AI26" s="9">
         <f t="shared" si="12"/>
-        <v>6168</v>
+        <v>6169</v>
       </c>
       <c r="AJ26" s="8">
-        <v>7944</v>
+        <v>7945</v>
       </c>
       <c r="AK26" s="10">
         <f t="shared" si="13"/>
-        <v>0.52731496846996351</v>
+        <v>0.52738134749419185</v>
       </c>
       <c r="AL26" s="5">
         <v>14868</v>
@@ -4621,14 +4621,14 @@
       </c>
       <c r="AN26" s="9">
         <f t="shared" si="14"/>
-        <v>6211</v>
+        <v>6212</v>
       </c>
       <c r="AO26" s="8">
-        <v>7980</v>
+        <v>7981</v>
       </c>
       <c r="AP26" s="10">
         <f t="shared" si="15"/>
-        <v>0.53672316384180796</v>
+        <v>0.53679042238364272</v>
       </c>
       <c r="AQ26" s="22">
         <v>26317</v>
@@ -4638,14 +4638,14 @@
       </c>
       <c r="AS26" s="9">
         <f t="shared" si="16"/>
-        <v>7562</v>
+        <v>7565</v>
       </c>
       <c r="AT26" s="8">
-        <v>18132</v>
+        <v>18135</v>
       </c>
       <c r="AU26" s="10">
         <f t="shared" si="17"/>
-        <v>0.68898430672189082</v>
+        <v>0.689098301478132</v>
       </c>
       <c r="AV26" s="22">
         <v>16878</v>
@@ -4655,14 +4655,14 @@
       </c>
       <c r="AX26" s="9">
         <f t="shared" si="18"/>
-        <v>7678</v>
+        <v>7680</v>
       </c>
       <c r="AY26" s="9">
-        <v>10299</v>
+        <v>10301</v>
       </c>
       <c r="AZ26" s="10">
         <f t="shared" si="19"/>
-        <v>0.61020263064344116</v>
+        <v>0.6103211280957459</v>
       </c>
       <c r="BA26" s="22">
         <v>16511</v>
@@ -4672,14 +4672,14 @@
       </c>
       <c r="BC26" s="9">
         <f t="shared" si="20"/>
-        <v>7373</v>
+        <v>7375</v>
       </c>
       <c r="BD26" s="8">
-        <v>10290</v>
+        <v>10292</v>
       </c>
       <c r="BE26" s="10">
         <f t="shared" si="21"/>
-        <v>0.62322088304766521</v>
+        <v>0.62334201441463266</v>
       </c>
       <c r="BF26" s="9">
         <v>25358</v>
@@ -4689,14 +4689,14 @@
       </c>
       <c r="BH26" s="9">
         <f t="shared" si="22"/>
-        <v>12731</v>
+        <v>12734</v>
       </c>
       <c r="BI26" s="6">
-        <v>18478</v>
+        <v>18481</v>
       </c>
       <c r="BJ26" s="10">
         <f t="shared" si="23"/>
-        <v>0.72868522754160425</v>
+        <v>0.7288035334016878</v>
       </c>
     </row>
     <row r="27" spans="1:62" x14ac:dyDescent="0.3">
@@ -4714,14 +4714,14 @@
       </c>
       <c r="E27" s="9">
         <f t="shared" si="0"/>
-        <v>27159</v>
+        <v>27161</v>
       </c>
       <c r="F27" s="8">
-        <v>53278</v>
+        <v>53280</v>
       </c>
       <c r="G27" s="10">
         <f t="shared" si="1"/>
-        <v>0.3664261789971045</v>
+        <v>0.36643993424989169</v>
       </c>
       <c r="H27" s="5">
         <v>133004</v>
@@ -4748,14 +4748,14 @@
       </c>
       <c r="O27" s="9">
         <f t="shared" si="4"/>
-        <v>89628</v>
+        <v>89632</v>
       </c>
       <c r="P27" s="8">
-        <v>121226</v>
+        <v>121230</v>
       </c>
       <c r="Q27" s="10">
         <f t="shared" si="5"/>
-        <v>0.82644323852635593</v>
+        <v>0.82647050803086908</v>
       </c>
       <c r="R27" s="5">
         <v>100364</v>
@@ -4765,14 +4765,14 @@
       </c>
       <c r="T27" s="9">
         <f t="shared" si="6"/>
-        <v>48154</v>
+        <v>48155</v>
       </c>
       <c r="U27" s="8">
-        <v>54585</v>
+        <v>54586</v>
       </c>
       <c r="V27" s="10">
         <f t="shared" si="7"/>
-        <v>0.54387031206408676</v>
+        <v>0.54388027579610221</v>
       </c>
       <c r="W27" s="5">
         <v>96252</v>
@@ -4782,14 +4782,14 @@
       </c>
       <c r="Y27" s="9">
         <f t="shared" si="8"/>
-        <v>45964</v>
+        <v>45966</v>
       </c>
       <c r="Z27" s="8">
-        <v>55295</v>
+        <v>55297</v>
       </c>
       <c r="AA27" s="10">
         <f t="shared" si="9"/>
-        <v>0.57448156921414617</v>
+        <v>0.57450234800315836</v>
       </c>
       <c r="AB27" s="5">
         <v>156081</v>
@@ -4799,14 +4799,14 @@
       </c>
       <c r="AD27" s="9">
         <f t="shared" si="10"/>
-        <v>70850</v>
+        <v>70855</v>
       </c>
       <c r="AE27" s="8">
-        <v>125728</v>
+        <v>125733</v>
       </c>
       <c r="AF27" s="10">
         <f t="shared" si="11"/>
-        <v>0.80553046174742604</v>
+        <v>0.805562496396102</v>
       </c>
       <c r="AG27" s="5">
         <v>90207</v>
@@ -4816,14 +4816,14 @@
       </c>
       <c r="AI27" s="9">
         <f t="shared" si="12"/>
-        <v>43209</v>
+        <v>43211</v>
       </c>
       <c r="AJ27" s="8">
-        <v>56363</v>
+        <v>56365</v>
       </c>
       <c r="AK27" s="10">
         <f t="shared" si="13"/>
-        <v>0.62481847306750027</v>
+        <v>0.62484064429589725</v>
       </c>
       <c r="AL27" s="5">
         <v>89207</v>
@@ -4833,14 +4833,14 @@
       </c>
       <c r="AN27" s="9">
         <f t="shared" si="14"/>
-        <v>43647</v>
+        <v>43649</v>
       </c>
       <c r="AO27" s="8">
-        <v>57100</v>
+        <v>57102</v>
       </c>
       <c r="AP27" s="10">
         <f t="shared" si="15"/>
-        <v>0.64008429831739666</v>
+        <v>0.64010671808266173</v>
       </c>
       <c r="AQ27" s="22">
         <v>161396</v>
@@ -4850,14 +4850,14 @@
       </c>
       <c r="AS27" s="9">
         <f t="shared" si="16"/>
-        <v>52383</v>
+        <v>52387</v>
       </c>
       <c r="AT27" s="8">
-        <v>131361</v>
+        <v>131365</v>
       </c>
       <c r="AU27" s="10">
         <f t="shared" si="17"/>
-        <v>0.81390492949019799</v>
+        <v>0.81392971325187735</v>
       </c>
       <c r="AV27" s="22">
         <v>108391</v>
@@ -4867,14 +4867,14 @@
       </c>
       <c r="AX27" s="9">
         <f t="shared" si="18"/>
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="AY27" s="9">
-        <v>81720</v>
+        <v>81724</v>
       </c>
       <c r="AZ27" s="10">
         <f t="shared" si="19"/>
-        <v>0.75393713500198356</v>
+        <v>0.75397403843492539</v>
       </c>
       <c r="BA27" s="22">
         <v>101826</v>
@@ -4884,14 +4884,14 @@
       </c>
       <c r="BC27" s="9">
         <f t="shared" si="20"/>
-        <v>56633</v>
+        <v>56637</v>
       </c>
       <c r="BD27" s="8">
-        <v>83633</v>
+        <v>83637</v>
       </c>
       <c r="BE27" s="10">
         <f t="shared" si="21"/>
-        <v>0.82133246911397872</v>
+        <v>0.82137175181191446</v>
       </c>
       <c r="BF27" s="9">
         <v>155251</v>
@@ -4901,14 +4901,14 @@
       </c>
       <c r="BH27" s="9">
         <f t="shared" si="22"/>
-        <v>92683</v>
+        <v>92688</v>
       </c>
       <c r="BI27" s="6">
-        <v>135906</v>
+        <v>135911</v>
       </c>
       <c r="BJ27" s="10">
         <f t="shared" si="23"/>
-        <v>0.8753953275663281</v>
+        <v>0.87542753347804525</v>
       </c>
     </row>
     <row r="28" spans="1:62" x14ac:dyDescent="0.3">
@@ -4960,14 +4960,14 @@
       </c>
       <c r="O28" s="9">
         <f t="shared" si="4"/>
-        <v>317136</v>
+        <v>317138</v>
       </c>
       <c r="P28" s="8">
-        <v>515635</v>
+        <v>515637</v>
       </c>
       <c r="Q28" s="10">
         <f t="shared" si="5"/>
-        <v>0.85078035154181098</v>
+        <v>0.85078365147432733</v>
       </c>
       <c r="R28" s="5">
         <v>322040</v>
@@ -5011,14 +5011,14 @@
       </c>
       <c r="AD28" s="9">
         <f t="shared" si="10"/>
-        <v>237488</v>
+        <v>237491</v>
       </c>
       <c r="AE28" s="8">
-        <v>521358</v>
+        <v>521361</v>
       </c>
       <c r="AF28" s="10">
         <f t="shared" si="11"/>
-        <v>0.84531335375176531</v>
+        <v>0.84531821785677808</v>
       </c>
       <c r="AG28" s="5">
         <v>279354</v>
@@ -5062,14 +5062,14 @@
       </c>
       <c r="AS28" s="9">
         <f t="shared" si="16"/>
-        <v>155356</v>
+        <v>155359</v>
       </c>
       <c r="AT28" s="8">
-        <v>532668</v>
+        <v>532671</v>
       </c>
       <c r="AU28" s="10">
         <f t="shared" si="17"/>
-        <v>0.85146229491425718</v>
+        <v>0.85146709037199964</v>
       </c>
       <c r="AV28" s="22">
         <v>329857</v>
@@ -5079,14 +5079,14 @@
       </c>
       <c r="AX28" s="9">
         <f t="shared" si="18"/>
-        <v>153805</v>
+        <v>153808</v>
       </c>
       <c r="AY28" s="9">
-        <v>254208</v>
+        <v>254211</v>
       </c>
       <c r="AZ28" s="10">
         <f t="shared" si="19"/>
-        <v>0.77066122592517361</v>
+        <v>0.77067032077536635</v>
       </c>
       <c r="BA28" s="22">
         <v>323426</v>
@@ -5096,14 +5096,14 @@
       </c>
       <c r="BC28" s="9">
         <f t="shared" si="20"/>
-        <v>140111</v>
+        <v>140114</v>
       </c>
       <c r="BD28" s="8">
-        <v>257983</v>
+        <v>257986</v>
       </c>
       <c r="BE28" s="10">
         <f t="shared" si="21"/>
-        <v>0.79765696017017806</v>
+        <v>0.79766623586229923</v>
       </c>
       <c r="BF28" s="9">
         <v>619161</v>
@@ -5113,14 +5113,14 @@
       </c>
       <c r="BH28" s="9">
         <f t="shared" si="22"/>
-        <v>279109</v>
+        <v>279111</v>
       </c>
       <c r="BI28" s="6">
-        <v>545821</v>
+        <v>545823</v>
       </c>
       <c r="BJ28" s="10">
         <f t="shared" si="23"/>
-        <v>0.88154938699304386</v>
+        <v>0.88155261717065514</v>
       </c>
     </row>
     <row r="29" spans="1:62" x14ac:dyDescent="0.3">
@@ -5138,14 +5138,14 @@
       </c>
       <c r="E29" s="9">
         <f t="shared" si="0"/>
-        <v>22276</v>
+        <v>22277</v>
       </c>
       <c r="F29" s="8">
-        <v>57877</v>
+        <v>57878</v>
       </c>
       <c r="G29" s="10">
         <f t="shared" si="1"/>
-        <v>0.40426497911515302</v>
+        <v>0.40427196401380217</v>
       </c>
       <c r="H29" s="5">
         <v>131410</v>
@@ -5155,14 +5155,14 @@
       </c>
       <c r="J29" s="9">
         <f t="shared" si="2"/>
-        <v>25108</v>
+        <v>25109</v>
       </c>
       <c r="K29" s="8">
-        <v>57936</v>
+        <v>57937</v>
       </c>
       <c r="L29" s="10">
         <f t="shared" si="3"/>
-        <v>0.44087968952134543</v>
+        <v>0.44088729929229131</v>
       </c>
       <c r="M29" s="5">
         <v>144577</v>
@@ -5172,14 +5172,14 @@
       </c>
       <c r="O29" s="9">
         <f t="shared" si="4"/>
-        <v>79876</v>
+        <v>79878</v>
       </c>
       <c r="P29" s="8">
-        <v>129716</v>
+        <v>129718</v>
       </c>
       <c r="Q29" s="10">
         <f t="shared" si="5"/>
-        <v>0.89721048299522055</v>
+        <v>0.89722431645420775</v>
       </c>
       <c r="R29" s="5">
         <v>86442</v>
@@ -5189,14 +5189,14 @@
       </c>
       <c r="T29" s="9">
         <f t="shared" si="6"/>
-        <v>49245</v>
+        <v>49246</v>
       </c>
       <c r="U29" s="8">
-        <v>59155</v>
+        <v>59156</v>
       </c>
       <c r="V29" s="10">
         <f t="shared" si="7"/>
-        <v>0.6843316906133593</v>
+        <v>0.68434325906388094</v>
       </c>
       <c r="W29" s="5">
         <v>83687</v>
@@ -5206,14 +5206,14 @@
       </c>
       <c r="Y29" s="9">
         <f t="shared" si="8"/>
-        <v>46725</v>
+        <v>46726</v>
       </c>
       <c r="Z29" s="8">
-        <v>59679</v>
+        <v>59680</v>
       </c>
       <c r="AA29" s="10">
         <f t="shared" si="9"/>
-        <v>0.71312151230179122</v>
+        <v>0.71313346158901625</v>
       </c>
       <c r="AB29" s="5">
         <v>153397</v>
@@ -5223,14 +5223,14 @@
       </c>
       <c r="AD29" s="9">
         <f t="shared" si="10"/>
-        <v>61926</v>
+        <v>61928</v>
       </c>
       <c r="AE29" s="8">
-        <v>133918</v>
+        <v>133920</v>
       </c>
       <c r="AF29" s="10">
         <f t="shared" si="11"/>
-        <v>0.87301576953916959</v>
+        <v>0.87302880760379931</v>
       </c>
       <c r="AG29" s="5">
         <v>79643</v>
@@ -5240,14 +5240,14 @@
       </c>
       <c r="AI29" s="9">
         <f t="shared" si="12"/>
-        <v>44064</v>
+        <v>44065</v>
       </c>
       <c r="AJ29" s="8">
-        <v>60819</v>
+        <v>60820</v>
       </c>
       <c r="AK29" s="10">
         <f t="shared" si="13"/>
-        <v>0.76364526700400537</v>
+        <v>0.76365782303529506</v>
       </c>
       <c r="AL29" s="5">
         <v>78780</v>
@@ -5274,14 +5274,14 @@
       </c>
       <c r="AS29" s="9">
         <f t="shared" si="16"/>
-        <v>41578</v>
+        <v>41580</v>
       </c>
       <c r="AT29" s="8">
-        <v>138703</v>
+        <v>138705</v>
       </c>
       <c r="AU29" s="10">
         <f t="shared" si="17"/>
-        <v>0.8918602632441921</v>
+        <v>0.8918731232438063</v>
       </c>
       <c r="AV29" s="22">
         <v>96040</v>
@@ -5325,14 +5325,14 @@
       </c>
       <c r="BH29" s="9">
         <f t="shared" si="22"/>
-        <v>83899</v>
+        <v>83901</v>
       </c>
       <c r="BI29" s="6">
-        <v>143671</v>
+        <v>143673</v>
       </c>
       <c r="BJ29" s="10">
         <f t="shared" si="23"/>
-        <v>0.93867644080309953</v>
+        <v>0.93868950783041616</v>
       </c>
     </row>
     <row r="30" spans="1:62" x14ac:dyDescent="0.3">
@@ -5350,14 +5350,14 @@
       </c>
       <c r="E30" s="9">
         <f t="shared" si="0"/>
-        <v>30456</v>
+        <v>30457</v>
       </c>
       <c r="F30" s="8">
-        <v>77354</v>
+        <v>77355</v>
       </c>
       <c r="G30" s="10">
         <f t="shared" si="1"/>
-        <v>0.34790234951246718</v>
+        <v>0.34790684704781777</v>
       </c>
       <c r="H30" s="5">
         <v>196739</v>
@@ -5367,14 +5367,14 @@
       </c>
       <c r="J30" s="9">
         <f t="shared" si="2"/>
-        <v>35386</v>
+        <v>35387</v>
       </c>
       <c r="K30" s="8">
-        <v>77592</v>
+        <v>77593</v>
       </c>
       <c r="L30" s="10">
         <f t="shared" si="3"/>
-        <v>0.39439053771748356</v>
+        <v>0.39439562059378158</v>
       </c>
       <c r="M30" s="5">
         <v>227236</v>
@@ -5384,14 +5384,14 @@
       </c>
       <c r="O30" s="9">
         <f t="shared" si="4"/>
-        <v>132034</v>
+        <v>132035</v>
       </c>
       <c r="P30" s="8">
-        <v>197263</v>
+        <v>197264</v>
       </c>
       <c r="Q30" s="10">
         <f t="shared" si="5"/>
-        <v>0.86809748455350388</v>
+        <v>0.86810188526465881</v>
       </c>
       <c r="R30" s="5">
         <v>127114</v>
@@ -5401,14 +5401,14 @@
       </c>
       <c r="T30" s="9">
         <f t="shared" si="6"/>
-        <v>67309</v>
+        <v>67310</v>
       </c>
       <c r="U30" s="8">
-        <v>79308</v>
+        <v>79309</v>
       </c>
       <c r="V30" s="10">
         <f t="shared" si="7"/>
-        <v>0.62391239359944617</v>
+        <v>0.6239202605535189</v>
       </c>
       <c r="W30" s="5">
         <v>123894</v>
@@ -5418,14 +5418,14 @@
       </c>
       <c r="Y30" s="9">
         <f t="shared" si="8"/>
-        <v>64461</v>
+        <v>64462</v>
       </c>
       <c r="Z30" s="8">
-        <v>79903</v>
+        <v>79904</v>
       </c>
       <c r="AA30" s="10">
         <f t="shared" si="9"/>
-        <v>0.64493034368088853</v>
+        <v>0.6449384150967763</v>
       </c>
       <c r="AB30" s="5">
         <v>242455</v>
@@ -5435,14 +5435,14 @@
       </c>
       <c r="AD30" s="9">
         <f t="shared" si="10"/>
-        <v>99286</v>
+        <v>99289</v>
       </c>
       <c r="AE30" s="8">
-        <v>203365</v>
+        <v>203368</v>
       </c>
       <c r="AF30" s="10">
         <f t="shared" si="11"/>
-        <v>0.83877420552267434</v>
+        <v>0.8387865789527954</v>
       </c>
       <c r="AG30" s="5">
         <v>117700</v>
@@ -5452,14 +5452,14 @@
       </c>
       <c r="AI30" s="9">
         <f t="shared" si="12"/>
-        <v>61298</v>
+        <v>61300</v>
       </c>
       <c r="AJ30" s="8">
-        <v>81936</v>
+        <v>81938</v>
       </c>
       <c r="AK30" s="10">
         <f t="shared" si="13"/>
-        <v>0.69614273576890395</v>
+        <v>0.69615972812234495</v>
       </c>
       <c r="AL30" s="5">
         <v>115490</v>
@@ -5469,14 +5469,14 @@
       </c>
       <c r="AN30" s="9">
         <f t="shared" si="14"/>
-        <v>62026</v>
+        <v>62027</v>
       </c>
       <c r="AO30" s="8">
-        <v>83086</v>
+        <v>83087</v>
       </c>
       <c r="AP30" s="10">
         <f t="shared" si="15"/>
-        <v>0.71942159494328517</v>
+        <v>0.71943025370161917</v>
       </c>
       <c r="AQ30" s="22">
         <v>248265</v>
@@ -5486,14 +5486,14 @@
       </c>
       <c r="AS30" s="9">
         <f t="shared" si="16"/>
-        <v>74370</v>
+        <v>74371</v>
       </c>
       <c r="AT30" s="8">
-        <v>212359</v>
+        <v>212360</v>
       </c>
       <c r="AU30" s="10">
         <f t="shared" si="17"/>
-        <v>0.85537228364852069</v>
+        <v>0.85537631160252148</v>
       </c>
       <c r="AV30" s="22">
         <v>136681</v>
@@ -5503,14 +5503,14 @@
       </c>
       <c r="AX30" s="9">
         <f t="shared" si="18"/>
-        <v>78444</v>
+        <v>78445</v>
       </c>
       <c r="AY30" s="9">
-        <v>110631</v>
+        <v>110632</v>
       </c>
       <c r="AZ30" s="10">
         <f t="shared" si="19"/>
-        <v>0.80941023258536304</v>
+        <v>0.80941754889121387</v>
       </c>
       <c r="BA30" s="22">
         <v>130520</v>
@@ -5520,14 +5520,14 @@
       </c>
       <c r="BC30" s="9">
         <f t="shared" si="20"/>
-        <v>76627</v>
+        <v>76628</v>
       </c>
       <c r="BD30" s="8">
-        <v>113438</v>
+        <v>113439</v>
       </c>
       <c r="BE30" s="10">
         <f t="shared" si="21"/>
-        <v>0.86912350597609567</v>
+        <v>0.86913116763714371</v>
       </c>
       <c r="BF30" s="9">
         <v>245647</v>
@@ -5537,14 +5537,14 @@
       </c>
       <c r="BH30" s="9">
         <f t="shared" si="22"/>
-        <v>141116</v>
+        <v>141117</v>
       </c>
       <c r="BI30" s="6">
-        <v>221809</v>
+        <v>221810</v>
       </c>
       <c r="BJ30" s="10">
         <f t="shared" si="23"/>
-        <v>0.90295831009538075</v>
+        <v>0.90296238097758164</v>
       </c>
     </row>
     <row r="31" spans="1:62" x14ac:dyDescent="0.3">
@@ -5562,14 +5562,14 @@
       </c>
       <c r="E31" s="9">
         <f t="shared" si="0"/>
-        <v>16308</v>
+        <v>16309</v>
       </c>
       <c r="F31" s="8">
-        <v>41822</v>
+        <v>41823</v>
       </c>
       <c r="G31" s="10">
         <f t="shared" si="1"/>
-        <v>0.39209472825628383</v>
+        <v>0.39210410357856051</v>
       </c>
       <c r="H31" s="5">
         <v>97781</v>
@@ -5579,14 +5579,14 @@
       </c>
       <c r="J31" s="9">
         <f t="shared" si="2"/>
-        <v>18553</v>
+        <v>18554</v>
       </c>
       <c r="K31" s="8">
-        <v>41901</v>
+        <v>41902</v>
       </c>
       <c r="L31" s="10">
         <f t="shared" si="3"/>
-        <v>0.42851883290209752</v>
+        <v>0.42852905983780082</v>
       </c>
       <c r="M31" s="5">
         <v>107995</v>
@@ -5596,14 +5596,14 @@
       </c>
       <c r="O31" s="9">
         <f t="shared" si="4"/>
-        <v>64556</v>
+        <v>64558</v>
       </c>
       <c r="P31" s="8">
-        <v>98085</v>
+        <v>98087</v>
       </c>
       <c r="Q31" s="10">
         <f t="shared" si="5"/>
-        <v>0.9082364924302051</v>
+        <v>0.90825501180610213</v>
       </c>
       <c r="R31" s="5">
         <v>65023</v>
@@ -5613,14 +5613,14 @@
       </c>
       <c r="T31" s="9">
         <f t="shared" si="6"/>
-        <v>35239</v>
+        <v>35240</v>
       </c>
       <c r="U31" s="8">
-        <v>42840</v>
+        <v>42841</v>
       </c>
       <c r="V31" s="10">
         <f t="shared" si="7"/>
-        <v>0.65884379373452473</v>
+        <v>0.65885917290804796</v>
       </c>
       <c r="W31" s="5">
         <v>62560</v>
@@ -5630,14 +5630,14 @@
       </c>
       <c r="Y31" s="9">
         <f t="shared" si="8"/>
-        <v>33335</v>
+        <v>33337</v>
       </c>
       <c r="Z31" s="8">
-        <v>43151</v>
+        <v>43153</v>
       </c>
       <c r="AA31" s="10">
         <f t="shared" si="9"/>
-        <v>0.6897538363171356</v>
+        <v>0.68978580562659841</v>
       </c>
       <c r="AB31" s="5">
         <v>113499</v>
@@ -5647,14 +5647,14 @@
       </c>
       <c r="AD31" s="9">
         <f t="shared" si="10"/>
-        <v>52962</v>
+        <v>52968</v>
       </c>
       <c r="AE31" s="8">
-        <v>101294</v>
+        <v>101300</v>
       </c>
       <c r="AF31" s="10">
         <f t="shared" si="11"/>
-        <v>0.89246601291641336</v>
+        <v>0.892518876818298</v>
       </c>
       <c r="AG31" s="5">
         <v>58990</v>
@@ -5664,14 +5664,14 @@
       </c>
       <c r="AI31" s="9">
         <f t="shared" si="12"/>
-        <v>31526</v>
+        <v>31528</v>
       </c>
       <c r="AJ31" s="8">
-        <v>43727</v>
+        <v>43729</v>
       </c>
       <c r="AK31" s="10">
         <f t="shared" si="13"/>
-        <v>0.74126123071707073</v>
+        <v>0.74129513476860487</v>
       </c>
       <c r="AL31" s="5">
         <v>57896</v>
@@ -5681,14 +5681,14 @@
       </c>
       <c r="AN31" s="9">
         <f t="shared" si="14"/>
-        <v>30990</v>
+        <v>30991</v>
       </c>
       <c r="AO31" s="8">
-        <v>44042</v>
+        <v>44043</v>
       </c>
       <c r="AP31" s="10">
         <f t="shared" si="15"/>
-        <v>0.76070885726129611</v>
+        <v>0.76072612961171759</v>
       </c>
       <c r="AQ31" s="22">
         <v>115872</v>
@@ -5698,14 +5698,14 @@
       </c>
       <c r="AS31" s="9">
         <f t="shared" si="16"/>
-        <v>37961</v>
+        <v>37966</v>
       </c>
       <c r="AT31" s="8">
-        <v>104656</v>
+        <v>104661</v>
       </c>
       <c r="AU31" s="10">
         <f t="shared" si="17"/>
-        <v>0.90320353493510075</v>
+        <v>0.90324668599834301</v>
       </c>
       <c r="AV31" s="22">
         <v>66185</v>
@@ -5715,14 +5715,14 @@
       </c>
       <c r="AX31" s="9">
         <f t="shared" si="18"/>
-        <v>37457</v>
+        <v>37460</v>
       </c>
       <c r="AY31" s="9">
-        <v>57179</v>
+        <v>57182</v>
       </c>
       <c r="AZ31" s="10">
         <f t="shared" si="19"/>
-        <v>0.86392687164765425</v>
+        <v>0.86397219913877765</v>
       </c>
       <c r="BA31" s="22">
         <v>65739</v>
@@ -5732,14 +5732,14 @@
       </c>
       <c r="BC31" s="9">
         <f t="shared" si="20"/>
-        <v>36888</v>
+        <v>36889</v>
       </c>
       <c r="BD31" s="8">
-        <v>59457</v>
+        <v>59458</v>
       </c>
       <c r="BE31" s="10">
         <f t="shared" si="21"/>
-        <v>0.90444028658787023</v>
+        <v>0.90445549825826377</v>
       </c>
       <c r="BF31" s="9">
         <v>116311</v>
@@ -5749,14 +5749,14 @@
       </c>
       <c r="BH31" s="9">
         <f t="shared" si="22"/>
-        <v>76439</v>
+        <v>76440</v>
       </c>
       <c r="BI31" s="6">
-        <v>109219</v>
+        <v>109220</v>
       </c>
       <c r="BJ31" s="10">
         <f t="shared" si="23"/>
-        <v>0.93902554358573131</v>
+        <v>0.93903414122481965</v>
       </c>
     </row>
     <row r="32" spans="1:62" x14ac:dyDescent="0.3">
@@ -5808,14 +5808,14 @@
       </c>
       <c r="O32" s="9">
         <f t="shared" si="4"/>
-        <v>199314</v>
+        <v>199315</v>
       </c>
       <c r="P32" s="8">
-        <v>329568</v>
+        <v>329569</v>
       </c>
       <c r="Q32" s="10">
         <f t="shared" si="5"/>
-        <v>0.93331634170171196</v>
+        <v>0.93331917364031547</v>
       </c>
       <c r="R32" s="5">
         <v>166950</v>
@@ -5825,14 +5825,14 @@
       </c>
       <c r="T32" s="9">
         <f t="shared" si="6"/>
-        <v>90909</v>
+        <v>90910</v>
       </c>
       <c r="U32" s="8">
-        <v>114751</v>
+        <v>114752</v>
       </c>
       <c r="V32" s="10">
         <f t="shared" si="7"/>
-        <v>0.68733752620545074</v>
+        <v>0.68734351602276134</v>
       </c>
       <c r="W32" s="5">
         <v>161498</v>
@@ -5842,14 +5842,14 @@
       </c>
       <c r="Y32" s="9">
         <f t="shared" si="8"/>
-        <v>86185</v>
+        <v>86186</v>
       </c>
       <c r="Z32" s="8">
-        <v>115311</v>
+        <v>115312</v>
       </c>
       <c r="AA32" s="10">
         <f t="shared" si="9"/>
-        <v>0.71400884221476424</v>
+        <v>0.71401503424191015</v>
       </c>
       <c r="AB32" s="5">
         <v>374326</v>
@@ -5859,14 +5859,14 @@
       </c>
       <c r="AD32" s="9">
         <f t="shared" si="10"/>
-        <v>160706</v>
+        <v>160707</v>
       </c>
       <c r="AE32" s="8">
-        <v>338749</v>
+        <v>338750</v>
       </c>
       <c r="AF32" s="10">
         <f t="shared" si="11"/>
-        <v>0.90495717636498663</v>
+        <v>0.90495984783317218</v>
       </c>
       <c r="AG32" s="5">
         <v>155463</v>
@@ -5910,14 +5910,14 @@
       </c>
       <c r="AS32" s="9">
         <f t="shared" si="16"/>
-        <v>111944</v>
+        <v>111946</v>
       </c>
       <c r="AT32" s="8">
-        <v>348808</v>
+        <v>348810</v>
       </c>
       <c r="AU32" s="10">
         <f t="shared" si="17"/>
-        <v>0.9206948341441139</v>
+        <v>0.92070011323653234</v>
       </c>
       <c r="AV32" s="22">
         <v>171744</v>
@@ -5927,14 +5927,14 @@
       </c>
       <c r="AX32" s="9">
         <f t="shared" si="18"/>
-        <v>96174</v>
+        <v>96175</v>
       </c>
       <c r="AY32" s="9">
-        <v>152309</v>
+        <v>152310</v>
       </c>
       <c r="AZ32" s="10">
         <f t="shared" si="19"/>
-        <v>0.88683738587665362</v>
+        <v>0.88684320849636666</v>
       </c>
       <c r="BA32" s="22">
         <v>169380</v>
@@ -5944,14 +5944,14 @@
       </c>
       <c r="BC32" s="9">
         <f t="shared" si="20"/>
-        <v>93103</v>
+        <v>93104</v>
       </c>
       <c r="BD32" s="8">
-        <v>156565</v>
+        <v>156566</v>
       </c>
       <c r="BE32" s="10">
         <f t="shared" si="21"/>
-        <v>0.92434171684968713</v>
+        <v>0.92434762073444321</v>
       </c>
       <c r="BF32" s="9">
         <v>378386</v>
@@ -5961,14 +5961,14 @@
       </c>
       <c r="BH32" s="9">
         <f t="shared" si="22"/>
-        <v>248542</v>
+        <v>248545</v>
       </c>
       <c r="BI32" s="6">
-        <v>358220</v>
+        <v>358223</v>
       </c>
       <c r="BJ32" s="10">
         <f t="shared" si="23"/>
-        <v>0.94670521636635607</v>
+        <v>0.94671314477808377</v>
       </c>
     </row>
     <row r="33" spans="1:63" x14ac:dyDescent="0.3">
@@ -5986,14 +5986,14 @@
       </c>
       <c r="E33" s="9">
         <f t="shared" si="0"/>
-        <v>57417</v>
+        <v>57418</v>
       </c>
       <c r="F33" s="8">
-        <v>294975</v>
+        <v>294976</v>
       </c>
       <c r="G33" s="10">
         <f t="shared" si="1"/>
-        <v>0.33093766513225725</v>
+        <v>0.33093878704992868</v>
       </c>
       <c r="H33" s="5">
         <v>840037</v>
@@ -6003,14 +6003,14 @@
       </c>
       <c r="J33" s="9">
         <f t="shared" si="2"/>
-        <v>65403</v>
+        <v>65404</v>
       </c>
       <c r="K33" s="8">
-        <v>295274</v>
+        <v>295275</v>
       </c>
       <c r="L33" s="10">
         <f t="shared" si="3"/>
-        <v>0.35150118387642448</v>
+        <v>0.35150237430017961</v>
       </c>
       <c r="M33" s="5">
         <v>888717</v>
@@ -6020,14 +6020,14 @@
       </c>
       <c r="O33" s="9">
         <f t="shared" si="4"/>
-        <v>331358</v>
+        <v>331363</v>
       </c>
       <c r="P33" s="8">
-        <v>837832</v>
+        <v>837837</v>
       </c>
       <c r="Q33" s="10">
         <f t="shared" si="5"/>
-        <v>0.942743302986215</v>
+        <v>0.94274892907415975</v>
       </c>
       <c r="R33" s="5">
         <v>410545</v>
@@ -6037,14 +6037,14 @@
       </c>
       <c r="T33" s="9">
         <f t="shared" si="6"/>
-        <v>191546</v>
+        <v>191547</v>
       </c>
       <c r="U33" s="8">
-        <v>299402</v>
+        <v>299403</v>
       </c>
       <c r="V33" s="10">
         <f t="shared" si="7"/>
-        <v>0.72927937254137798</v>
+        <v>0.72928180832795431</v>
       </c>
       <c r="W33" s="5">
         <v>395753</v>
@@ -6054,14 +6054,14 @@
       </c>
       <c r="Y33" s="9">
         <f t="shared" si="8"/>
-        <v>163286</v>
+        <v>163287</v>
       </c>
       <c r="Z33" s="8">
-        <v>301317</v>
+        <v>301318</v>
       </c>
       <c r="AA33" s="10">
         <f t="shared" si="9"/>
-        <v>0.76137641407645673</v>
+        <v>0.76137894090505942</v>
       </c>
       <c r="AB33" s="5">
         <v>919225</v>
@@ -6071,14 +6071,14 @@
       </c>
       <c r="AD33" s="9">
         <f t="shared" si="10"/>
-        <v>217523</v>
+        <v>217529</v>
       </c>
       <c r="AE33" s="8">
-        <v>863394</v>
+        <v>863400</v>
       </c>
       <c r="AF33" s="10">
         <f t="shared" si="11"/>
-        <v>0.93926296608556126</v>
+        <v>0.93926949332317988</v>
       </c>
       <c r="AG33" s="5">
         <v>374721</v>
@@ -6088,14 +6088,14 @@
       </c>
       <c r="AI33" s="9">
         <f t="shared" si="12"/>
-        <v>140252</v>
+        <v>140256</v>
       </c>
       <c r="AJ33" s="8">
-        <v>305404</v>
+        <v>305408</v>
       </c>
       <c r="AK33" s="10">
         <f t="shared" si="13"/>
-        <v>0.81501703934393854</v>
+        <v>0.81502771395251405</v>
       </c>
       <c r="AL33" s="5">
         <v>367134</v>
@@ -6105,14 +6105,14 @@
       </c>
       <c r="AN33" s="9">
         <f t="shared" si="14"/>
-        <v>142090</v>
+        <v>142092</v>
       </c>
       <c r="AO33" s="8">
-        <v>307671</v>
+        <v>307673</v>
       </c>
       <c r="AP33" s="10">
         <f t="shared" si="15"/>
-        <v>0.83803461406461943</v>
+        <v>0.83804006166685729</v>
       </c>
       <c r="AQ33" s="22">
         <v>933808</v>
@@ -6122,14 +6122,14 @@
       </c>
       <c r="AS33" s="9">
         <f t="shared" si="16"/>
-        <v>111349</v>
+        <v>111357</v>
       </c>
       <c r="AT33" s="8">
-        <v>891174</v>
+        <v>891182</v>
       </c>
       <c r="AU33" s="10">
         <f t="shared" si="17"/>
-        <v>0.95434393365659753</v>
+        <v>0.9543525007282011</v>
       </c>
       <c r="AV33" s="22">
         <v>471208</v>
@@ -6139,14 +6139,14 @@
       </c>
       <c r="AX33" s="9">
         <f t="shared" si="18"/>
-        <v>148147</v>
+        <v>148152</v>
       </c>
       <c r="AY33" s="9">
-        <v>435388</v>
+        <v>435393</v>
       </c>
       <c r="AZ33" s="10">
         <f t="shared" si="19"/>
-        <v>0.92398261489618172</v>
+        <v>0.92399322592146138</v>
       </c>
       <c r="BA33" s="22">
         <v>469534</v>
@@ -6156,14 +6156,14 @@
       </c>
       <c r="BC33" s="9">
         <f t="shared" si="20"/>
-        <v>133508</v>
+        <v>133513</v>
       </c>
       <c r="BD33" s="8">
-        <v>447363</v>
+        <v>447368</v>
       </c>
       <c r="BE33" s="10">
         <f t="shared" si="21"/>
-        <v>0.95278084228192206</v>
+        <v>0.95279149113802197</v>
       </c>
       <c r="BF33" s="9">
         <v>935950</v>
@@ -6173,14 +6173,14 @@
       </c>
       <c r="BH33" s="9">
         <f t="shared" si="22"/>
-        <v>270368</v>
+        <v>270375</v>
       </c>
       <c r="BI33" s="6">
-        <v>916111</v>
+        <v>916118</v>
       </c>
       <c r="BJ33" s="10">
         <f t="shared" si="23"/>
-        <v>0.97880335488006842</v>
+        <v>0.97881083391206791</v>
       </c>
     </row>
     <row r="34" spans="1:63" x14ac:dyDescent="0.3">
@@ -6605,14 +6605,14 @@
       </c>
       <c r="E36" s="9">
         <f t="shared" si="0"/>
-        <v>160260</v>
+        <v>160266</v>
       </c>
       <c r="F36" s="8">
-        <v>404010</v>
+        <v>404016</v>
       </c>
       <c r="G36" s="10">
         <f t="shared" si="1"/>
-        <v>0.29322812220342415</v>
+        <v>0.29323247696873495</v>
       </c>
       <c r="H36" s="5">
         <v>1292614</v>
@@ -6622,14 +6622,14 @@
       </c>
       <c r="J36" s="9">
         <f t="shared" si="2"/>
-        <v>174079</v>
+        <v>174084</v>
       </c>
       <c r="K36" s="8">
-        <v>404211</v>
+        <v>404216</v>
       </c>
       <c r="L36" s="10">
         <f t="shared" si="3"/>
-        <v>0.31270820213923106</v>
+        <v>0.31271207027001102</v>
       </c>
       <c r="M36" s="5">
         <v>1376699</v>
@@ -6639,14 +6639,14 @@
       </c>
       <c r="O36" s="9">
         <f t="shared" si="4"/>
-        <v>743393</v>
+        <v>743402</v>
       </c>
       <c r="P36" s="8">
-        <v>1226727</v>
+        <v>1226736</v>
       </c>
       <c r="Q36" s="10">
         <f t="shared" si="5"/>
-        <v>0.89106405975452874</v>
+        <v>0.89107059713125381</v>
       </c>
       <c r="R36" s="5">
         <v>745641</v>
@@ -6656,14 +6656,14 @@
       </c>
       <c r="T36" s="9">
         <f t="shared" si="6"/>
-        <v>301879</v>
+        <v>301885</v>
       </c>
       <c r="U36" s="8">
-        <v>409697</v>
+        <v>409703</v>
       </c>
       <c r="V36" s="10">
         <f t="shared" si="7"/>
-        <v>0.54945610555213564</v>
+        <v>0.54946415231995027</v>
       </c>
       <c r="W36" s="5">
         <v>686690</v>
@@ -6673,14 +6673,14 @@
       </c>
       <c r="Y36" s="9">
         <f t="shared" si="8"/>
-        <v>276515</v>
+        <v>276522</v>
       </c>
       <c r="Z36" s="8">
-        <v>412176</v>
+        <v>412183</v>
       </c>
       <c r="AA36" s="10">
         <f t="shared" si="9"/>
-        <v>0.60023591431359125</v>
+        <v>0.60024610814195634</v>
       </c>
       <c r="AB36" s="5">
         <v>1408098</v>
@@ -6690,14 +6690,14 @@
       </c>
       <c r="AD36" s="9">
         <f t="shared" si="10"/>
-        <v>511488</v>
+        <v>511498</v>
       </c>
       <c r="AE36" s="8">
-        <v>1248554</v>
+        <v>1248564</v>
       </c>
       <c r="AF36" s="10">
         <f t="shared" si="11"/>
-        <v>0.88669538625862687</v>
+        <v>0.8867024880370542</v>
       </c>
       <c r="AG36" s="5">
         <v>587071</v>
@@ -6707,14 +6707,14 @@
       </c>
       <c r="AI36" s="9">
         <f t="shared" si="12"/>
-        <v>248195</v>
+        <v>248200</v>
       </c>
       <c r="AJ36" s="8">
-        <v>417502</v>
+        <v>417507</v>
       </c>
       <c r="AK36" s="10">
         <f t="shared" si="13"/>
-        <v>0.71116100096921842</v>
+        <v>0.71116951782663429</v>
       </c>
       <c r="AL36" s="5">
         <v>562582</v>
@@ -6724,14 +6724,14 @@
       </c>
       <c r="AN36" s="9">
         <f t="shared" si="14"/>
-        <v>238174</v>
+        <v>238180</v>
       </c>
       <c r="AO36" s="8">
-        <v>421193</v>
+        <v>421199</v>
       </c>
       <c r="AP36" s="10">
         <f t="shared" si="15"/>
-        <v>0.74867841487996412</v>
+        <v>0.74868907999189449</v>
       </c>
       <c r="AQ36" s="22">
         <v>1406326</v>
@@ -6741,14 +6741,14 @@
       </c>
       <c r="AS36" s="9">
         <f t="shared" si="16"/>
-        <v>335752</v>
+        <v>335764</v>
       </c>
       <c r="AT36" s="8">
-        <v>1284240</v>
+        <v>1284252</v>
       </c>
       <c r="AU36" s="10">
         <f t="shared" si="17"/>
-        <v>0.91318798059624862</v>
+        <v>0.91319651346842767</v>
       </c>
       <c r="AV36" s="22">
         <v>685313</v>
@@ -6758,14 +6758,14 @@
       </c>
       <c r="AX36" s="9">
         <f t="shared" si="18"/>
-        <v>333889</v>
+        <v>333899</v>
       </c>
       <c r="AY36" s="9">
-        <v>603397</v>
+        <v>603407</v>
       </c>
       <c r="AZ36" s="10">
         <f t="shared" si="19"/>
-        <v>0.88046921625592978</v>
+        <v>0.88048380812854854</v>
       </c>
       <c r="BA36" s="22">
         <v>667446</v>
@@ -6775,14 +6775,14 @@
       </c>
       <c r="BC36" s="9">
         <f t="shared" si="20"/>
-        <v>306846</v>
+        <v>306855</v>
       </c>
       <c r="BD36" s="8">
-        <v>617036</v>
+        <v>617045</v>
       </c>
       <c r="BE36" s="10">
         <f t="shared" si="21"/>
-        <v>0.92447329072314466</v>
+        <v>0.9244867749600717</v>
       </c>
       <c r="BF36" s="9">
         <v>1363993</v>
@@ -6792,14 +6792,14 @@
       </c>
       <c r="BH36" s="9">
         <f t="shared" si="22"/>
-        <v>656300</v>
+        <v>656312</v>
       </c>
       <c r="BI36" s="6">
-        <v>1309765</v>
+        <v>1309777</v>
       </c>
       <c r="BJ36" s="10">
         <f t="shared" si="23"/>
-        <v>0.96024319772902056</v>
+        <v>0.960251995428129</v>
       </c>
     </row>
     <row r="37" spans="1:63" x14ac:dyDescent="0.3">
@@ -6817,14 +6817,14 @@
       </c>
       <c r="E37" s="9">
         <f t="shared" si="0"/>
-        <v>126093</v>
+        <v>126097</v>
       </c>
       <c r="F37" s="8">
-        <v>409796</v>
+        <v>409800</v>
       </c>
       <c r="G37" s="10">
         <f t="shared" si="1"/>
-        <v>0.55923774796117776</v>
+        <v>0.55924320665523986</v>
       </c>
       <c r="H37" s="5">
         <v>674591</v>
@@ -6834,14 +6834,14 @@
       </c>
       <c r="J37" s="9">
         <f t="shared" si="2"/>
-        <v>147506</v>
+        <v>147511</v>
       </c>
       <c r="K37" s="8">
-        <v>413304</v>
+        <v>413309</v>
       </c>
       <c r="L37" s="10">
         <f t="shared" si="3"/>
-        <v>0.61267345695391728</v>
+        <v>0.61268086885238615</v>
       </c>
       <c r="M37" s="5">
         <v>737436</v>
@@ -6851,14 +6851,14 @@
       </c>
       <c r="O37" s="9">
         <f t="shared" si="4"/>
-        <v>346095</v>
+        <v>346104</v>
       </c>
       <c r="P37" s="8">
-        <v>645246</v>
+        <v>645255</v>
       </c>
       <c r="Q37" s="10">
         <f t="shared" si="5"/>
-        <v>0.87498576147625018</v>
+        <v>0.87499796592517864</v>
       </c>
       <c r="R37" s="5">
         <v>540612</v>
@@ -6868,14 +6868,14 @@
       </c>
       <c r="T37" s="9">
         <f t="shared" si="6"/>
-        <v>330376</v>
+        <v>330382</v>
       </c>
       <c r="U37" s="8">
-        <v>420069</v>
+        <v>420075</v>
       </c>
       <c r="V37" s="10">
         <f t="shared" si="7"/>
-        <v>0.77702492730461037</v>
+        <v>0.77703602583738429</v>
       </c>
       <c r="W37" s="5">
         <v>536259</v>
@@ -6885,14 +6885,14 @@
       </c>
       <c r="Y37" s="9">
         <f t="shared" si="8"/>
-        <v>307335</v>
+        <v>307341</v>
       </c>
       <c r="Z37" s="8">
-        <v>423764</v>
+        <v>423770</v>
       </c>
       <c r="AA37" s="10">
         <f t="shared" si="9"/>
-        <v>0.79022263495810796</v>
+        <v>0.79023382358151562</v>
       </c>
       <c r="AB37" s="5">
         <v>768520</v>
@@ -6902,14 +6902,14 @@
       </c>
       <c r="AD37" s="9">
         <f t="shared" si="10"/>
-        <v>226265</v>
+        <v>226278</v>
       </c>
       <c r="AE37" s="8">
-        <v>661203</v>
+        <v>661216</v>
       </c>
       <c r="AF37" s="10">
         <f t="shared" si="11"/>
-        <v>0.86035887159735591</v>
+        <v>0.86037578722739816</v>
       </c>
       <c r="AG37" s="5">
         <v>524373</v>
@@ -6919,14 +6919,14 @@
       </c>
       <c r="AI37" s="9">
         <f t="shared" si="12"/>
-        <v>282804</v>
+        <v>282810</v>
       </c>
       <c r="AJ37" s="8">
-        <v>431777</v>
+        <v>431783</v>
       </c>
       <c r="AK37" s="10">
         <f t="shared" si="13"/>
-        <v>0.82341577464896176</v>
+        <v>0.82342721688569009</v>
       </c>
       <c r="AL37" s="5">
         <v>516478</v>
@@ -6936,14 +6936,14 @@
       </c>
       <c r="AN37" s="9">
         <f t="shared" si="14"/>
-        <v>277991</v>
+        <v>277998</v>
       </c>
       <c r="AO37" s="8">
-        <v>437364</v>
+        <v>437371</v>
       </c>
       <c r="AP37" s="10">
         <f t="shared" si="15"/>
-        <v>0.84682019369653694</v>
+        <v>0.84683374703278746</v>
       </c>
       <c r="AQ37" s="22">
         <v>769503</v>
@@ -6953,14 +6953,14 @@
       </c>
       <c r="AS37" s="9">
         <f t="shared" si="16"/>
-        <v>145902</v>
+        <v>145912</v>
       </c>
       <c r="AT37" s="8">
-        <v>682709</v>
+        <v>682719</v>
       </c>
       <c r="AU37" s="10">
         <f t="shared" si="17"/>
-        <v>0.8872077171888868</v>
+        <v>0.8872207125898145</v>
       </c>
       <c r="AV37" s="22">
         <v>526610</v>
@@ -6970,14 +6970,14 @@
       </c>
       <c r="AX37" s="9">
         <f t="shared" si="18"/>
-        <v>255392</v>
+        <v>255396</v>
       </c>
       <c r="AY37" s="9">
-        <v>463247</v>
+        <v>463251</v>
       </c>
       <c r="AZ37" s="10">
         <f t="shared" si="19"/>
-        <v>0.87967756024382371</v>
+        <v>0.87968515599779729</v>
       </c>
       <c r="BA37" s="22">
         <v>525208</v>
@@ -6987,14 +6987,14 @@
       </c>
       <c r="BC37" s="9">
         <f t="shared" si="20"/>
-        <v>248168</v>
+        <v>248171</v>
       </c>
       <c r="BD37" s="8">
-        <v>471687</v>
+        <v>471690</v>
       </c>
       <c r="BE37" s="10">
         <f t="shared" si="21"/>
-        <v>0.89809561164338703</v>
+        <v>0.89810132366605233</v>
       </c>
       <c r="BF37" s="9">
         <v>765317</v>
@@ -7004,14 +7004,14 @@
       </c>
       <c r="BH37" s="9">
         <f t="shared" si="22"/>
-        <v>359919</v>
+        <v>359926</v>
       </c>
       <c r="BI37" s="6">
-        <v>707088</v>
+        <v>707095</v>
       </c>
       <c r="BJ37" s="10">
         <f t="shared" si="23"/>
-        <v>0.92391518808546003</v>
+        <v>0.92392433462212387</v>
       </c>
     </row>
     <row r="38" spans="1:63" x14ac:dyDescent="0.3">
@@ -7216,14 +7216,14 @@
       </c>
       <c r="BH38" s="9">
         <f t="shared" si="22"/>
-        <v>16720</v>
+        <v>16722</v>
       </c>
       <c r="BI38" s="6">
-        <v>31045</v>
+        <v>31047</v>
       </c>
       <c r="BJ38" s="10">
         <f t="shared" si="23"/>
-        <v>0.87551820412307169</v>
+        <v>0.87557460729292991</v>
       </c>
     </row>
     <row r="39" spans="1:63" x14ac:dyDescent="0.3">
@@ -7453,14 +7453,14 @@
       </c>
       <c r="E40" s="9">
         <f t="shared" si="0"/>
-        <v>58084</v>
+        <v>58086</v>
       </c>
       <c r="F40" s="8">
-        <v>174005</v>
+        <v>174007</v>
       </c>
       <c r="G40" s="10">
         <f t="shared" si="1"/>
-        <v>0.57364159639209589</v>
+        <v>0.57364818978419829</v>
       </c>
       <c r="H40" s="5">
         <v>287028</v>
@@ -7470,14 +7470,14 @@
       </c>
       <c r="J40" s="9">
         <f t="shared" si="2"/>
-        <v>72964</v>
+        <v>72966</v>
       </c>
       <c r="K40" s="8">
-        <v>174656</v>
+        <v>174658</v>
       </c>
       <c r="L40" s="10">
         <f t="shared" si="3"/>
-        <v>0.60849812561840655</v>
+        <v>0.60850509357972049</v>
       </c>
       <c r="M40" s="5">
         <v>303033</v>
@@ -7487,14 +7487,14 @@
       </c>
       <c r="O40" s="9">
         <f t="shared" si="4"/>
-        <v>166278</v>
+        <v>166281</v>
       </c>
       <c r="P40" s="8">
-        <v>273164</v>
+        <v>273167</v>
       </c>
       <c r="Q40" s="10">
         <f t="shared" si="5"/>
-        <v>0.90143317724472249</v>
+        <v>0.90144307715661331</v>
       </c>
       <c r="R40" s="5">
         <v>226941</v>
@@ -7504,14 +7504,14 @@
       </c>
       <c r="T40" s="9">
         <f t="shared" si="6"/>
-        <v>150770</v>
+        <v>150774</v>
       </c>
       <c r="U40" s="8">
-        <v>177632</v>
+        <v>177636</v>
       </c>
       <c r="V40" s="10">
         <f t="shared" si="7"/>
-        <v>0.78272326287449157</v>
+        <v>0.78274088860100199</v>
       </c>
       <c r="W40" s="5">
         <v>224663</v>
@@ -7521,14 +7521,14 @@
       </c>
       <c r="Y40" s="9">
         <f t="shared" si="8"/>
-        <v>132198</v>
+        <v>132203</v>
       </c>
       <c r="Z40" s="8">
-        <v>179923</v>
+        <v>179928</v>
       </c>
       <c r="AA40" s="10">
         <f t="shared" si="9"/>
-        <v>0.8008572840209558</v>
+        <v>0.80087953957705538</v>
       </c>
       <c r="AB40" s="5">
         <v>313197</v>
@@ -7538,14 +7538,14 @@
       </c>
       <c r="AD40" s="9">
         <f t="shared" si="10"/>
-        <v>87364</v>
+        <v>87371</v>
       </c>
       <c r="AE40" s="8">
-        <v>280650</v>
+        <v>280657</v>
       </c>
       <c r="AF40" s="10">
         <f t="shared" si="11"/>
-        <v>0.89608138008984761</v>
+        <v>0.8961037302400725</v>
       </c>
       <c r="AG40" s="5">
         <v>217708</v>
@@ -7555,14 +7555,14 @@
       </c>
       <c r="AI40" s="9">
         <f t="shared" si="12"/>
-        <v>92085</v>
+        <v>92088</v>
       </c>
       <c r="AJ40" s="8">
-        <v>184508</v>
+        <v>184511</v>
       </c>
       <c r="AK40" s="10">
         <f t="shared" si="13"/>
-        <v>0.84750215885498004</v>
+        <v>0.84751593878038478</v>
       </c>
       <c r="AL40" s="5">
         <v>217966</v>
@@ -7572,14 +7572,14 @@
       </c>
       <c r="AN40" s="9">
         <f t="shared" si="14"/>
-        <v>88620</v>
+        <v>88623</v>
       </c>
       <c r="AO40" s="8">
-        <v>187513</v>
+        <v>187516</v>
       </c>
       <c r="AP40" s="10">
         <f t="shared" si="15"/>
-        <v>0.86028554912234023</v>
+        <v>0.8602993127368489</v>
       </c>
       <c r="AQ40" s="22">
         <v>320883</v>
@@ -7589,14 +7589,14 @@
       </c>
       <c r="AS40" s="9">
         <f t="shared" si="16"/>
-        <v>54259</v>
+        <v>54264</v>
       </c>
       <c r="AT40" s="8">
-        <v>291071</v>
+        <v>291076</v>
       </c>
       <c r="AU40" s="10">
         <f t="shared" si="17"/>
-        <v>0.90709386287213722</v>
+        <v>0.90710944487554657</v>
       </c>
       <c r="AV40" s="22">
         <v>237287</v>
@@ -7606,14 +7606,14 @@
       </c>
       <c r="AX40" s="9">
         <f t="shared" si="18"/>
-        <v>104137</v>
+        <v>104141</v>
       </c>
       <c r="AY40" s="9">
-        <v>212767</v>
+        <v>212771</v>
       </c>
       <c r="AZ40" s="10">
         <f t="shared" si="19"/>
-        <v>0.89666521975498026</v>
+        <v>0.89668207697851121</v>
       </c>
       <c r="BA40" s="22">
         <v>231690</v>
@@ -7623,14 +7623,14 @@
       </c>
       <c r="BC40" s="9">
         <f t="shared" si="20"/>
-        <v>100492</v>
+        <v>100495</v>
       </c>
       <c r="BD40" s="8">
-        <v>215374</v>
+        <v>215377</v>
       </c>
       <c r="BE40" s="10">
         <f t="shared" si="21"/>
-        <v>0.9295783158530796</v>
+        <v>0.92959126418921834</v>
       </c>
       <c r="BF40" s="9">
         <v>314391</v>
@@ -7640,14 +7640,14 @@
       </c>
       <c r="BH40" s="9">
         <f t="shared" si="22"/>
-        <v>147479</v>
+        <v>147483</v>
       </c>
       <c r="BI40" s="6">
-        <v>298967</v>
+        <v>298971</v>
       </c>
       <c r="BJ40" s="10">
         <f t="shared" si="23"/>
-        <v>0.95094007143970405</v>
+        <v>0.95095279445022285</v>
       </c>
     </row>
     <row r="41" spans="1:63" x14ac:dyDescent="0.3">
@@ -7665,14 +7665,14 @@
       </c>
       <c r="E41" s="9">
         <f t="shared" si="0"/>
-        <v>174727</v>
+        <v>174744</v>
       </c>
       <c r="F41" s="8">
-        <v>589418</v>
+        <v>589435</v>
       </c>
       <c r="G41" s="10">
         <f t="shared" si="1"/>
-        <v>0.67350588299820946</v>
+        <v>0.67352530826179313</v>
       </c>
       <c r="H41" s="5">
         <v>834053</v>
@@ -7682,14 +7682,14 @@
       </c>
       <c r="J41" s="9">
         <f t="shared" si="2"/>
-        <v>212026</v>
+        <v>212047</v>
       </c>
       <c r="K41" s="8">
-        <v>593107</v>
+        <v>593128</v>
       </c>
       <c r="L41" s="10">
         <f t="shared" si="3"/>
-        <v>0.71111428170631841</v>
+        <v>0.71113945996237649</v>
       </c>
       <c r="M41" s="5">
         <v>879453</v>
@@ -7699,14 +7699,14 @@
       </c>
       <c r="O41" s="9">
         <f t="shared" si="4"/>
-        <v>392345</v>
+        <v>392381</v>
       </c>
       <c r="P41" s="8">
-        <v>788429</v>
+        <v>788465</v>
       </c>
       <c r="Q41" s="10">
         <f t="shared" si="5"/>
-        <v>0.89649930127022137</v>
+        <v>0.89654023580566555</v>
       </c>
       <c r="R41" s="5">
         <v>738453</v>
@@ -7716,14 +7716,14 @@
       </c>
       <c r="T41" s="9">
         <f t="shared" si="6"/>
-        <v>486265</v>
+        <v>486287</v>
       </c>
       <c r="U41" s="8">
-        <v>605633</v>
+        <v>605655</v>
       </c>
       <c r="V41" s="10">
         <f t="shared" si="7"/>
-        <v>0.82013750367321958</v>
+        <v>0.82016729568435631</v>
       </c>
       <c r="W41" s="5">
         <v>740008</v>
@@ -7733,14 +7733,14 @@
       </c>
       <c r="Y41" s="9">
         <f t="shared" si="8"/>
-        <v>428149</v>
+        <v>428172</v>
       </c>
       <c r="Z41" s="8">
-        <v>611266</v>
+        <v>611289</v>
       </c>
       <c r="AA41" s="10">
         <f t="shared" si="9"/>
-        <v>0.82602620512210678</v>
+        <v>0.82605728586717986</v>
       </c>
       <c r="AB41" s="5">
         <v>928683</v>
@@ -7750,14 +7750,14 @@
       </c>
       <c r="AD41" s="9">
         <f t="shared" si="10"/>
-        <v>220678</v>
+        <v>220714</v>
       </c>
       <c r="AE41" s="8">
-        <v>813196</v>
+        <v>813232</v>
       </c>
       <c r="AF41" s="10">
         <f t="shared" si="11"/>
-        <v>0.87564432642785539</v>
+        <v>0.87568309100091202</v>
       </c>
       <c r="AG41" s="5">
         <v>734303</v>
@@ -7767,14 +7767,14 @@
       </c>
       <c r="AI41" s="9">
         <f t="shared" si="12"/>
-        <v>376553</v>
+        <v>376576</v>
       </c>
       <c r="AJ41" s="8">
-        <v>623712</v>
+        <v>623735</v>
       </c>
       <c r="AK41" s="10">
         <f t="shared" si="13"/>
-        <v>0.84939323412814605</v>
+        <v>0.84942455634799263</v>
       </c>
       <c r="AL41" s="5">
         <v>728636</v>
@@ -7784,14 +7784,14 @@
       </c>
       <c r="AN41" s="9">
         <f t="shared" si="14"/>
-        <v>357945</v>
+        <v>357965</v>
       </c>
       <c r="AO41" s="8">
-        <v>631366</v>
+        <v>631386</v>
       </c>
       <c r="AP41" s="10">
         <f t="shared" si="15"/>
-        <v>0.86650398827398045</v>
+        <v>0.86653143682167777</v>
       </c>
       <c r="AQ41" s="22">
         <v>923873</v>
@@ -7801,14 +7801,14 @@
       </c>
       <c r="AS41" s="9">
         <f t="shared" si="16"/>
-        <v>140512</v>
+        <v>140547</v>
       </c>
       <c r="AT41" s="8">
-        <v>842119</v>
+        <v>842154</v>
       </c>
       <c r="AU41" s="10">
         <f t="shared" si="17"/>
-        <v>0.91150948236391793</v>
+        <v>0.91154736635879607</v>
       </c>
       <c r="AV41" s="22">
         <v>726271</v>
@@ -7818,14 +7818,14 @@
       </c>
       <c r="AX41" s="9">
         <f t="shared" si="18"/>
-        <v>325958</v>
+        <v>325977</v>
       </c>
       <c r="AY41" s="9">
-        <v>662955</v>
+        <v>662974</v>
       </c>
       <c r="AZ41" s="10">
         <f t="shared" si="19"/>
-        <v>0.91282042102741268</v>
+        <v>0.91284658206096625</v>
       </c>
       <c r="BA41" s="22">
         <v>715104</v>
@@ -7835,14 +7835,14 @@
       </c>
       <c r="BC41" s="9">
         <f t="shared" si="20"/>
-        <v>312305</v>
+        <v>312324</v>
       </c>
       <c r="BD41" s="8">
-        <v>671063</v>
+        <v>671082</v>
       </c>
       <c r="BE41" s="10">
         <f t="shared" si="21"/>
-        <v>0.93841315389090263</v>
+        <v>0.93843972345281246</v>
       </c>
       <c r="BF41" s="9">
         <v>910875</v>
@@ -7852,14 +7852,14 @@
       </c>
       <c r="BH41" s="9">
         <f t="shared" si="22"/>
-        <v>397977</v>
+        <v>398006</v>
       </c>
       <c r="BI41" s="6">
-        <v>867188</v>
+        <v>867217</v>
       </c>
       <c r="BJ41" s="10">
         <f t="shared" si="23"/>
-        <v>0.95203842459173871</v>
+        <v>0.95207026211060797</v>
       </c>
     </row>
     <row r="42" spans="1:63" x14ac:dyDescent="0.3">
@@ -7877,14 +7877,14 @@
       </c>
       <c r="E42" s="9">
         <f t="shared" si="0"/>
-        <v>3410</v>
+        <v>3411</v>
       </c>
       <c r="F42" s="8">
-        <v>12436</v>
+        <v>12437</v>
       </c>
       <c r="G42" s="10">
         <f t="shared" si="1"/>
-        <v>0.63316531744819515</v>
+        <v>0.63321623135278249</v>
       </c>
       <c r="H42" s="5">
         <v>18257</v>
@@ -7894,14 +7894,14 @@
       </c>
       <c r="J42" s="9">
         <f t="shared" si="2"/>
-        <v>4250</v>
+        <v>4251</v>
       </c>
       <c r="K42" s="8">
-        <v>12414</v>
+        <v>12415</v>
       </c>
       <c r="L42" s="10">
         <f t="shared" si="3"/>
-        <v>0.67995837213123733</v>
+        <v>0.68001314564276716</v>
       </c>
       <c r="M42" s="5">
         <v>19399</v>
@@ -7911,14 +7911,14 @@
       </c>
       <c r="O42" s="9">
         <f t="shared" si="4"/>
-        <v>8206</v>
+        <v>8207</v>
       </c>
       <c r="P42" s="8">
-        <v>17006</v>
+        <v>17007</v>
       </c>
       <c r="Q42" s="10">
         <f t="shared" si="5"/>
-        <v>0.87664312593432647</v>
+        <v>0.8766946749832466</v>
       </c>
       <c r="R42" s="5">
         <v>15746</v>
@@ -8581,14 +8581,14 @@
       </c>
       <c r="Y45" s="9">
         <f t="shared" si="8"/>
-        <v>128836</v>
+        <v>128837</v>
       </c>
       <c r="Z45" s="8">
-        <v>171553</v>
+        <v>171554</v>
       </c>
       <c r="AA45" s="10">
         <f t="shared" si="9"/>
-        <v>0.77912410814444089</v>
+        <v>0.77912864973863127</v>
       </c>
       <c r="AB45" s="5">
         <v>291802</v>
@@ -8615,14 +8615,14 @@
       </c>
       <c r="AI45" s="9">
         <f t="shared" si="12"/>
-        <v>119864</v>
+        <v>119865</v>
       </c>
       <c r="AJ45" s="8">
-        <v>174766</v>
+        <v>174767</v>
       </c>
       <c r="AK45" s="10">
         <f t="shared" si="13"/>
-        <v>0.8080655825631019</v>
+        <v>0.8080702062632642</v>
       </c>
       <c r="AL45" s="5">
         <v>214950</v>
@@ -8632,14 +8632,14 @@
       </c>
       <c r="AN45" s="9">
         <f t="shared" si="14"/>
-        <v>115741</v>
+        <v>115742</v>
       </c>
       <c r="AO45" s="8">
-        <v>176815</v>
+        <v>176816</v>
       </c>
       <c r="AP45" s="10">
         <f t="shared" si="15"/>
-        <v>0.82258664805768789</v>
+        <v>0.82259130030239591</v>
       </c>
       <c r="AQ45" s="22">
         <v>297340</v>
@@ -8700,14 +8700,14 @@
       </c>
       <c r="BH45" s="9">
         <f t="shared" si="22"/>
-        <v>145216</v>
+        <v>145218</v>
       </c>
       <c r="BI45" s="6">
-        <v>262770</v>
+        <v>262772</v>
       </c>
       <c r="BJ45" s="10">
         <f t="shared" si="23"/>
-        <v>0.90390913093731085</v>
+        <v>0.90391601078760531</v>
       </c>
     </row>
     <row r="46" spans="1:63" x14ac:dyDescent="0.3">
@@ -8878,14 +8878,14 @@
       </c>
       <c r="AX46" s="9">
         <f t="shared" si="18"/>
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="AY46" s="9">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="AZ46" s="10">
         <f t="shared" si="19"/>
-        <v>0.7623363544813696</v>
+        <v>0.76283987915407858</v>
       </c>
       <c r="BA46" s="22">
         <v>2072</v>
@@ -8895,14 +8895,14 @@
       </c>
       <c r="BC46" s="9">
         <f t="shared" si="20"/>
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="BD46" s="8">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="BE46" s="10">
         <f t="shared" si="21"/>
-        <v>0.82191119691119696</v>
+        <v>0.82239382239382242</v>
       </c>
       <c r="BF46" s="9">
         <v>4235</v>
@@ -8912,14 +8912,14 @@
       </c>
       <c r="BH46" s="9">
         <f t="shared" si="22"/>
-        <v>2711</v>
+        <v>2712</v>
       </c>
       <c r="BI46" s="6">
-        <v>3784</v>
+        <v>3785</v>
       </c>
       <c r="BJ46" s="10">
         <f t="shared" si="23"/>
-        <v>0.89350649350649347</v>
+        <v>0.89374262101534829</v>
       </c>
     </row>
     <row r="47" spans="1:63" x14ac:dyDescent="0.3">
@@ -9149,15 +9149,15 @@
       </c>
       <c r="E48" s="18">
         <f t="shared" si="0"/>
-        <v>1253701</v>
+        <v>1253742</v>
       </c>
       <c r="F48" s="20">
         <f>SUM(F10:F47)</f>
-        <v>3917858</v>
+        <v>3917899</v>
       </c>
       <c r="G48" s="19">
         <f t="shared" si="1"/>
-        <v>0.37682893212351282</v>
+        <v>0.37683287560135631</v>
       </c>
       <c r="H48" s="20">
         <f>SUM(H10:H47)</f>
@@ -9169,15 +9169,15 @@
       </c>
       <c r="J48" s="18">
         <f t="shared" si="2"/>
-        <v>1452529</v>
+        <v>1452574</v>
       </c>
       <c r="K48" s="20">
         <f>SUM(K10:K47)</f>
-        <v>3929305</v>
+        <v>3929350</v>
       </c>
       <c r="L48" s="19">
         <f t="shared" si="3"/>
-        <v>0.40921585892990392</v>
+        <v>0.40922054543646219</v>
       </c>
       <c r="M48" s="20">
         <f>SUM(M10:M47)</f>
@@ -9189,15 +9189,15 @@
       </c>
       <c r="O48" s="18">
         <f t="shared" si="4"/>
-        <v>5094041</v>
+        <v>5094140</v>
       </c>
       <c r="P48" s="20">
         <f>SUM(P10:P47)</f>
-        <v>9212360</v>
+        <v>9212459</v>
       </c>
       <c r="Q48" s="19">
         <f t="shared" si="5"/>
-        <v>0.88596579047766322</v>
+        <v>0.88597531144875619</v>
       </c>
       <c r="R48" s="20">
         <f>SUM(R10:R47)</f>
@@ -9209,15 +9209,15 @@
       </c>
       <c r="T48" s="18">
         <f t="shared" si="6"/>
-        <v>3084951</v>
+        <v>3085003</v>
       </c>
       <c r="U48" s="20">
         <f>SUM(U10:U47)</f>
-        <v>4004720</v>
+        <v>4004772</v>
       </c>
       <c r="V48" s="19">
         <f t="shared" si="7"/>
-        <v>0.6660895150512659</v>
+        <v>0.6660981640091912</v>
       </c>
       <c r="W48" s="20">
         <f>SUM(W10:W47)</f>
@@ -9229,15 +9229,15 @@
       </c>
       <c r="Y48" s="18">
         <f t="shared" si="8"/>
-        <v>2823338</v>
+        <v>2823396</v>
       </c>
       <c r="Z48" s="20">
         <f>SUM(Z10:Z47)</f>
-        <v>4036995</v>
+        <v>4037053</v>
       </c>
       <c r="AA48" s="19">
         <f t="shared" si="9"/>
-        <v>0.69476220585294424</v>
+        <v>0.69477218758637216</v>
       </c>
       <c r="AB48" s="20">
         <f>SUM(AB10:AB47)</f>
@@ -9249,15 +9249,15 @@
       </c>
       <c r="AD48" s="18">
         <f t="shared" si="10"/>
-        <v>3618164</v>
+        <v>3618285</v>
       </c>
       <c r="AE48" s="20">
         <f>SUM(AE10:AE47)</f>
-        <v>9489186</v>
+        <v>9489307</v>
       </c>
       <c r="AF48" s="19">
         <f t="shared" si="11"/>
-        <v>0.87449827232608668</v>
+        <v>0.87450942336590731</v>
       </c>
       <c r="AG48" s="20">
         <f>SUM(AG10:AG47)</f>
@@ -9269,15 +9269,15 @@
       </c>
       <c r="AI48" s="18">
         <f t="shared" si="12"/>
-        <v>2580094</v>
+        <v>2580153</v>
       </c>
       <c r="AJ48" s="20">
         <f>SUM(AJ10:AJ47)</f>
-        <v>4110326</v>
+        <v>4110385</v>
       </c>
       <c r="AK48" s="19">
         <f t="shared" si="13"/>
-        <v>0.75238061069423301</v>
+        <v>0.75239141043518565</v>
       </c>
       <c r="AL48" s="20">
         <f>SUM(AL10:AL47)</f>
@@ -9289,15 +9289,15 @@
       </c>
       <c r="AN48" s="18">
         <f t="shared" si="14"/>
-        <v>2523215</v>
+        <v>2523264</v>
       </c>
       <c r="AO48" s="20">
         <f>SUM(AO10:AO47)</f>
-        <v>4159085</v>
+        <v>4159134</v>
       </c>
       <c r="AP48" s="19">
         <f t="shared" si="15"/>
-        <v>0.777651402398984</v>
+        <v>0.7776605642503811</v>
       </c>
       <c r="AQ48" s="20">
         <f>SUM(AQ10:AQ47)</f>
@@ -9309,15 +9309,15 @@
       </c>
       <c r="AS48" s="18">
         <f t="shared" si="16"/>
-        <v>2270583</v>
+        <v>2270692</v>
       </c>
       <c r="AT48" s="20">
         <f>SUM(AT10:AT47)</f>
-        <v>9815655</v>
+        <v>9815764</v>
       </c>
       <c r="AU48" s="19">
         <f t="shared" si="17"/>
-        <v>0.89361469104662383</v>
+        <v>0.89362461437841612</v>
       </c>
       <c r="AV48" s="20">
         <f>SUM(AV10:AV47)</f>
@@ -9329,15 +9329,15 @@
       </c>
       <c r="AX48" s="18">
         <f t="shared" si="18"/>
-        <v>2882198</v>
+        <v>2882269</v>
       </c>
       <c r="AY48" s="20">
         <f>SUM(AY10:AY47)</f>
-        <v>5362471</v>
+        <v>5362542</v>
       </c>
       <c r="AZ48" s="19">
         <f t="shared" si="19"/>
-        <v>0.8562896310549386</v>
+        <v>0.85630096847080617</v>
       </c>
       <c r="BA48" s="20">
         <f>SUM(BA10:BA47)</f>
@@ -9349,15 +9349,15 @@
       </c>
       <c r="BC48" s="18">
         <f t="shared" si="20"/>
-        <v>2728123</v>
+        <v>2728186</v>
       </c>
       <c r="BD48" s="20">
         <f>SUM(BD10:BD47)</f>
-        <v>5477467</v>
+        <v>5477530</v>
       </c>
       <c r="BE48" s="19">
         <f t="shared" si="21"/>
-        <v>0.89257634364306637</v>
+        <v>0.89258660975870885</v>
       </c>
       <c r="BF48" s="20">
         <f>SUM(BF10:BF47)</f>
@@ -9369,15 +9369,15 @@
       </c>
       <c r="BH48" s="18">
         <f t="shared" si="22"/>
-        <v>4902422</v>
+        <v>4902517</v>
       </c>
       <c r="BI48" s="20">
         <f>SUM(BI10:BI47)</f>
-        <v>10081743</v>
+        <v>10081838</v>
       </c>
       <c r="BJ48" s="19">
         <f t="shared" si="23"/>
-        <v>0.93526280190986977</v>
+        <v>0.9352716148667346</v>
       </c>
       <c r="BK48"/>
     </row>

--- a/gstdatabase/GSTR-1-2020-2021.xlsx
+++ b/gstdatabase/GSTR-1-2020-2021.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Jun-26\GST Statistics Downloads 31st May 26\Downloads\GSTR 1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Jul-26\GST Statistics Downloads 31st Jul 26\Downloads\GSTR 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BDB9475-65A5-450F-9287-46556B71A78B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7E03F15-DD43-4373-9614-188DAFDFA14F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -182,10 +182,10 @@
     <t>Andaman and Nicobar Islands</t>
   </si>
   <si>
-    <t>Data Considered upto 30th Jun 2026</t>
+    <t>Data Considered upto 31st Jul 2026</t>
   </si>
   <si>
-    <t>Filing %age as on 30th Jun 2026</t>
+    <t>Filing %age as on 31st Jul 2026</t>
   </si>
 </sst>
 </file>
@@ -758,7 +758,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BK59"/>
+  <dimension ref="A1:BK57"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.44140625" customWidth="1"/>
@@ -1110,14 +1110,14 @@
       </c>
       <c r="E10" s="9">
         <f>F10-D10</f>
-        <v>14211</v>
+        <v>14212</v>
       </c>
       <c r="F10" s="8">
-        <v>27751</v>
+        <v>27752</v>
       </c>
       <c r="G10" s="10">
         <f>F10/C10</f>
-        <v>0.3336258716037509</v>
+        <v>0.33363789372445302</v>
       </c>
       <c r="H10" s="5">
         <v>76769</v>
@@ -1127,14 +1127,14 @@
       </c>
       <c r="J10" s="9">
         <f>K10-I10</f>
-        <v>15291</v>
+        <v>15292</v>
       </c>
       <c r="K10" s="8">
-        <v>27770</v>
+        <v>27771</v>
       </c>
       <c r="L10" s="10">
         <f>K10/H10</f>
-        <v>0.36173455431228752</v>
+        <v>0.36174758040354832</v>
       </c>
       <c r="M10" s="5">
         <v>83835</v>
@@ -1144,14 +1144,14 @@
       </c>
       <c r="O10" s="9">
         <f>P10-N10</f>
-        <v>53276</v>
+        <v>53277</v>
       </c>
       <c r="P10" s="8">
-        <v>73136</v>
+        <v>73137</v>
       </c>
       <c r="Q10" s="10">
         <f>P10/M10</f>
-        <v>0.87238027076996483</v>
+        <v>0.87239219896224729</v>
       </c>
       <c r="R10" s="5">
         <v>48665</v>
@@ -1161,14 +1161,14 @@
       </c>
       <c r="T10" s="9">
         <f>U10-S10</f>
-        <v>24615</v>
+        <v>24617</v>
       </c>
       <c r="U10" s="8">
-        <v>28379</v>
+        <v>28381</v>
       </c>
       <c r="V10" s="10">
         <f>U10/R10</f>
-        <v>0.58315010788040689</v>
+        <v>0.58319120517825951</v>
       </c>
       <c r="W10" s="5">
         <v>46482</v>
@@ -1178,14 +1178,14 @@
       </c>
       <c r="Y10" s="9">
         <f>Z10-X10</f>
-        <v>23495</v>
+        <v>23496</v>
       </c>
       <c r="Z10" s="8">
-        <v>28610</v>
+        <v>28611</v>
       </c>
       <c r="AA10" s="10">
         <f>Z10/W10</f>
-        <v>0.61550707800869153</v>
+        <v>0.61552859171292118</v>
       </c>
       <c r="AB10" s="5">
         <v>88382</v>
@@ -1195,14 +1195,14 @@
       </c>
       <c r="AD10" s="9">
         <f>AE10-AC10</f>
-        <v>41497</v>
+        <v>41498</v>
       </c>
       <c r="AE10" s="8">
-        <v>74583</v>
+        <v>74584</v>
       </c>
       <c r="AF10" s="10">
         <f>AE10/AB10</f>
-        <v>0.84387092394378949</v>
+        <v>0.84388223846484578</v>
       </c>
       <c r="AG10" s="5">
         <v>40367</v>
@@ -1212,14 +1212,14 @@
       </c>
       <c r="AI10" s="9">
         <f>AJ10-AH10</f>
-        <v>22878</v>
+        <v>22879</v>
       </c>
       <c r="AJ10" s="8">
-        <v>29167</v>
+        <v>29168</v>
       </c>
       <c r="AK10" s="10">
         <f>AJ10/AG10</f>
-        <v>0.7225456437188793</v>
+        <v>0.72257041642926156</v>
       </c>
       <c r="AL10" s="5">
         <v>37461</v>
@@ -1229,14 +1229,14 @@
       </c>
       <c r="AN10" s="9">
         <f>AO10-AM10</f>
-        <v>22125</v>
+        <v>22126</v>
       </c>
       <c r="AO10" s="8">
-        <v>29440</v>
+        <v>29441</v>
       </c>
       <c r="AP10" s="10">
         <f>AO10/AL10</f>
-        <v>0.78588398601211928</v>
+        <v>0.78591068044099199</v>
       </c>
       <c r="AQ10" s="22">
         <v>84627</v>
@@ -1246,14 +1246,14 @@
       </c>
       <c r="AS10" s="9">
         <f>AT10-AR10</f>
-        <v>27500</v>
+        <v>27501</v>
       </c>
       <c r="AT10" s="8">
-        <v>75887</v>
+        <v>75888</v>
       </c>
       <c r="AU10" s="10">
         <f>AT10/AQ10</f>
-        <v>0.89672326798775803</v>
+        <v>0.89673508454748485</v>
       </c>
       <c r="AV10" s="22">
         <v>45594</v>
@@ -1263,14 +1263,14 @@
       </c>
       <c r="AX10" s="9">
         <f>AY10-AW10</f>
-        <v>27130</v>
+        <v>27131</v>
       </c>
       <c r="AY10" s="9">
-        <v>39603</v>
+        <v>39604</v>
       </c>
       <c r="AZ10" s="10">
         <f>AY10/AV10</f>
-        <v>0.86860113172785891</v>
+        <v>0.86862306443830328</v>
       </c>
       <c r="BA10" s="22">
         <v>44931</v>
@@ -1280,14 +1280,14 @@
       </c>
       <c r="BC10" s="9">
         <f>BD10-BB10</f>
-        <v>26088</v>
+        <v>26089</v>
       </c>
       <c r="BD10" s="8">
-        <v>40406</v>
+        <v>40407</v>
       </c>
       <c r="BE10" s="10">
         <f>BD10/BA10</f>
-        <v>0.8992900224789121</v>
+        <v>0.89931227882753551</v>
       </c>
       <c r="BF10" s="9">
         <v>84140</v>
@@ -1297,14 +1297,14 @@
       </c>
       <c r="BH10" s="9">
         <f>BI10-BG10</f>
-        <v>48792</v>
+        <v>48794</v>
       </c>
       <c r="BI10" s="6">
-        <v>78615</v>
+        <v>78617</v>
       </c>
       <c r="BJ10" s="10">
         <f>BI10/BF10</f>
-        <v>0.93433563109103879</v>
+        <v>0.93435940099833614</v>
       </c>
     </row>
     <row r="11" spans="1:62" x14ac:dyDescent="0.3">
@@ -1568,14 +1568,14 @@
       </c>
       <c r="O12" s="9">
         <f t="shared" si="4"/>
-        <v>124077</v>
+        <v>124079</v>
       </c>
       <c r="P12" s="8">
-        <v>286591</v>
+        <v>286593</v>
       </c>
       <c r="Q12" s="10">
         <f t="shared" si="5"/>
-        <v>0.91628193979077677</v>
+        <v>0.9162883341432847</v>
       </c>
       <c r="R12" s="5">
         <v>125200</v>
@@ -1619,14 +1619,14 @@
       </c>
       <c r="AD12" s="9">
         <f t="shared" si="10"/>
-        <v>87172</v>
+        <v>87173</v>
       </c>
       <c r="AE12" s="8">
-        <v>293220</v>
+        <v>293221</v>
       </c>
       <c r="AF12" s="10">
         <f t="shared" si="11"/>
-        <v>0.9193895820072806</v>
+        <v>0.9193927175013874</v>
       </c>
       <c r="AG12" s="5">
         <v>113974</v>
@@ -1670,14 +1670,14 @@
       </c>
       <c r="AS12" s="9">
         <f t="shared" si="16"/>
-        <v>38426</v>
+        <v>38427</v>
       </c>
       <c r="AT12" s="8">
-        <v>299680</v>
+        <v>299681</v>
       </c>
       <c r="AU12" s="10">
         <f t="shared" si="17"/>
-        <v>0.92622469479214964</v>
+        <v>0.92622778550455875</v>
       </c>
       <c r="AV12" s="22">
         <v>144846</v>
@@ -1687,14 +1687,14 @@
       </c>
       <c r="AX12" s="9">
         <f t="shared" si="18"/>
-        <v>44872</v>
+        <v>44873</v>
       </c>
       <c r="AY12" s="9">
-        <v>126338</v>
+        <v>126339</v>
       </c>
       <c r="AZ12" s="10">
         <f t="shared" si="19"/>
-        <v>0.87222291261063478</v>
+        <v>0.87222981649475995</v>
       </c>
       <c r="BA12" s="22">
         <v>144289</v>
@@ -1704,14 +1704,14 @@
       </c>
       <c r="BC12" s="9">
         <f t="shared" si="20"/>
-        <v>40164</v>
+        <v>40165</v>
       </c>
       <c r="BD12" s="8">
-        <v>129017</v>
+        <v>129018</v>
       </c>
       <c r="BE12" s="10">
         <f t="shared" si="21"/>
-        <v>0.89415686573474074</v>
+        <v>0.89416379626998588</v>
       </c>
       <c r="BF12" s="9">
         <v>318519</v>
@@ -1958,14 +1958,14 @@
       </c>
       <c r="E14" s="9">
         <f t="shared" si="0"/>
-        <v>11303</v>
+        <v>11306</v>
       </c>
       <c r="F14" s="8">
-        <v>34688</v>
+        <v>34691</v>
       </c>
       <c r="G14" s="10">
         <f t="shared" si="1"/>
-        <v>0.26453138107221841</v>
+        <v>0.26455425913215891</v>
       </c>
       <c r="H14" s="5">
         <v>113453</v>
@@ -1975,14 +1975,14 @@
       </c>
       <c r="J14" s="9">
         <f t="shared" si="2"/>
-        <v>13246</v>
+        <v>13248</v>
       </c>
       <c r="K14" s="8">
-        <v>34875</v>
+        <v>34877</v>
       </c>
       <c r="L14" s="10">
         <f t="shared" si="3"/>
-        <v>0.30739601420852686</v>
+        <v>0.30741364265378612</v>
       </c>
       <c r="M14" s="5">
         <v>130093</v>
@@ -1992,14 +1992,14 @@
       </c>
       <c r="O14" s="9">
         <f t="shared" si="4"/>
-        <v>66717</v>
+        <v>66720</v>
       </c>
       <c r="P14" s="8">
-        <v>115530</v>
+        <v>115533</v>
       </c>
       <c r="Q14" s="10">
         <f t="shared" si="5"/>
-        <v>0.8880570053730793</v>
+        <v>0.88808006579908216</v>
       </c>
       <c r="R14" s="5">
         <v>63308</v>
@@ -2009,14 +2009,14 @@
       </c>
       <c r="T14" s="9">
         <f t="shared" si="6"/>
-        <v>27583</v>
+        <v>27586</v>
       </c>
       <c r="U14" s="8">
-        <v>35696</v>
+        <v>35699</v>
       </c>
       <c r="V14" s="10">
         <f t="shared" si="7"/>
-        <v>0.56384659126808623</v>
+        <v>0.56389397864408919</v>
       </c>
       <c r="W14" s="5">
         <v>61226</v>
@@ -2026,14 +2026,14 @@
       </c>
       <c r="Y14" s="9">
         <f t="shared" si="8"/>
-        <v>25504</v>
+        <v>25506</v>
       </c>
       <c r="Z14" s="8">
-        <v>36046</v>
+        <v>36048</v>
       </c>
       <c r="AA14" s="10">
         <f t="shared" si="9"/>
-        <v>0.58873681115865806</v>
+        <v>0.58876947701956683</v>
       </c>
       <c r="AB14" s="5">
         <v>138271</v>
@@ -2043,14 +2043,14 @@
       </c>
       <c r="AD14" s="9">
         <f t="shared" si="10"/>
-        <v>53073</v>
+        <v>53076</v>
       </c>
       <c r="AE14" s="8">
-        <v>120154</v>
+        <v>120157</v>
       </c>
       <c r="AF14" s="10">
         <f t="shared" si="11"/>
-        <v>0.86897469462143184</v>
+        <v>0.86899639114492555</v>
       </c>
       <c r="AG14" s="5">
         <v>55999</v>
@@ -2060,14 +2060,14 @@
       </c>
       <c r="AI14" s="9">
         <f t="shared" si="12"/>
-        <v>24998</v>
+        <v>25001</v>
       </c>
       <c r="AJ14" s="8">
-        <v>37048</v>
+        <v>37051</v>
       </c>
       <c r="AK14" s="10">
         <f t="shared" si="13"/>
-        <v>0.6615832425579028</v>
+        <v>0.66163681494312399</v>
       </c>
       <c r="AL14" s="5">
         <v>53588</v>
@@ -2077,14 +2077,14 @@
       </c>
       <c r="AN14" s="9">
         <f t="shared" si="14"/>
-        <v>24300</v>
+        <v>24303</v>
       </c>
       <c r="AO14" s="8">
-        <v>37515</v>
+        <v>37518</v>
       </c>
       <c r="AP14" s="10">
         <f t="shared" si="15"/>
-        <v>0.70006344704038215</v>
+        <v>0.70011942972307228</v>
       </c>
       <c r="AQ14" s="22">
         <v>140248</v>
@@ -2094,14 +2094,14 @@
       </c>
       <c r="AS14" s="9">
         <f t="shared" si="16"/>
-        <v>35437</v>
+        <v>35442</v>
       </c>
       <c r="AT14" s="8">
-        <v>125131</v>
+        <v>125136</v>
       </c>
       <c r="AU14" s="10">
         <f t="shared" si="17"/>
-        <v>0.89221236666476522</v>
+        <v>0.89224801779704521</v>
       </c>
       <c r="AV14" s="22">
         <v>71286</v>
@@ -2111,14 +2111,14 @@
       </c>
       <c r="AX14" s="9">
         <f t="shared" si="18"/>
-        <v>35675</v>
+        <v>35681</v>
       </c>
       <c r="AY14" s="9">
-        <v>59682</v>
+        <v>59688</v>
       </c>
       <c r="AZ14" s="10">
         <f t="shared" si="19"/>
-        <v>0.83721908930224731</v>
+        <v>0.83730325730157396</v>
       </c>
       <c r="BA14" s="22">
         <v>69175</v>
@@ -2128,14 +2128,14 @@
       </c>
       <c r="BC14" s="9">
         <f t="shared" si="20"/>
-        <v>34349</v>
+        <v>34354</v>
       </c>
       <c r="BD14" s="8">
-        <v>61426</v>
+        <v>61431</v>
       </c>
       <c r="BE14" s="10">
         <f t="shared" si="21"/>
-        <v>0.88797976147452118</v>
+        <v>0.88805204192265996</v>
       </c>
       <c r="BF14" s="9">
         <v>138667</v>
@@ -2145,14 +2145,14 @@
       </c>
       <c r="BH14" s="9">
         <f t="shared" si="22"/>
-        <v>70015</v>
+        <v>70023</v>
       </c>
       <c r="BI14" s="6">
-        <v>129523</v>
+        <v>129531</v>
       </c>
       <c r="BJ14" s="10">
         <f t="shared" si="23"/>
-        <v>0.93405785082247395</v>
+        <v>0.93411554299148314</v>
       </c>
     </row>
     <row r="15" spans="1:62" x14ac:dyDescent="0.3">
@@ -2170,14 +2170,14 @@
       </c>
       <c r="E15" s="9">
         <f t="shared" si="0"/>
-        <v>31562</v>
+        <v>31563</v>
       </c>
       <c r="F15" s="8">
-        <v>137789</v>
+        <v>137790</v>
       </c>
       <c r="G15" s="10">
         <f t="shared" si="1"/>
-        <v>0.32612240743940335</v>
+        <v>0.32612477426409503</v>
       </c>
       <c r="H15" s="5">
         <v>384273</v>
@@ -2187,14 +2187,14 @@
       </c>
       <c r="J15" s="9">
         <f t="shared" si="2"/>
-        <v>38312</v>
+        <v>38313</v>
       </c>
       <c r="K15" s="8">
-        <v>138263</v>
+        <v>138264</v>
       </c>
       <c r="L15" s="10">
         <f t="shared" si="3"/>
-        <v>0.35980409760769039</v>
+        <v>0.35980669992427261</v>
       </c>
       <c r="M15" s="5">
         <v>424733</v>
@@ -2382,14 +2382,14 @@
       </c>
       <c r="E16" s="9">
         <f t="shared" si="0"/>
-        <v>60757</v>
+        <v>60758</v>
       </c>
       <c r="F16" s="8">
-        <v>204019</v>
+        <v>204020</v>
       </c>
       <c r="G16" s="10">
         <f t="shared" si="1"/>
-        <v>0.27232888926857135</v>
+        <v>0.27233022408978541</v>
       </c>
       <c r="H16" s="5">
         <v>684312</v>
@@ -2399,14 +2399,14 @@
       </c>
       <c r="J16" s="9">
         <f t="shared" si="2"/>
-        <v>71834</v>
+        <v>71835</v>
       </c>
       <c r="K16" s="8">
-        <v>203977</v>
+        <v>203978</v>
       </c>
       <c r="L16" s="10">
         <f t="shared" si="3"/>
-        <v>0.29807602380200843</v>
+        <v>0.29807748512374471</v>
       </c>
       <c r="M16" s="5">
         <v>735720</v>
@@ -2416,14 +2416,14 @@
       </c>
       <c r="O16" s="9">
         <f t="shared" si="4"/>
-        <v>326402</v>
+        <v>326403</v>
       </c>
       <c r="P16" s="8">
-        <v>630727</v>
+        <v>630728</v>
       </c>
       <c r="Q16" s="10">
         <f t="shared" si="5"/>
-        <v>0.85729217637144561</v>
+        <v>0.85729353558418964</v>
       </c>
       <c r="R16" s="5">
         <v>377107</v>
@@ -2433,14 +2433,14 @@
       </c>
       <c r="T16" s="9">
         <f t="shared" si="6"/>
-        <v>145098</v>
+        <v>145099</v>
       </c>
       <c r="U16" s="8">
-        <v>208421</v>
+        <v>208422</v>
       </c>
       <c r="V16" s="10">
         <f t="shared" si="7"/>
-        <v>0.55268398624263138</v>
+        <v>0.5526866380099017</v>
       </c>
       <c r="W16" s="5">
         <v>358920</v>
@@ -2450,14 +2450,14 @@
       </c>
       <c r="Y16" s="9">
         <f t="shared" si="8"/>
-        <v>131039</v>
+        <v>131040</v>
       </c>
       <c r="Z16" s="8">
-        <v>210724</v>
+        <v>210725</v>
       </c>
       <c r="AA16" s="10">
         <f t="shared" si="9"/>
-        <v>0.58710576172963336</v>
+        <v>0.58710854786581967</v>
       </c>
       <c r="AB16" s="5">
         <v>764172</v>
@@ -2484,14 +2484,14 @@
       </c>
       <c r="AI16" s="9">
         <f t="shared" si="12"/>
-        <v>121827</v>
+        <v>121829</v>
       </c>
       <c r="AJ16" s="8">
-        <v>214303</v>
+        <v>214305</v>
       </c>
       <c r="AK16" s="10">
         <f t="shared" si="13"/>
-        <v>0.64309485441292535</v>
+        <v>0.64310085614742662</v>
       </c>
       <c r="AL16" s="5">
         <v>323065</v>
@@ -2501,14 +2501,14 @@
       </c>
       <c r="AN16" s="9">
         <f t="shared" si="14"/>
-        <v>116995</v>
+        <v>116997</v>
       </c>
       <c r="AO16" s="8">
-        <v>217708</v>
+        <v>217710</v>
       </c>
       <c r="AP16" s="10">
         <f t="shared" si="15"/>
-        <v>0.67388296472846021</v>
+        <v>0.67388915543311723</v>
       </c>
       <c r="AQ16" s="22">
         <v>767321</v>
@@ -2552,14 +2552,14 @@
       </c>
       <c r="BC16" s="9">
         <f t="shared" si="20"/>
-        <v>130509</v>
+        <v>130510</v>
       </c>
       <c r="BD16" s="8">
-        <v>312755</v>
+        <v>312756</v>
       </c>
       <c r="BE16" s="10">
         <f t="shared" si="21"/>
-        <v>0.8631033692919492</v>
+        <v>0.86310612897083294</v>
       </c>
       <c r="BF16" s="9">
         <v>717401</v>
@@ -2628,14 +2628,14 @@
       </c>
       <c r="O17" s="9">
         <f t="shared" si="4"/>
-        <v>259027</v>
+        <v>259034</v>
       </c>
       <c r="P17" s="8">
-        <v>514374</v>
+        <v>514381</v>
       </c>
       <c r="Q17" s="10">
         <f t="shared" si="5"/>
-        <v>0.92369107221100877</v>
+        <v>0.92370364251492276</v>
       </c>
       <c r="R17" s="5">
         <v>233458</v>
@@ -2679,14 +2679,14 @@
       </c>
       <c r="AD17" s="9">
         <f t="shared" si="10"/>
-        <v>196954</v>
+        <v>196958</v>
       </c>
       <c r="AE17" s="8">
-        <v>535863</v>
+        <v>535867</v>
       </c>
       <c r="AF17" s="10">
         <f t="shared" si="11"/>
-        <v>0.92064454722258493</v>
+        <v>0.9206514194608042</v>
       </c>
       <c r="AG17" s="5">
         <v>198905</v>
@@ -2730,14 +2730,14 @@
       </c>
       <c r="AS17" s="9">
         <f t="shared" si="16"/>
-        <v>115080</v>
+        <v>115086</v>
       </c>
       <c r="AT17" s="8">
-        <v>556259</v>
+        <v>556265</v>
       </c>
       <c r="AU17" s="10">
         <f t="shared" si="17"/>
-        <v>0.93493621527135817</v>
+        <v>0.93494629981343602</v>
       </c>
       <c r="AV17" s="22">
         <v>254447</v>
@@ -2747,14 +2747,14 @@
       </c>
       <c r="AX17" s="9">
         <f t="shared" si="18"/>
-        <v>115488</v>
+        <v>115494</v>
       </c>
       <c r="AY17" s="9">
-        <v>224987</v>
+        <v>224993</v>
       </c>
       <c r="AZ17" s="10">
         <f t="shared" si="19"/>
-        <v>0.88421950347223588</v>
+        <v>0.88424308402142682</v>
       </c>
       <c r="BA17" s="22">
         <v>254024</v>
@@ -2764,14 +2764,14 @@
       </c>
       <c r="BC17" s="9">
         <f t="shared" si="20"/>
-        <v>106327</v>
+        <v>106333</v>
       </c>
       <c r="BD17" s="8">
-        <v>234306</v>
+        <v>234312</v>
       </c>
       <c r="BE17" s="10">
         <f t="shared" si="21"/>
-        <v>0.92237741315781185</v>
+        <v>0.92240103297326237</v>
       </c>
       <c r="BF17" s="9">
         <v>590776</v>
@@ -2781,14 +2781,14 @@
       </c>
       <c r="BH17" s="9">
         <f t="shared" si="22"/>
-        <v>261177</v>
+        <v>261182</v>
       </c>
       <c r="BI17" s="6">
-        <v>572585</v>
+        <v>572590</v>
       </c>
       <c r="BJ17" s="10">
         <f t="shared" si="23"/>
-        <v>0.96920829552994703</v>
+        <v>0.96921675897463677</v>
       </c>
     </row>
     <row r="18" spans="1:62" x14ac:dyDescent="0.3">
@@ -2806,14 +2806,14 @@
       </c>
       <c r="E18" s="9">
         <f t="shared" si="0"/>
-        <v>117501</v>
+        <v>117505</v>
       </c>
       <c r="F18" s="8">
-        <v>332221</v>
+        <v>332225</v>
       </c>
       <c r="G18" s="10">
         <f t="shared" si="1"/>
-        <v>0.28891696901600511</v>
+        <v>0.2889204476277607</v>
       </c>
       <c r="H18" s="5">
         <v>1037981</v>
@@ -2823,14 +2823,14 @@
       </c>
       <c r="J18" s="9">
         <f t="shared" si="2"/>
-        <v>131828</v>
+        <v>131831</v>
       </c>
       <c r="K18" s="8">
-        <v>332137</v>
+        <v>332140</v>
       </c>
       <c r="L18" s="10">
         <f t="shared" si="3"/>
-        <v>0.31998369912358704</v>
+        <v>0.31998658934990137</v>
       </c>
       <c r="M18" s="5">
         <v>1134575</v>
@@ -2840,14 +2840,14 @@
       </c>
       <c r="O18" s="9">
         <f t="shared" si="4"/>
-        <v>604410</v>
+        <v>604415</v>
       </c>
       <c r="P18" s="8">
-        <v>1000756</v>
+        <v>1000761</v>
       </c>
       <c r="Q18" s="10">
         <f t="shared" si="5"/>
-        <v>0.88205363241742507</v>
+        <v>0.88205803935394311</v>
       </c>
       <c r="R18" s="5">
         <v>560923</v>
@@ -2857,14 +2857,14 @@
       </c>
       <c r="T18" s="9">
         <f t="shared" si="6"/>
-        <v>280945</v>
+        <v>280948</v>
       </c>
       <c r="U18" s="8">
-        <v>340408</v>
+        <v>340411</v>
       </c>
       <c r="V18" s="10">
         <f t="shared" si="7"/>
-        <v>0.60687117483148312</v>
+        <v>0.60687652315915019</v>
       </c>
       <c r="W18" s="5">
         <v>535952</v>
@@ -2874,14 +2874,14 @@
       </c>
       <c r="Y18" s="9">
         <f t="shared" si="8"/>
-        <v>262474</v>
+        <v>262479</v>
       </c>
       <c r="Z18" s="8">
-        <v>344127</v>
+        <v>344132</v>
       </c>
       <c r="AA18" s="10">
         <f t="shared" si="9"/>
-        <v>0.64208548526733733</v>
+        <v>0.64209481446099648</v>
       </c>
       <c r="AB18" s="5">
         <v>1210642</v>
@@ -2891,14 +2891,14 @@
       </c>
       <c r="AD18" s="9">
         <f t="shared" si="10"/>
-        <v>486262</v>
+        <v>486265</v>
       </c>
       <c r="AE18" s="8">
-        <v>1048114</v>
+        <v>1048117</v>
       </c>
       <c r="AF18" s="10">
         <f t="shared" si="11"/>
-        <v>0.86575056870652101</v>
+        <v>0.86575304673057762</v>
       </c>
       <c r="AG18" s="5">
         <v>495943</v>
@@ -2908,14 +2908,14 @@
       </c>
       <c r="AI18" s="9">
         <f t="shared" si="12"/>
-        <v>257045</v>
+        <v>257048</v>
       </c>
       <c r="AJ18" s="8">
-        <v>353150</v>
+        <v>353153</v>
       </c>
       <c r="AK18" s="10">
         <f t="shared" si="13"/>
-        <v>0.71207779926322179</v>
+        <v>0.71208384834547522</v>
       </c>
       <c r="AL18" s="5">
         <v>477702</v>
@@ -2925,14 +2925,14 @@
       </c>
       <c r="AN18" s="9">
         <f t="shared" si="14"/>
-        <v>255789</v>
+        <v>255793</v>
       </c>
       <c r="AO18" s="8">
-        <v>358370</v>
+        <v>358374</v>
       </c>
       <c r="AP18" s="10">
         <f t="shared" si="15"/>
-        <v>0.75019572871790363</v>
+        <v>0.75020410213899047</v>
       </c>
       <c r="AQ18" s="22">
         <v>1231355</v>
@@ -2942,14 +2942,14 @@
       </c>
       <c r="AS18" s="9">
         <f t="shared" si="16"/>
-        <v>296465</v>
+        <v>296470</v>
       </c>
       <c r="AT18" s="8">
-        <v>1092325</v>
+        <v>1092330</v>
       </c>
       <c r="AU18" s="10">
         <f t="shared" si="17"/>
-        <v>0.88709186221682623</v>
+        <v>0.88709592278424987</v>
       </c>
       <c r="AV18" s="22">
         <v>676361</v>
@@ -2959,14 +2959,14 @@
       </c>
       <c r="AX18" s="9">
         <f t="shared" si="18"/>
-        <v>330637</v>
+        <v>330640</v>
       </c>
       <c r="AY18" s="9">
-        <v>573211</v>
+        <v>573214</v>
       </c>
       <c r="AZ18" s="10">
         <f t="shared" si="19"/>
-        <v>0.84749268511933717</v>
+        <v>0.84749712062049709</v>
       </c>
       <c r="BA18" s="22">
         <v>652080</v>
@@ -2976,14 +2976,14 @@
       </c>
       <c r="BC18" s="9">
         <f t="shared" si="20"/>
-        <v>316144</v>
+        <v>316147</v>
       </c>
       <c r="BD18" s="8">
-        <v>587355</v>
+        <v>587358</v>
       </c>
       <c r="BE18" s="10">
         <f t="shared" si="21"/>
-        <v>0.90074070666175932</v>
+        <v>0.90074530732425473</v>
       </c>
       <c r="BF18" s="9">
         <v>1203078</v>
@@ -2993,14 +2993,14 @@
       </c>
       <c r="BH18" s="9">
         <f t="shared" si="22"/>
-        <v>595070</v>
+        <v>595077</v>
       </c>
       <c r="BI18" s="6">
-        <v>1125693</v>
+        <v>1125700</v>
       </c>
       <c r="BJ18" s="10">
         <f t="shared" si="23"/>
-        <v>0.93567748724521604</v>
+        <v>0.93568330565433</v>
       </c>
     </row>
     <row r="19" spans="1:62" x14ac:dyDescent="0.3">
@@ -3052,14 +3052,14 @@
       </c>
       <c r="O19" s="9">
         <f t="shared" si="4"/>
-        <v>210399</v>
+        <v>210400</v>
       </c>
       <c r="P19" s="8">
-        <v>278112</v>
+        <v>278113</v>
       </c>
       <c r="Q19" s="10">
         <f t="shared" si="5"/>
-        <v>0.85102893251120737</v>
+        <v>0.85103199253354544</v>
       </c>
       <c r="R19" s="5">
         <v>182406</v>
@@ -3069,14 +3069,14 @@
       </c>
       <c r="T19" s="9">
         <f t="shared" si="6"/>
-        <v>85575</v>
+        <v>85576</v>
       </c>
       <c r="U19" s="8">
-        <v>95493</v>
+        <v>95494</v>
       </c>
       <c r="V19" s="10">
         <f t="shared" si="7"/>
-        <v>0.52351896319200031</v>
+        <v>0.52352444546780263</v>
       </c>
       <c r="W19" s="5">
         <v>174793</v>
@@ -3086,14 +3086,14 @@
       </c>
       <c r="Y19" s="9">
         <f t="shared" si="8"/>
-        <v>83341</v>
+        <v>83342</v>
       </c>
       <c r="Z19" s="8">
-        <v>96684</v>
+        <v>96685</v>
       </c>
       <c r="AA19" s="10">
         <f t="shared" si="9"/>
-        <v>0.55313427883267641</v>
+        <v>0.55313999988557894</v>
       </c>
       <c r="AB19" s="5">
         <v>355383</v>
@@ -3103,14 +3103,14 @@
       </c>
       <c r="AD19" s="9">
         <f t="shared" si="10"/>
-        <v>164273</v>
+        <v>164276</v>
       </c>
       <c r="AE19" s="8">
-        <v>291745</v>
+        <v>291748</v>
       </c>
       <c r="AF19" s="10">
         <f t="shared" si="11"/>
-        <v>0.8209312206830377</v>
+        <v>0.82093966227985016</v>
       </c>
       <c r="AG19" s="5">
         <v>163328</v>
@@ -3120,14 +3120,14 @@
       </c>
       <c r="AI19" s="9">
         <f t="shared" si="12"/>
-        <v>81718</v>
+        <v>81719</v>
       </c>
       <c r="AJ19" s="8">
-        <v>99296</v>
+        <v>99297</v>
       </c>
       <c r="AK19" s="10">
         <f t="shared" si="13"/>
-        <v>0.60795454545454541</v>
+        <v>0.60796066810344829</v>
       </c>
       <c r="AL19" s="5">
         <v>160483</v>
@@ -3137,14 +3137,14 @@
       </c>
       <c r="AN19" s="9">
         <f t="shared" si="14"/>
-        <v>83152</v>
+        <v>83154</v>
       </c>
       <c r="AO19" s="8">
-        <v>100623</v>
+        <v>100625</v>
       </c>
       <c r="AP19" s="10">
         <f t="shared" si="15"/>
-        <v>0.62700099075914584</v>
+        <v>0.62701345313833867</v>
       </c>
       <c r="AQ19" s="22">
         <v>372999</v>
@@ -3154,14 +3154,14 @@
       </c>
       <c r="AS19" s="9">
         <f t="shared" si="16"/>
-        <v>120088</v>
+        <v>120091</v>
       </c>
       <c r="AT19" s="8">
-        <v>306824</v>
+        <v>306827</v>
       </c>
       <c r="AU19" s="10">
         <f t="shared" si="17"/>
-        <v>0.82258665572829959</v>
+        <v>0.82259469864530466</v>
       </c>
       <c r="AV19" s="22">
         <v>223136</v>
@@ -3171,14 +3171,14 @@
       </c>
       <c r="AX19" s="9">
         <f t="shared" si="18"/>
-        <v>120772</v>
+        <v>120775</v>
       </c>
       <c r="AY19" s="9">
-        <v>165129</v>
+        <v>165132</v>
       </c>
       <c r="AZ19" s="10">
         <f t="shared" si="19"/>
-        <v>0.74003746594005448</v>
+        <v>0.74005091065538509</v>
       </c>
       <c r="BA19" s="22">
         <v>218799</v>
@@ -3188,14 +3188,14 @@
       </c>
       <c r="BC19" s="9">
         <f t="shared" si="20"/>
-        <v>118608</v>
+        <v>118610</v>
       </c>
       <c r="BD19" s="8">
-        <v>171499</v>
+        <v>171501</v>
       </c>
       <c r="BE19" s="10">
         <f t="shared" si="21"/>
-        <v>0.78381985292437351</v>
+        <v>0.78382899373397497</v>
       </c>
       <c r="BF19" s="9">
         <v>376756</v>
@@ -3205,14 +3205,14 @@
       </c>
       <c r="BH19" s="9">
         <f t="shared" si="22"/>
-        <v>222001</v>
+        <v>222004</v>
       </c>
       <c r="BI19" s="6">
-        <v>323355</v>
+        <v>323358</v>
       </c>
       <c r="BJ19" s="10">
         <f t="shared" si="23"/>
-        <v>0.85826104959177818</v>
+        <v>0.85826901230504626</v>
       </c>
     </row>
     <row r="20" spans="1:62" x14ac:dyDescent="0.3">
@@ -3264,14 +3264,14 @@
       </c>
       <c r="O20" s="9">
         <f t="shared" si="4"/>
-        <v>3843</v>
+        <v>3844</v>
       </c>
       <c r="P20" s="8">
-        <v>6374</v>
+        <v>6375</v>
       </c>
       <c r="Q20" s="10">
         <f t="shared" si="5"/>
-        <v>0.84156324267229998</v>
+        <v>0.84169527330340643</v>
       </c>
       <c r="R20" s="5">
         <v>4791</v>
@@ -3315,14 +3315,14 @@
       </c>
       <c r="AD20" s="9">
         <f t="shared" si="10"/>
-        <v>2703</v>
+        <v>2704</v>
       </c>
       <c r="AE20" s="8">
-        <v>6411</v>
+        <v>6412</v>
       </c>
       <c r="AF20" s="10">
         <f t="shared" si="11"/>
-        <v>0.8319491305476252</v>
+        <v>0.83207889955878533</v>
       </c>
       <c r="AG20" s="5">
         <v>4195</v>
@@ -3442,14 +3442,14 @@
       </c>
       <c r="E21" s="9">
         <f t="shared" si="0"/>
-        <v>2152</v>
+        <v>2153</v>
       </c>
       <c r="F21" s="8">
-        <v>3861</v>
+        <v>3862</v>
       </c>
       <c r="G21" s="10">
         <f t="shared" si="1"/>
-        <v>0.31089459698848537</v>
+        <v>0.31097511876962719</v>
       </c>
       <c r="H21" s="5">
         <v>10801</v>
@@ -3459,14 +3459,14 @@
       </c>
       <c r="J21" s="9">
         <f t="shared" si="2"/>
-        <v>2327</v>
+        <v>2328</v>
       </c>
       <c r="K21" s="8">
-        <v>3820</v>
+        <v>3821</v>
       </c>
       <c r="L21" s="10">
         <f t="shared" si="3"/>
-        <v>0.35367095639292656</v>
+        <v>0.35376354041292474</v>
       </c>
       <c r="M21" s="5">
         <v>12071</v>
@@ -3476,14 +3476,14 @@
       </c>
       <c r="O21" s="9">
         <f t="shared" si="4"/>
-        <v>6468</v>
+        <v>6470</v>
       </c>
       <c r="P21" s="8">
-        <v>8745</v>
+        <v>8747</v>
       </c>
       <c r="Q21" s="10">
         <f t="shared" si="5"/>
-        <v>0.72446359042332864</v>
+        <v>0.7246292767790572</v>
       </c>
       <c r="R21" s="5">
         <v>8791</v>
@@ -3493,14 +3493,14 @@
       </c>
       <c r="T21" s="9">
         <f t="shared" si="6"/>
-        <v>3391</v>
+        <v>3392</v>
       </c>
       <c r="U21" s="8">
-        <v>3858</v>
+        <v>3859</v>
       </c>
       <c r="V21" s="10">
         <f t="shared" si="7"/>
-        <v>0.43885792287566827</v>
+        <v>0.43897167557729494</v>
       </c>
       <c r="W21" s="5">
         <v>8479</v>
@@ -3510,14 +3510,14 @@
       </c>
       <c r="Y21" s="9">
         <f t="shared" si="8"/>
-        <v>3196</v>
+        <v>3197</v>
       </c>
       <c r="Z21" s="8">
-        <v>3920</v>
+        <v>3921</v>
       </c>
       <c r="AA21" s="10">
         <f t="shared" si="9"/>
-        <v>0.46231866965444041</v>
+        <v>0.46243660809057674</v>
       </c>
       <c r="AB21" s="5">
         <v>12614</v>
@@ -3527,14 +3527,14 @@
       </c>
       <c r="AD21" s="9">
         <f t="shared" si="10"/>
-        <v>5217</v>
+        <v>5218</v>
       </c>
       <c r="AE21" s="8">
-        <v>8998</v>
+        <v>8999</v>
       </c>
       <c r="AF21" s="10">
         <f t="shared" si="11"/>
-        <v>0.71333439035991753</v>
+        <v>0.7134136673537339</v>
       </c>
       <c r="AG21" s="5">
         <v>7886</v>
@@ -3544,14 +3544,14 @@
       </c>
       <c r="AI21" s="9">
         <f t="shared" si="12"/>
-        <v>3132</v>
+        <v>3134</v>
       </c>
       <c r="AJ21" s="8">
-        <v>4024</v>
+        <v>4026</v>
       </c>
       <c r="AK21" s="10">
         <f t="shared" si="13"/>
-        <v>0.5102713669794573</v>
+        <v>0.51052498097895005</v>
       </c>
       <c r="AL21" s="5">
         <v>7852</v>
@@ -3561,14 +3561,14 @@
       </c>
       <c r="AN21" s="9">
         <f t="shared" si="14"/>
-        <v>3182</v>
+        <v>3184</v>
       </c>
       <c r="AO21" s="8">
-        <v>4087</v>
+        <v>4089</v>
       </c>
       <c r="AP21" s="10">
         <f t="shared" si="15"/>
-        <v>0.52050433010697916</v>
+        <v>0.52075904228222114</v>
       </c>
       <c r="AQ21" s="22">
         <v>13123</v>
@@ -3578,14 +3578,14 @@
       </c>
       <c r="AS21" s="9">
         <f t="shared" si="16"/>
-        <v>4041</v>
+        <v>4043</v>
       </c>
       <c r="AT21" s="8">
-        <v>9430</v>
+        <v>9432</v>
       </c>
       <c r="AU21" s="10">
         <f t="shared" si="17"/>
-        <v>0.71858568924788535</v>
+        <v>0.71873809342375983</v>
       </c>
       <c r="AV21" s="22">
         <v>9474</v>
@@ -3595,14 +3595,14 @@
       </c>
       <c r="AX21" s="9">
         <f t="shared" si="18"/>
-        <v>4667</v>
+        <v>4670</v>
       </c>
       <c r="AY21" s="9">
-        <v>6069</v>
+        <v>6072</v>
       </c>
       <c r="AZ21" s="10">
         <f t="shared" si="19"/>
-        <v>0.64059531348955034</v>
+        <v>0.64091196960101326</v>
       </c>
       <c r="BA21" s="22">
         <v>9339</v>
@@ -3612,14 +3612,14 @@
       </c>
       <c r="BC21" s="9">
         <f t="shared" si="20"/>
-        <v>4609</v>
+        <v>4612</v>
       </c>
       <c r="BD21" s="8">
-        <v>6188</v>
+        <v>6191</v>
       </c>
       <c r="BE21" s="10">
         <f t="shared" si="21"/>
-        <v>0.66259770853410427</v>
+        <v>0.66291894207088553</v>
       </c>
       <c r="BF21" s="9">
         <v>12705</v>
@@ -3629,14 +3629,14 @@
       </c>
       <c r="BH21" s="9">
         <f t="shared" si="22"/>
-        <v>7292</v>
+        <v>7294</v>
       </c>
       <c r="BI21" s="6">
-        <v>9738</v>
+        <v>9740</v>
       </c>
       <c r="BJ21" s="10">
         <f t="shared" si="23"/>
-        <v>0.76646989374262098</v>
+        <v>0.76662731208185753</v>
       </c>
     </row>
     <row r="22" spans="1:62" x14ac:dyDescent="0.3">
@@ -3739,14 +3739,14 @@
       </c>
       <c r="AD22" s="9">
         <f t="shared" si="10"/>
-        <v>2738</v>
+        <v>2739</v>
       </c>
       <c r="AE22" s="8">
-        <v>5395</v>
+        <v>5396</v>
       </c>
       <c r="AF22" s="10">
         <f t="shared" si="11"/>
-        <v>0.79175227472850018</v>
+        <v>0.79189903140592899</v>
       </c>
       <c r="AG22" s="5">
         <v>5399</v>
@@ -3756,14 +3756,14 @@
       </c>
       <c r="AI22" s="9">
         <f t="shared" si="12"/>
-        <v>3054</v>
+        <v>3055</v>
       </c>
       <c r="AJ22" s="8">
-        <v>3851</v>
+        <v>3852</v>
       </c>
       <c r="AK22" s="10">
         <f t="shared" si="13"/>
-        <v>0.7132802370809409</v>
+        <v>0.71346545656603078</v>
       </c>
       <c r="AL22" s="5">
         <v>5432</v>
@@ -3790,14 +3790,14 @@
       </c>
       <c r="AS22" s="9">
         <f t="shared" si="16"/>
-        <v>2102</v>
+        <v>2103</v>
       </c>
       <c r="AT22" s="8">
-        <v>5598</v>
+        <v>5599</v>
       </c>
       <c r="AU22" s="10">
         <f t="shared" si="17"/>
-        <v>0.78978555304740405</v>
+        <v>0.78992663656884876</v>
       </c>
       <c r="AV22" s="22">
         <v>5686</v>
@@ -4053,14 +4053,14 @@
       </c>
       <c r="BH23" s="9">
         <f t="shared" si="22"/>
-        <v>5945</v>
+        <v>5946</v>
       </c>
       <c r="BI23" s="6">
-        <v>7828</v>
+        <v>7829</v>
       </c>
       <c r="BJ23" s="10">
         <f t="shared" si="23"/>
-        <v>0.71228389444949958</v>
+        <v>0.71237488626023659</v>
       </c>
     </row>
     <row r="24" spans="1:62" x14ac:dyDescent="0.3">
@@ -4078,14 +4078,14 @@
       </c>
       <c r="E24" s="9">
         <f t="shared" si="0"/>
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="F24" s="8">
-        <v>2895</v>
+        <v>2897</v>
       </c>
       <c r="G24" s="10">
         <f t="shared" si="1"/>
-        <v>0.46573359073359072</v>
+        <v>0.46605534105534108</v>
       </c>
       <c r="H24" s="5">
         <v>5730</v>
@@ -4095,14 +4095,14 @@
       </c>
       <c r="J24" s="9">
         <f t="shared" si="2"/>
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="K24" s="8">
-        <v>2897</v>
+        <v>2899</v>
       </c>
       <c r="L24" s="10">
         <f t="shared" si="3"/>
-        <v>0.50558464223385691</v>
+        <v>0.50593368237347291</v>
       </c>
       <c r="M24" s="5">
         <v>6293</v>
@@ -4112,14 +4112,14 @@
       </c>
       <c r="O24" s="9">
         <f t="shared" si="4"/>
-        <v>2282</v>
+        <v>2283</v>
       </c>
       <c r="P24" s="8">
-        <v>4480</v>
+        <v>4481</v>
       </c>
       <c r="Q24" s="10">
         <f t="shared" si="5"/>
-        <v>0.71190211345939935</v>
+        <v>0.71206102018115369</v>
       </c>
       <c r="R24" s="5">
         <v>5052</v>
@@ -4129,14 +4129,14 @@
       </c>
       <c r="T24" s="9">
         <f t="shared" si="6"/>
-        <v>2405</v>
+        <v>2406</v>
       </c>
       <c r="U24" s="8">
-        <v>2981</v>
+        <v>2982</v>
       </c>
       <c r="V24" s="10">
         <f t="shared" si="7"/>
-        <v>0.59006334125098969</v>
+        <v>0.59026128266033251</v>
       </c>
       <c r="W24" s="5">
         <v>5122</v>
@@ -4146,14 +4146,14 @@
       </c>
       <c r="Y24" s="9">
         <f t="shared" si="8"/>
-        <v>2412</v>
+        <v>2415</v>
       </c>
       <c r="Z24" s="8">
-        <v>3023</v>
+        <v>3026</v>
       </c>
       <c r="AA24" s="10">
         <f t="shared" si="9"/>
-        <v>0.59019914096056225</v>
+        <v>0.59078484966809841</v>
       </c>
       <c r="AB24" s="5">
         <v>6663</v>
@@ -4163,14 +4163,14 @@
       </c>
       <c r="AD24" s="9">
         <f t="shared" si="10"/>
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="AE24" s="8">
-        <v>4644</v>
+        <v>4647</v>
       </c>
       <c r="AF24" s="10">
         <f t="shared" si="11"/>
-        <v>0.69698334083746061</v>
+        <v>0.69743358847366055</v>
       </c>
       <c r="AG24" s="5">
         <v>5175</v>
@@ -4180,14 +4180,14 @@
       </c>
       <c r="AI24" s="9">
         <f t="shared" si="12"/>
-        <v>2339</v>
+        <v>2340</v>
       </c>
       <c r="AJ24" s="8">
-        <v>3098</v>
+        <v>3099</v>
       </c>
       <c r="AK24" s="10">
         <f t="shared" si="13"/>
-        <v>0.59864734299516909</v>
+        <v>0.59884057971014493</v>
       </c>
       <c r="AL24" s="5">
         <v>5189</v>
@@ -4197,14 +4197,14 @@
       </c>
       <c r="AN24" s="9">
         <f t="shared" si="14"/>
-        <v>2327</v>
+        <v>2330</v>
       </c>
       <c r="AO24" s="8">
-        <v>3181</v>
+        <v>3184</v>
       </c>
       <c r="AP24" s="10">
         <f t="shared" si="15"/>
-        <v>0.61302755829639621</v>
+        <v>0.61360570437463868</v>
       </c>
       <c r="AQ24" s="22">
         <v>6826</v>
@@ -4214,14 +4214,14 @@
       </c>
       <c r="AS24" s="9">
         <f t="shared" si="16"/>
-        <v>1152</v>
+        <v>1154</v>
       </c>
       <c r="AT24" s="8">
-        <v>4993</v>
+        <v>4995</v>
       </c>
       <c r="AU24" s="10">
         <f t="shared" si="17"/>
-        <v>0.7314679167887489</v>
+        <v>0.73176091415177258</v>
       </c>
       <c r="AV24" s="22">
         <v>5390</v>
@@ -4231,14 +4231,14 @@
       </c>
       <c r="AX24" s="9">
         <f t="shared" si="18"/>
-        <v>2758</v>
+        <v>2759</v>
       </c>
       <c r="AY24" s="9">
-        <v>3737</v>
+        <v>3738</v>
       </c>
       <c r="AZ24" s="10">
         <f t="shared" si="19"/>
-        <v>0.69332096474953619</v>
+        <v>0.69350649350649352</v>
       </c>
       <c r="BA24" s="22">
         <v>5125</v>
@@ -4248,14 +4248,14 @@
       </c>
       <c r="BC24" s="9">
         <f t="shared" si="20"/>
-        <v>2877</v>
+        <v>2878</v>
       </c>
       <c r="BD24" s="8">
-        <v>3820</v>
+        <v>3821</v>
       </c>
       <c r="BE24" s="10">
         <f t="shared" si="21"/>
-        <v>0.74536585365853658</v>
+        <v>0.74556097560975609</v>
       </c>
       <c r="BF24" s="9">
         <v>6600</v>
@@ -4265,14 +4265,14 @@
       </c>
       <c r="BH24" s="9">
         <f t="shared" si="22"/>
-        <v>3998</v>
+        <v>3999</v>
       </c>
       <c r="BI24" s="6">
-        <v>5238</v>
+        <v>5239</v>
       </c>
       <c r="BJ24" s="10">
         <f t="shared" si="23"/>
-        <v>0.79363636363636358</v>
+        <v>0.79378787878787882</v>
       </c>
     </row>
     <row r="25" spans="1:62" x14ac:dyDescent="0.3">
@@ -4502,14 +4502,14 @@
       </c>
       <c r="E26" s="9">
         <f t="shared" si="0"/>
-        <v>3527</v>
+        <v>3529</v>
       </c>
       <c r="F26" s="8">
-        <v>7626</v>
+        <v>7628</v>
       </c>
       <c r="G26" s="10">
         <f t="shared" si="1"/>
-        <v>0.28721000301295568</v>
+        <v>0.28728532690569447</v>
       </c>
       <c r="H26" s="5">
         <v>23466</v>
@@ -4519,14 +4519,14 @@
       </c>
       <c r="J26" s="9">
         <f t="shared" si="2"/>
-        <v>3887</v>
+        <v>3889</v>
       </c>
       <c r="K26" s="8">
-        <v>7646</v>
+        <v>7648</v>
       </c>
       <c r="L26" s="10">
         <f t="shared" si="3"/>
-        <v>0.32583312025909827</v>
+        <v>0.32591834995312369</v>
       </c>
       <c r="M26" s="5">
         <v>25760</v>
@@ -4536,14 +4536,14 @@
       </c>
       <c r="O26" s="9">
         <f t="shared" si="4"/>
-        <v>10448</v>
+        <v>10451</v>
       </c>
       <c r="P26" s="8">
-        <v>17319</v>
+        <v>17322</v>
       </c>
       <c r="Q26" s="10">
         <f t="shared" si="5"/>
-        <v>0.67232142857142863</v>
+        <v>0.67243788819875772</v>
       </c>
       <c r="R26" s="5">
         <v>16534</v>
@@ -4553,14 +4553,14 @@
       </c>
       <c r="T26" s="9">
         <f t="shared" si="6"/>
-        <v>6351</v>
+        <v>6353</v>
       </c>
       <c r="U26" s="8">
-        <v>7698</v>
+        <v>7700</v>
       </c>
       <c r="V26" s="10">
         <f t="shared" si="7"/>
-        <v>0.46558606507802103</v>
+        <v>0.46570702794242169</v>
       </c>
       <c r="W26" s="5">
         <v>16064</v>
@@ -4570,14 +4570,14 @@
       </c>
       <c r="Y26" s="9">
         <f t="shared" si="8"/>
-        <v>6287</v>
+        <v>6291</v>
       </c>
       <c r="Z26" s="8">
-        <v>7763</v>
+        <v>7767</v>
       </c>
       <c r="AA26" s="10">
         <f t="shared" si="9"/>
-        <v>0.48325448207171312</v>
+        <v>0.48350348605577687</v>
       </c>
       <c r="AB26" s="5">
         <v>25659</v>
@@ -4587,14 +4587,14 @@
       </c>
       <c r="AD26" s="9">
         <f t="shared" si="10"/>
-        <v>9221</v>
+        <v>9226</v>
       </c>
       <c r="AE26" s="8">
-        <v>17589</v>
+        <v>17594</v>
       </c>
       <c r="AF26" s="10">
         <f t="shared" si="11"/>
-        <v>0.68549047117970308</v>
+        <v>0.6856853345804591</v>
       </c>
       <c r="AG26" s="5">
         <v>15065</v>
@@ -4604,14 +4604,14 @@
       </c>
       <c r="AI26" s="9">
         <f t="shared" si="12"/>
-        <v>6169</v>
+        <v>6171</v>
       </c>
       <c r="AJ26" s="8">
-        <v>7945</v>
+        <v>7947</v>
       </c>
       <c r="AK26" s="10">
         <f t="shared" si="13"/>
-        <v>0.52738134749419185</v>
+        <v>0.52751410554264855</v>
       </c>
       <c r="AL26" s="5">
         <v>14868</v>
@@ -4621,14 +4621,14 @@
       </c>
       <c r="AN26" s="9">
         <f t="shared" si="14"/>
-        <v>6212</v>
+        <v>6215</v>
       </c>
       <c r="AO26" s="8">
-        <v>7981</v>
+        <v>7984</v>
       </c>
       <c r="AP26" s="10">
         <f t="shared" si="15"/>
-        <v>0.53679042238364272</v>
+        <v>0.53699219800914721</v>
       </c>
       <c r="AQ26" s="22">
         <v>26317</v>
@@ -4638,14 +4638,14 @@
       </c>
       <c r="AS26" s="9">
         <f t="shared" si="16"/>
-        <v>7565</v>
+        <v>7567</v>
       </c>
       <c r="AT26" s="8">
-        <v>18135</v>
+        <v>18137</v>
       </c>
       <c r="AU26" s="10">
         <f t="shared" si="17"/>
-        <v>0.689098301478132</v>
+        <v>0.68917429798229279</v>
       </c>
       <c r="AV26" s="22">
         <v>16878</v>
@@ -4655,14 +4655,14 @@
       </c>
       <c r="AX26" s="9">
         <f t="shared" si="18"/>
-        <v>7680</v>
+        <v>7684</v>
       </c>
       <c r="AY26" s="9">
-        <v>10301</v>
+        <v>10305</v>
       </c>
       <c r="AZ26" s="10">
         <f t="shared" si="19"/>
-        <v>0.6103211280957459</v>
+        <v>0.6105581230003555</v>
       </c>
       <c r="BA26" s="22">
         <v>16511</v>
@@ -4672,14 +4672,14 @@
       </c>
       <c r="BC26" s="9">
         <f t="shared" si="20"/>
-        <v>7375</v>
+        <v>7378</v>
       </c>
       <c r="BD26" s="8">
-        <v>10292</v>
+        <v>10295</v>
       </c>
       <c r="BE26" s="10">
         <f t="shared" si="21"/>
-        <v>0.62334201441463266</v>
+        <v>0.6235237114650839</v>
       </c>
       <c r="BF26" s="9">
         <v>25358</v>
@@ -4689,14 +4689,14 @@
       </c>
       <c r="BH26" s="9">
         <f t="shared" si="22"/>
-        <v>12734</v>
+        <v>12736</v>
       </c>
       <c r="BI26" s="6">
-        <v>18481</v>
+        <v>18483</v>
       </c>
       <c r="BJ26" s="10">
         <f t="shared" si="23"/>
-        <v>0.7288035334016878</v>
+        <v>0.72888240397507686</v>
       </c>
     </row>
     <row r="27" spans="1:62" x14ac:dyDescent="0.3">
@@ -4714,14 +4714,14 @@
       </c>
       <c r="E27" s="9">
         <f t="shared" si="0"/>
-        <v>27161</v>
+        <v>27163</v>
       </c>
       <c r="F27" s="8">
-        <v>53280</v>
+        <v>53282</v>
       </c>
       <c r="G27" s="10">
         <f t="shared" si="1"/>
-        <v>0.36643993424989169</v>
+        <v>0.36645368950267881</v>
       </c>
       <c r="H27" s="5">
         <v>133004</v>
@@ -4731,14 +4731,14 @@
       </c>
       <c r="J27" s="9">
         <f t="shared" si="2"/>
-        <v>30765</v>
+        <v>30767</v>
       </c>
       <c r="K27" s="8">
-        <v>53263</v>
+        <v>53265</v>
       </c>
       <c r="L27" s="10">
         <f t="shared" si="3"/>
-        <v>0.400461640251421</v>
+        <v>0.40047667739316112</v>
       </c>
       <c r="M27" s="5">
         <v>146684</v>
@@ -4748,14 +4748,14 @@
       </c>
       <c r="O27" s="9">
         <f t="shared" si="4"/>
-        <v>89632</v>
+        <v>89635</v>
       </c>
       <c r="P27" s="8">
-        <v>121230</v>
+        <v>121233</v>
       </c>
       <c r="Q27" s="10">
         <f t="shared" si="5"/>
-        <v>0.82647050803086908</v>
+        <v>0.82649096015925394</v>
       </c>
       <c r="R27" s="5">
         <v>100364</v>
@@ -4765,14 +4765,14 @@
       </c>
       <c r="T27" s="9">
         <f t="shared" si="6"/>
-        <v>48155</v>
+        <v>48157</v>
       </c>
       <c r="U27" s="8">
-        <v>54586</v>
+        <v>54588</v>
       </c>
       <c r="V27" s="10">
         <f t="shared" si="7"/>
-        <v>0.54388027579610221</v>
+        <v>0.54390020326013311</v>
       </c>
       <c r="W27" s="5">
         <v>96252</v>
@@ -4782,14 +4782,14 @@
       </c>
       <c r="Y27" s="9">
         <f t="shared" si="8"/>
-        <v>45966</v>
+        <v>45968</v>
       </c>
       <c r="Z27" s="8">
-        <v>55297</v>
+        <v>55299</v>
       </c>
       <c r="AA27" s="10">
         <f t="shared" si="9"/>
-        <v>0.57450234800315836</v>
+        <v>0.57452312679217055</v>
       </c>
       <c r="AB27" s="5">
         <v>156081</v>
@@ -4799,14 +4799,14 @@
       </c>
       <c r="AD27" s="9">
         <f t="shared" si="10"/>
-        <v>70855</v>
+        <v>70860</v>
       </c>
       <c r="AE27" s="8">
-        <v>125733</v>
+        <v>125738</v>
       </c>
       <c r="AF27" s="10">
         <f t="shared" si="11"/>
-        <v>0.805562496396102</v>
+        <v>0.80559453104477807</v>
       </c>
       <c r="AG27" s="5">
         <v>90207</v>
@@ -4816,14 +4816,14 @@
       </c>
       <c r="AI27" s="9">
         <f t="shared" si="12"/>
-        <v>43211</v>
+        <v>43214</v>
       </c>
       <c r="AJ27" s="8">
-        <v>56365</v>
+        <v>56368</v>
       </c>
       <c r="AK27" s="10">
         <f t="shared" si="13"/>
-        <v>0.62484064429589725</v>
+        <v>0.62487390113849262</v>
       </c>
       <c r="AL27" s="5">
         <v>89207</v>
@@ -4833,14 +4833,14 @@
       </c>
       <c r="AN27" s="9">
         <f t="shared" si="14"/>
-        <v>43649</v>
+        <v>43651</v>
       </c>
       <c r="AO27" s="8">
-        <v>57102</v>
+        <v>57104</v>
       </c>
       <c r="AP27" s="10">
         <f t="shared" si="15"/>
-        <v>0.64010671808266173</v>
+        <v>0.64012913784792669</v>
       </c>
       <c r="AQ27" s="22">
         <v>161396</v>
@@ -4850,14 +4850,14 @@
       </c>
       <c r="AS27" s="9">
         <f t="shared" si="16"/>
-        <v>52387</v>
+        <v>52392</v>
       </c>
       <c r="AT27" s="8">
-        <v>131365</v>
+        <v>131370</v>
       </c>
       <c r="AU27" s="10">
         <f t="shared" si="17"/>
-        <v>0.81392971325187735</v>
+        <v>0.81396069295397655</v>
       </c>
       <c r="AV27" s="22">
         <v>108391</v>
@@ -4867,14 +4867,14 @@
       </c>
       <c r="AX27" s="9">
         <f t="shared" si="18"/>
-        <v>57656</v>
+        <v>57659</v>
       </c>
       <c r="AY27" s="9">
-        <v>81724</v>
+        <v>81727</v>
       </c>
       <c r="AZ27" s="10">
         <f t="shared" si="19"/>
-        <v>0.75397403843492539</v>
+        <v>0.75400171600963184</v>
       </c>
       <c r="BA27" s="22">
         <v>101826</v>
@@ -4884,14 +4884,14 @@
       </c>
       <c r="BC27" s="9">
         <f t="shared" si="20"/>
-        <v>56637</v>
+        <v>56641</v>
       </c>
       <c r="BD27" s="8">
-        <v>83637</v>
+        <v>83641</v>
       </c>
       <c r="BE27" s="10">
         <f t="shared" si="21"/>
-        <v>0.82137175181191446</v>
+        <v>0.82141103450985009</v>
       </c>
       <c r="BF27" s="9">
         <v>155251</v>
@@ -4901,14 +4901,14 @@
       </c>
       <c r="BH27" s="9">
         <f t="shared" si="22"/>
-        <v>92688</v>
+        <v>92694</v>
       </c>
       <c r="BI27" s="6">
-        <v>135911</v>
+        <v>135917</v>
       </c>
       <c r="BJ27" s="10">
         <f t="shared" si="23"/>
-        <v>0.87542753347804525</v>
+        <v>0.87546618057210579</v>
       </c>
     </row>
     <row r="28" spans="1:62" x14ac:dyDescent="0.3">
@@ -4960,14 +4960,14 @@
       </c>
       <c r="O28" s="9">
         <f t="shared" si="4"/>
-        <v>317138</v>
+        <v>317140</v>
       </c>
       <c r="P28" s="8">
-        <v>515637</v>
+        <v>515639</v>
       </c>
       <c r="Q28" s="10">
         <f t="shared" si="5"/>
-        <v>0.85078365147432733</v>
+        <v>0.85078695140684368</v>
       </c>
       <c r="R28" s="5">
         <v>322040</v>
@@ -5011,14 +5011,14 @@
       </c>
       <c r="AD28" s="9">
         <f t="shared" si="10"/>
-        <v>237491</v>
+        <v>237494</v>
       </c>
       <c r="AE28" s="8">
-        <v>521361</v>
+        <v>521364</v>
       </c>
       <c r="AF28" s="10">
         <f t="shared" si="11"/>
-        <v>0.84531821785677808</v>
+        <v>0.84532308196179085</v>
       </c>
       <c r="AG28" s="5">
         <v>279354</v>
@@ -5028,14 +5028,14 @@
       </c>
       <c r="AI28" s="9">
         <f t="shared" si="12"/>
-        <v>132097</v>
+        <v>132098</v>
       </c>
       <c r="AJ28" s="8">
-        <v>195000</v>
+        <v>195001</v>
       </c>
       <c r="AK28" s="10">
         <f t="shared" si="13"/>
-        <v>0.69803904723039589</v>
+        <v>0.69804262691781749</v>
       </c>
       <c r="AL28" s="5">
         <v>276143</v>
@@ -5045,14 +5045,14 @@
       </c>
       <c r="AN28" s="9">
         <f t="shared" si="14"/>
-        <v>129667</v>
+        <v>129669</v>
       </c>
       <c r="AO28" s="8">
-        <v>196865</v>
+        <v>196867</v>
       </c>
       <c r="AP28" s="10">
         <f t="shared" si="15"/>
-        <v>0.71290961567014188</v>
+        <v>0.71291685829443441</v>
       </c>
       <c r="AQ28" s="22">
         <v>625592</v>
@@ -5062,14 +5062,14 @@
       </c>
       <c r="AS28" s="9">
         <f t="shared" si="16"/>
-        <v>155359</v>
+        <v>155363</v>
       </c>
       <c r="AT28" s="8">
-        <v>532671</v>
+        <v>532675</v>
       </c>
       <c r="AU28" s="10">
         <f t="shared" si="17"/>
-        <v>0.85146709037199964</v>
+        <v>0.85147348431565617</v>
       </c>
       <c r="AV28" s="22">
         <v>329857</v>
@@ -5079,14 +5079,14 @@
       </c>
       <c r="AX28" s="9">
         <f t="shared" si="18"/>
-        <v>153808</v>
+        <v>153809</v>
       </c>
       <c r="AY28" s="9">
-        <v>254211</v>
+        <v>254212</v>
       </c>
       <c r="AZ28" s="10">
         <f t="shared" si="19"/>
-        <v>0.77067032077536635</v>
+        <v>0.77067335239209722</v>
       </c>
       <c r="BA28" s="22">
         <v>323426</v>
@@ -5096,14 +5096,14 @@
       </c>
       <c r="BC28" s="9">
         <f t="shared" si="20"/>
-        <v>140114</v>
+        <v>140115</v>
       </c>
       <c r="BD28" s="8">
-        <v>257986</v>
+        <v>257987</v>
       </c>
       <c r="BE28" s="10">
         <f t="shared" si="21"/>
-        <v>0.79766623586229923</v>
+        <v>0.79766932775967303</v>
       </c>
       <c r="BF28" s="9">
         <v>619161</v>
@@ -5113,14 +5113,14 @@
       </c>
       <c r="BH28" s="9">
         <f t="shared" si="22"/>
-        <v>279111</v>
+        <v>279113</v>
       </c>
       <c r="BI28" s="6">
-        <v>545823</v>
+        <v>545825</v>
       </c>
       <c r="BJ28" s="10">
         <f t="shared" si="23"/>
-        <v>0.88155261717065514</v>
+        <v>0.88155584734826642</v>
       </c>
     </row>
     <row r="29" spans="1:62" x14ac:dyDescent="0.3">
@@ -5155,14 +5155,14 @@
       </c>
       <c r="J29" s="9">
         <f t="shared" si="2"/>
-        <v>25109</v>
+        <v>25110</v>
       </c>
       <c r="K29" s="8">
-        <v>57937</v>
+        <v>57938</v>
       </c>
       <c r="L29" s="10">
         <f t="shared" si="3"/>
-        <v>0.44088729929229131</v>
+        <v>0.44089490906323719</v>
       </c>
       <c r="M29" s="5">
         <v>144577</v>
@@ -5172,14 +5172,14 @@
       </c>
       <c r="O29" s="9">
         <f t="shared" si="4"/>
-        <v>79878</v>
+        <v>79879</v>
       </c>
       <c r="P29" s="8">
-        <v>129718</v>
+        <v>129719</v>
       </c>
       <c r="Q29" s="10">
         <f t="shared" si="5"/>
-        <v>0.89722431645420775</v>
+        <v>0.89723123318370146</v>
       </c>
       <c r="R29" s="5">
         <v>86442</v>
@@ -5189,14 +5189,14 @@
       </c>
       <c r="T29" s="9">
         <f t="shared" si="6"/>
-        <v>49246</v>
+        <v>49247</v>
       </c>
       <c r="U29" s="8">
-        <v>59156</v>
+        <v>59157</v>
       </c>
       <c r="V29" s="10">
         <f t="shared" si="7"/>
-        <v>0.68434325906388094</v>
+        <v>0.68435482751440269</v>
       </c>
       <c r="W29" s="5">
         <v>83687</v>
@@ -5206,14 +5206,14 @@
       </c>
       <c r="Y29" s="9">
         <f t="shared" si="8"/>
-        <v>46726</v>
+        <v>46727</v>
       </c>
       <c r="Z29" s="8">
-        <v>59680</v>
+        <v>59681</v>
       </c>
       <c r="AA29" s="10">
         <f t="shared" si="9"/>
-        <v>0.71313346158901625</v>
+        <v>0.71314541087624128</v>
       </c>
       <c r="AB29" s="5">
         <v>153397</v>
@@ -5223,14 +5223,14 @@
       </c>
       <c r="AD29" s="9">
         <f t="shared" si="10"/>
-        <v>61928</v>
+        <v>61929</v>
       </c>
       <c r="AE29" s="8">
-        <v>133920</v>
+        <v>133921</v>
       </c>
       <c r="AF29" s="10">
         <f t="shared" si="11"/>
-        <v>0.87302880760379931</v>
+        <v>0.87303532663611416</v>
       </c>
       <c r="AG29" s="5">
         <v>79643</v>
@@ -5240,14 +5240,14 @@
       </c>
       <c r="AI29" s="9">
         <f t="shared" si="12"/>
-        <v>44065</v>
+        <v>44066</v>
       </c>
       <c r="AJ29" s="8">
-        <v>60820</v>
+        <v>60821</v>
       </c>
       <c r="AK29" s="10">
         <f t="shared" si="13"/>
-        <v>0.76365782303529506</v>
+        <v>0.76367037906658464</v>
       </c>
       <c r="AL29" s="5">
         <v>78780</v>
@@ -5257,14 +5257,14 @@
       </c>
       <c r="AN29" s="9">
         <f t="shared" si="14"/>
-        <v>44298</v>
+        <v>44299</v>
       </c>
       <c r="AO29" s="8">
-        <v>61654</v>
+        <v>61655</v>
       </c>
       <c r="AP29" s="10">
         <f t="shared" si="15"/>
-        <v>0.78260979944148257</v>
+        <v>0.78262249301853259</v>
       </c>
       <c r="AQ29" s="22">
         <v>155521</v>
@@ -5274,14 +5274,14 @@
       </c>
       <c r="AS29" s="9">
         <f t="shared" si="16"/>
-        <v>41580</v>
+        <v>41581</v>
       </c>
       <c r="AT29" s="8">
-        <v>138705</v>
+        <v>138706</v>
       </c>
       <c r="AU29" s="10">
         <f t="shared" si="17"/>
-        <v>0.8918731232438063</v>
+        <v>0.89187955324361345</v>
       </c>
       <c r="AV29" s="22">
         <v>96040</v>
@@ -5291,14 +5291,14 @@
       </c>
       <c r="AX29" s="9">
         <f t="shared" si="18"/>
-        <v>51817</v>
+        <v>51819</v>
       </c>
       <c r="AY29" s="9">
-        <v>83589</v>
+        <v>83591</v>
       </c>
       <c r="AZ29" s="10">
         <f t="shared" si="19"/>
-        <v>0.8703561016243232</v>
+        <v>0.87037692628071639</v>
       </c>
       <c r="BA29" s="22">
         <v>92820</v>
@@ -5308,14 +5308,14 @@
       </c>
       <c r="BC29" s="9">
         <f t="shared" si="20"/>
-        <v>48851</v>
+        <v>48853</v>
       </c>
       <c r="BD29" s="8">
-        <v>85031</v>
+        <v>85033</v>
       </c>
       <c r="BE29" s="10">
         <f t="shared" si="21"/>
-        <v>0.91608489549666017</v>
+        <v>0.91610644257703078</v>
       </c>
       <c r="BF29" s="9">
         <v>153057</v>
@@ -5325,14 +5325,14 @@
       </c>
       <c r="BH29" s="9">
         <f t="shared" si="22"/>
-        <v>83901</v>
+        <v>83902</v>
       </c>
       <c r="BI29" s="6">
-        <v>143673</v>
+        <v>143674</v>
       </c>
       <c r="BJ29" s="10">
         <f t="shared" si="23"/>
-        <v>0.93868950783041616</v>
+        <v>0.93869604134407447</v>
       </c>
     </row>
     <row r="30" spans="1:62" x14ac:dyDescent="0.3">
@@ -5350,14 +5350,14 @@
       </c>
       <c r="E30" s="9">
         <f t="shared" si="0"/>
-        <v>30457</v>
+        <v>30458</v>
       </c>
       <c r="F30" s="8">
-        <v>77355</v>
+        <v>77356</v>
       </c>
       <c r="G30" s="10">
         <f t="shared" si="1"/>
-        <v>0.34790684704781777</v>
+        <v>0.34791134458316841</v>
       </c>
       <c r="H30" s="5">
         <v>196739</v>
@@ -5367,14 +5367,14 @@
       </c>
       <c r="J30" s="9">
         <f t="shared" si="2"/>
-        <v>35387</v>
+        <v>35388</v>
       </c>
       <c r="K30" s="8">
-        <v>77593</v>
+        <v>77594</v>
       </c>
       <c r="L30" s="10">
         <f t="shared" si="3"/>
-        <v>0.39439562059378158</v>
+        <v>0.39440070347007966</v>
       </c>
       <c r="M30" s="5">
         <v>227236</v>
@@ -5384,14 +5384,14 @@
       </c>
       <c r="O30" s="9">
         <f t="shared" si="4"/>
-        <v>132035</v>
+        <v>132040</v>
       </c>
       <c r="P30" s="8">
-        <v>197264</v>
+        <v>197269</v>
       </c>
       <c r="Q30" s="10">
         <f t="shared" si="5"/>
-        <v>0.86810188526465881</v>
+        <v>0.86812388882043334</v>
       </c>
       <c r="R30" s="5">
         <v>127114</v>
@@ -5401,14 +5401,14 @@
       </c>
       <c r="T30" s="9">
         <f t="shared" si="6"/>
-        <v>67310</v>
+        <v>67311</v>
       </c>
       <c r="U30" s="8">
-        <v>79309</v>
+        <v>79310</v>
       </c>
       <c r="V30" s="10">
         <f t="shared" si="7"/>
-        <v>0.6239202605535189</v>
+        <v>0.62392812750759163</v>
       </c>
       <c r="W30" s="5">
         <v>123894</v>
@@ -5418,14 +5418,14 @@
       </c>
       <c r="Y30" s="9">
         <f t="shared" si="8"/>
-        <v>64462</v>
+        <v>64463</v>
       </c>
       <c r="Z30" s="8">
-        <v>79904</v>
+        <v>79905</v>
       </c>
       <c r="AA30" s="10">
         <f t="shared" si="9"/>
-        <v>0.6449384150967763</v>
+        <v>0.64494648651266406</v>
       </c>
       <c r="AB30" s="5">
         <v>242455</v>
@@ -5435,14 +5435,14 @@
       </c>
       <c r="AD30" s="9">
         <f t="shared" si="10"/>
-        <v>99289</v>
+        <v>99294</v>
       </c>
       <c r="AE30" s="8">
-        <v>203368</v>
+        <v>203373</v>
       </c>
       <c r="AF30" s="10">
         <f t="shared" si="11"/>
-        <v>0.8387865789527954</v>
+        <v>0.83880720133633047</v>
       </c>
       <c r="AG30" s="5">
         <v>117700</v>
@@ -5452,14 +5452,14 @@
       </c>
       <c r="AI30" s="9">
         <f t="shared" si="12"/>
-        <v>61300</v>
+        <v>61301</v>
       </c>
       <c r="AJ30" s="8">
-        <v>81938</v>
+        <v>81939</v>
       </c>
       <c r="AK30" s="10">
         <f t="shared" si="13"/>
-        <v>0.69615972812234495</v>
+        <v>0.69616822429906544</v>
       </c>
       <c r="AL30" s="5">
         <v>115490</v>
@@ -5469,14 +5469,14 @@
       </c>
       <c r="AN30" s="9">
         <f t="shared" si="14"/>
-        <v>62027</v>
+        <v>62028</v>
       </c>
       <c r="AO30" s="8">
-        <v>83087</v>
+        <v>83088</v>
       </c>
       <c r="AP30" s="10">
         <f t="shared" si="15"/>
-        <v>0.71943025370161917</v>
+        <v>0.71943891245995328</v>
       </c>
       <c r="AQ30" s="22">
         <v>248265</v>
@@ -5486,14 +5486,14 @@
       </c>
       <c r="AS30" s="9">
         <f t="shared" si="16"/>
-        <v>74371</v>
+        <v>74376</v>
       </c>
       <c r="AT30" s="8">
-        <v>212360</v>
+        <v>212365</v>
       </c>
       <c r="AU30" s="10">
         <f t="shared" si="17"/>
-        <v>0.85537631160252148</v>
+        <v>0.85539645137252529</v>
       </c>
       <c r="AV30" s="22">
         <v>136681</v>
@@ -5503,14 +5503,14 @@
       </c>
       <c r="AX30" s="9">
         <f t="shared" si="18"/>
-        <v>78445</v>
+        <v>78446</v>
       </c>
       <c r="AY30" s="9">
-        <v>110632</v>
+        <v>110633</v>
       </c>
       <c r="AZ30" s="10">
         <f t="shared" si="19"/>
-        <v>0.80941754889121387</v>
+        <v>0.80942486519706469</v>
       </c>
       <c r="BA30" s="22">
         <v>130520</v>
@@ -5537,14 +5537,14 @@
       </c>
       <c r="BH30" s="9">
         <f t="shared" si="22"/>
-        <v>141117</v>
+        <v>141118</v>
       </c>
       <c r="BI30" s="6">
-        <v>221810</v>
+        <v>221811</v>
       </c>
       <c r="BJ30" s="10">
         <f t="shared" si="23"/>
-        <v>0.90296238097758164</v>
+        <v>0.90296645185978253</v>
       </c>
     </row>
     <row r="31" spans="1:62" x14ac:dyDescent="0.3">
@@ -5596,14 +5596,14 @@
       </c>
       <c r="O31" s="9">
         <f t="shared" si="4"/>
-        <v>64558</v>
+        <v>64560</v>
       </c>
       <c r="P31" s="8">
-        <v>98087</v>
+        <v>98089</v>
       </c>
       <c r="Q31" s="10">
         <f t="shared" si="5"/>
-        <v>0.90825501180610213</v>
+        <v>0.90827353118199916</v>
       </c>
       <c r="R31" s="5">
         <v>65023</v>
@@ -5647,14 +5647,14 @@
       </c>
       <c r="AD31" s="9">
         <f t="shared" si="10"/>
-        <v>52968</v>
+        <v>52971</v>
       </c>
       <c r="AE31" s="8">
-        <v>101300</v>
+        <v>101303</v>
       </c>
       <c r="AF31" s="10">
         <f t="shared" si="11"/>
-        <v>0.892518876818298</v>
+        <v>0.89254530876924021</v>
       </c>
       <c r="AG31" s="5">
         <v>58990</v>
@@ -5698,14 +5698,14 @@
       </c>
       <c r="AS31" s="9">
         <f t="shared" si="16"/>
-        <v>37966</v>
+        <v>37969</v>
       </c>
       <c r="AT31" s="8">
-        <v>104661</v>
+        <v>104664</v>
       </c>
       <c r="AU31" s="10">
         <f t="shared" si="17"/>
-        <v>0.90324668599834301</v>
+        <v>0.90327257663628835</v>
       </c>
       <c r="AV31" s="22">
         <v>66185</v>
@@ -5715,14 +5715,14 @@
       </c>
       <c r="AX31" s="9">
         <f t="shared" si="18"/>
-        <v>37460</v>
+        <v>37461</v>
       </c>
       <c r="AY31" s="9">
-        <v>57182</v>
+        <v>57183</v>
       </c>
       <c r="AZ31" s="10">
         <f t="shared" si="19"/>
-        <v>0.86397219913877765</v>
+        <v>0.86398730830248549</v>
       </c>
       <c r="BA31" s="22">
         <v>65739</v>
@@ -5732,14 +5732,14 @@
       </c>
       <c r="BC31" s="9">
         <f t="shared" si="20"/>
-        <v>36889</v>
+        <v>36890</v>
       </c>
       <c r="BD31" s="8">
-        <v>59458</v>
+        <v>59459</v>
       </c>
       <c r="BE31" s="10">
         <f t="shared" si="21"/>
-        <v>0.90445549825826377</v>
+        <v>0.9044707099286573</v>
       </c>
       <c r="BF31" s="9">
         <v>116311</v>
@@ -5749,14 +5749,14 @@
       </c>
       <c r="BH31" s="9">
         <f t="shared" si="22"/>
-        <v>76440</v>
+        <v>76442</v>
       </c>
       <c r="BI31" s="6">
-        <v>109220</v>
+        <v>109222</v>
       </c>
       <c r="BJ31" s="10">
         <f t="shared" si="23"/>
-        <v>0.93903414122481965</v>
+        <v>0.93905133650299633</v>
       </c>
     </row>
     <row r="32" spans="1:62" x14ac:dyDescent="0.3">
@@ -5808,14 +5808,14 @@
       </c>
       <c r="O32" s="9">
         <f t="shared" si="4"/>
-        <v>199315</v>
+        <v>199316</v>
       </c>
       <c r="P32" s="8">
-        <v>329569</v>
+        <v>329570</v>
       </c>
       <c r="Q32" s="10">
         <f t="shared" si="5"/>
-        <v>0.93331917364031547</v>
+        <v>0.93332200557891909</v>
       </c>
       <c r="R32" s="5">
         <v>166950</v>
@@ -5859,14 +5859,14 @@
       </c>
       <c r="AD32" s="9">
         <f t="shared" si="10"/>
-        <v>160707</v>
+        <v>160708</v>
       </c>
       <c r="AE32" s="8">
-        <v>338750</v>
+        <v>338751</v>
       </c>
       <c r="AF32" s="10">
         <f t="shared" si="11"/>
-        <v>0.90495984783317218</v>
+        <v>0.90496251930135763</v>
       </c>
       <c r="AG32" s="5">
         <v>155463</v>
@@ -5910,14 +5910,14 @@
       </c>
       <c r="AS32" s="9">
         <f t="shared" si="16"/>
-        <v>111946</v>
+        <v>111948</v>
       </c>
       <c r="AT32" s="8">
-        <v>348810</v>
+        <v>348812</v>
       </c>
       <c r="AU32" s="10">
         <f t="shared" si="17"/>
-        <v>0.92070011323653234</v>
+        <v>0.92070539232895077</v>
       </c>
       <c r="AV32" s="22">
         <v>171744</v>
@@ -5927,14 +5927,14 @@
       </c>
       <c r="AX32" s="9">
         <f t="shared" si="18"/>
-        <v>96175</v>
+        <v>96177</v>
       </c>
       <c r="AY32" s="9">
-        <v>152310</v>
+        <v>152312</v>
       </c>
       <c r="AZ32" s="10">
         <f t="shared" si="19"/>
-        <v>0.88684320849636666</v>
+        <v>0.88685485373579276</v>
       </c>
       <c r="BA32" s="22">
         <v>169380</v>
@@ -5944,14 +5944,14 @@
       </c>
       <c r="BC32" s="9">
         <f t="shared" si="20"/>
-        <v>93104</v>
+        <v>93107</v>
       </c>
       <c r="BD32" s="8">
-        <v>156566</v>
+        <v>156569</v>
       </c>
       <c r="BE32" s="10">
         <f t="shared" si="21"/>
-        <v>0.92434762073444321</v>
+        <v>0.92436533238871177</v>
       </c>
       <c r="BF32" s="9">
         <v>378386</v>
@@ -5986,14 +5986,14 @@
       </c>
       <c r="E33" s="9">
         <f t="shared" si="0"/>
-        <v>57418</v>
+        <v>57422</v>
       </c>
       <c r="F33" s="8">
-        <v>294976</v>
+        <v>294980</v>
       </c>
       <c r="G33" s="10">
         <f t="shared" si="1"/>
-        <v>0.33093878704992868</v>
+        <v>0.33094327472061447</v>
       </c>
       <c r="H33" s="5">
         <v>840037</v>
@@ -6003,14 +6003,14 @@
       </c>
       <c r="J33" s="9">
         <f t="shared" si="2"/>
-        <v>65404</v>
+        <v>65408</v>
       </c>
       <c r="K33" s="8">
-        <v>295275</v>
+        <v>295279</v>
       </c>
       <c r="L33" s="10">
         <f t="shared" si="3"/>
-        <v>0.35150237430017961</v>
+        <v>0.35150713599520023</v>
       </c>
       <c r="M33" s="5">
         <v>888717</v>
@@ -6020,14 +6020,14 @@
       </c>
       <c r="O33" s="9">
         <f t="shared" si="4"/>
-        <v>331363</v>
+        <v>331372</v>
       </c>
       <c r="P33" s="8">
-        <v>837837</v>
+        <v>837846</v>
       </c>
       <c r="Q33" s="10">
         <f t="shared" si="5"/>
-        <v>0.94274892907415975</v>
+        <v>0.94275905603246024</v>
       </c>
       <c r="R33" s="5">
         <v>410545</v>
@@ -6037,14 +6037,14 @@
       </c>
       <c r="T33" s="9">
         <f t="shared" si="6"/>
-        <v>191547</v>
+        <v>191552</v>
       </c>
       <c r="U33" s="8">
-        <v>299403</v>
+        <v>299408</v>
       </c>
       <c r="V33" s="10">
         <f t="shared" si="7"/>
-        <v>0.72928180832795431</v>
+        <v>0.72929398726083616</v>
       </c>
       <c r="W33" s="5">
         <v>395753</v>
@@ -6054,14 +6054,14 @@
       </c>
       <c r="Y33" s="9">
         <f t="shared" si="8"/>
-        <v>163287</v>
+        <v>163291</v>
       </c>
       <c r="Z33" s="8">
-        <v>301318</v>
+        <v>301322</v>
       </c>
       <c r="AA33" s="10">
         <f t="shared" si="9"/>
-        <v>0.76137894090505942</v>
+        <v>0.76138904821947018</v>
       </c>
       <c r="AB33" s="5">
         <v>919225</v>
@@ -6071,14 +6071,14 @@
       </c>
       <c r="AD33" s="9">
         <f t="shared" si="10"/>
-        <v>217529</v>
+        <v>217535</v>
       </c>
       <c r="AE33" s="8">
-        <v>863400</v>
+        <v>863406</v>
       </c>
       <c r="AF33" s="10">
         <f t="shared" si="11"/>
-        <v>0.93926949332317988</v>
+        <v>0.93927602056079851</v>
       </c>
       <c r="AG33" s="5">
         <v>374721</v>
@@ -6088,14 +6088,14 @@
       </c>
       <c r="AI33" s="9">
         <f t="shared" si="12"/>
-        <v>140256</v>
+        <v>140259</v>
       </c>
       <c r="AJ33" s="8">
-        <v>305408</v>
+        <v>305411</v>
       </c>
       <c r="AK33" s="10">
         <f t="shared" si="13"/>
-        <v>0.81502771395251405</v>
+        <v>0.81503571990894563</v>
       </c>
       <c r="AL33" s="5">
         <v>367134</v>
@@ -6105,14 +6105,14 @@
       </c>
       <c r="AN33" s="9">
         <f t="shared" si="14"/>
-        <v>142092</v>
+        <v>142097</v>
       </c>
       <c r="AO33" s="8">
-        <v>307673</v>
+        <v>307678</v>
       </c>
       <c r="AP33" s="10">
         <f t="shared" si="15"/>
-        <v>0.83804006166685729</v>
+        <v>0.83805368067245201</v>
       </c>
       <c r="AQ33" s="22">
         <v>933808</v>
@@ -6122,14 +6122,14 @@
       </c>
       <c r="AS33" s="9">
         <f t="shared" si="16"/>
-        <v>111357</v>
+        <v>111365</v>
       </c>
       <c r="AT33" s="8">
-        <v>891182</v>
+        <v>891190</v>
       </c>
       <c r="AU33" s="10">
         <f t="shared" si="17"/>
-        <v>0.9543525007282011</v>
+        <v>0.95436106779980467</v>
       </c>
       <c r="AV33" s="22">
         <v>471208</v>
@@ -6139,14 +6139,14 @@
       </c>
       <c r="AX33" s="9">
         <f t="shared" si="18"/>
-        <v>148152</v>
+        <v>148156</v>
       </c>
       <c r="AY33" s="9">
-        <v>435393</v>
+        <v>435397</v>
       </c>
       <c r="AZ33" s="10">
         <f t="shared" si="19"/>
-        <v>0.92399322592146138</v>
+        <v>0.92400171474168524</v>
       </c>
       <c r="BA33" s="22">
         <v>469534</v>
@@ -6156,14 +6156,14 @@
       </c>
       <c r="BC33" s="9">
         <f t="shared" si="20"/>
-        <v>133513</v>
+        <v>133518</v>
       </c>
       <c r="BD33" s="8">
-        <v>447368</v>
+        <v>447373</v>
       </c>
       <c r="BE33" s="10">
         <f t="shared" si="21"/>
-        <v>0.95279149113802197</v>
+        <v>0.95280213999412178</v>
       </c>
       <c r="BF33" s="9">
         <v>935950</v>
@@ -6173,14 +6173,14 @@
       </c>
       <c r="BH33" s="9">
         <f t="shared" si="22"/>
-        <v>270375</v>
+        <v>270379</v>
       </c>
       <c r="BI33" s="6">
-        <v>916118</v>
+        <v>916122</v>
       </c>
       <c r="BJ33" s="10">
         <f t="shared" si="23"/>
-        <v>0.97881083391206791</v>
+        <v>0.97881510764463908</v>
       </c>
     </row>
     <row r="34" spans="1:63" x14ac:dyDescent="0.3">
@@ -6605,14 +6605,14 @@
       </c>
       <c r="E36" s="9">
         <f t="shared" si="0"/>
-        <v>160266</v>
+        <v>160273</v>
       </c>
       <c r="F36" s="8">
-        <v>404016</v>
+        <v>404023</v>
       </c>
       <c r="G36" s="10">
         <f t="shared" si="1"/>
-        <v>0.29323247696873495</v>
+        <v>0.29323755752826425</v>
       </c>
       <c r="H36" s="5">
         <v>1292614</v>
@@ -6622,14 +6622,14 @@
       </c>
       <c r="J36" s="9">
         <f t="shared" si="2"/>
-        <v>174084</v>
+        <v>174091</v>
       </c>
       <c r="K36" s="8">
-        <v>404216</v>
+        <v>404223</v>
       </c>
       <c r="L36" s="10">
         <f t="shared" si="3"/>
-        <v>0.31271207027001102</v>
+        <v>0.31271748565310292</v>
       </c>
       <c r="M36" s="5">
         <v>1376699</v>
@@ -6639,14 +6639,14 @@
       </c>
       <c r="O36" s="9">
         <f t="shared" si="4"/>
-        <v>743402</v>
+        <v>743410</v>
       </c>
       <c r="P36" s="8">
-        <v>1226736</v>
+        <v>1226744</v>
       </c>
       <c r="Q36" s="10">
         <f t="shared" si="5"/>
-        <v>0.89107059713125381</v>
+        <v>0.89107640813278721</v>
       </c>
       <c r="R36" s="5">
         <v>745641</v>
@@ -6656,14 +6656,14 @@
       </c>
       <c r="T36" s="9">
         <f t="shared" si="6"/>
-        <v>301885</v>
+        <v>301890</v>
       </c>
       <c r="U36" s="8">
-        <v>409703</v>
+        <v>409708</v>
       </c>
       <c r="V36" s="10">
         <f t="shared" si="7"/>
-        <v>0.54946415231995027</v>
+        <v>0.54947085795979567</v>
       </c>
       <c r="W36" s="5">
         <v>686690</v>
@@ -6673,14 +6673,14 @@
       </c>
       <c r="Y36" s="9">
         <f t="shared" si="8"/>
-        <v>276522</v>
+        <v>276528</v>
       </c>
       <c r="Z36" s="8">
-        <v>412183</v>
+        <v>412189</v>
       </c>
       <c r="AA36" s="10">
         <f t="shared" si="9"/>
-        <v>0.60024610814195634</v>
+        <v>0.60025484570912635</v>
       </c>
       <c r="AB36" s="5">
         <v>1408098</v>
@@ -6690,14 +6690,14 @@
       </c>
       <c r="AD36" s="9">
         <f t="shared" si="10"/>
-        <v>511498</v>
+        <v>511512</v>
       </c>
       <c r="AE36" s="8">
-        <v>1248564</v>
+        <v>1248578</v>
       </c>
       <c r="AF36" s="10">
         <f t="shared" si="11"/>
-        <v>0.8867024880370542</v>
+        <v>0.88671243052685256</v>
       </c>
       <c r="AG36" s="5">
         <v>587071</v>
@@ -6707,14 +6707,14 @@
       </c>
       <c r="AI36" s="9">
         <f t="shared" si="12"/>
-        <v>248200</v>
+        <v>248206</v>
       </c>
       <c r="AJ36" s="8">
-        <v>417507</v>
+        <v>417513</v>
       </c>
       <c r="AK36" s="10">
         <f t="shared" si="13"/>
-        <v>0.71116951782663429</v>
+        <v>0.71117973805553336</v>
       </c>
       <c r="AL36" s="5">
         <v>562582</v>
@@ -6724,14 +6724,14 @@
       </c>
       <c r="AN36" s="9">
         <f t="shared" si="14"/>
-        <v>238180</v>
+        <v>238185</v>
       </c>
       <c r="AO36" s="8">
-        <v>421199</v>
+        <v>421204</v>
       </c>
       <c r="AP36" s="10">
         <f t="shared" si="15"/>
-        <v>0.74868907999189449</v>
+        <v>0.74869796758516982</v>
       </c>
       <c r="AQ36" s="22">
         <v>1406326</v>
@@ -6741,14 +6741,14 @@
       </c>
       <c r="AS36" s="9">
         <f t="shared" si="16"/>
-        <v>335764</v>
+        <v>335774</v>
       </c>
       <c r="AT36" s="8">
-        <v>1284252</v>
+        <v>1284262</v>
       </c>
       <c r="AU36" s="10">
         <f t="shared" si="17"/>
-        <v>0.91319651346842767</v>
+        <v>0.91320362419524348</v>
       </c>
       <c r="AV36" s="22">
         <v>685313</v>
@@ -6758,14 +6758,14 @@
       </c>
       <c r="AX36" s="9">
         <f t="shared" si="18"/>
-        <v>333899</v>
+        <v>333905</v>
       </c>
       <c r="AY36" s="9">
-        <v>603407</v>
+        <v>603413</v>
       </c>
       <c r="AZ36" s="10">
         <f t="shared" si="19"/>
-        <v>0.88048380812854854</v>
+        <v>0.88049256325211989</v>
       </c>
       <c r="BA36" s="22">
         <v>667446</v>
@@ -6775,14 +6775,14 @@
       </c>
       <c r="BC36" s="9">
         <f t="shared" si="20"/>
-        <v>306855</v>
+        <v>306863</v>
       </c>
       <c r="BD36" s="8">
-        <v>617045</v>
+        <v>617053</v>
       </c>
       <c r="BE36" s="10">
         <f t="shared" si="21"/>
-        <v>0.9244867749600717</v>
+        <v>0.92449876094845129</v>
       </c>
       <c r="BF36" s="9">
         <v>1363993</v>
@@ -6792,14 +6792,14 @@
       </c>
       <c r="BH36" s="9">
         <f t="shared" si="22"/>
-        <v>656312</v>
+        <v>656322</v>
       </c>
       <c r="BI36" s="6">
-        <v>1309777</v>
+        <v>1309787</v>
       </c>
       <c r="BJ36" s="10">
         <f t="shared" si="23"/>
-        <v>0.960251995428129</v>
+        <v>0.96025932684405269</v>
       </c>
     </row>
     <row r="37" spans="1:63" x14ac:dyDescent="0.3">
@@ -6817,14 +6817,14 @@
       </c>
       <c r="E37" s="9">
         <f t="shared" si="0"/>
-        <v>126097</v>
+        <v>126105</v>
       </c>
       <c r="F37" s="8">
-        <v>409800</v>
+        <v>409808</v>
       </c>
       <c r="G37" s="10">
         <f t="shared" si="1"/>
-        <v>0.55924320665523986</v>
+        <v>0.55925412404336383</v>
       </c>
       <c r="H37" s="5">
         <v>674591</v>
@@ -6834,14 +6834,14 @@
       </c>
       <c r="J37" s="9">
         <f t="shared" si="2"/>
-        <v>147511</v>
+        <v>147517</v>
       </c>
       <c r="K37" s="8">
-        <v>413309</v>
+        <v>413315</v>
       </c>
       <c r="L37" s="10">
         <f t="shared" si="3"/>
-        <v>0.61268086885238615</v>
+        <v>0.61268976313054868</v>
       </c>
       <c r="M37" s="5">
         <v>737436</v>
@@ -6851,14 +6851,14 @@
       </c>
       <c r="O37" s="9">
         <f t="shared" si="4"/>
-        <v>346104</v>
+        <v>346117</v>
       </c>
       <c r="P37" s="8">
-        <v>645255</v>
+        <v>645268</v>
       </c>
       <c r="Q37" s="10">
         <f t="shared" si="5"/>
-        <v>0.87499796592517864</v>
+        <v>0.87501559457363076</v>
       </c>
       <c r="R37" s="5">
         <v>540612</v>
@@ -6868,14 +6868,14 @@
       </c>
       <c r="T37" s="9">
         <f t="shared" si="6"/>
-        <v>330382</v>
+        <v>330392</v>
       </c>
       <c r="U37" s="8">
-        <v>420075</v>
+        <v>420085</v>
       </c>
       <c r="V37" s="10">
         <f t="shared" si="7"/>
-        <v>0.77703602583738429</v>
+        <v>0.77705452339200753</v>
       </c>
       <c r="W37" s="5">
         <v>536259</v>
@@ -6885,14 +6885,14 @@
       </c>
       <c r="Y37" s="9">
         <f t="shared" si="8"/>
-        <v>307341</v>
+        <v>307349</v>
       </c>
       <c r="Z37" s="8">
-        <v>423770</v>
+        <v>423778</v>
       </c>
       <c r="AA37" s="10">
         <f t="shared" si="9"/>
-        <v>0.79023382358151562</v>
+        <v>0.7902487417460593</v>
       </c>
       <c r="AB37" s="5">
         <v>768520</v>
@@ -6902,14 +6902,14 @@
       </c>
       <c r="AD37" s="9">
         <f t="shared" si="10"/>
-        <v>226278</v>
+        <v>226292</v>
       </c>
       <c r="AE37" s="8">
-        <v>661216</v>
+        <v>661230</v>
       </c>
       <c r="AF37" s="10">
         <f t="shared" si="11"/>
-        <v>0.86037578722739816</v>
+        <v>0.86039400405975119</v>
       </c>
       <c r="AG37" s="5">
         <v>524373</v>
@@ -6919,14 +6919,14 @@
       </c>
       <c r="AI37" s="9">
         <f t="shared" si="12"/>
-        <v>282810</v>
+        <v>282817</v>
       </c>
       <c r="AJ37" s="8">
-        <v>431783</v>
+        <v>431790</v>
       </c>
       <c r="AK37" s="10">
         <f t="shared" si="13"/>
-        <v>0.82342721688569009</v>
+        <v>0.82344056616187333</v>
       </c>
       <c r="AL37" s="5">
         <v>516478</v>
@@ -6936,14 +6936,14 @@
       </c>
       <c r="AN37" s="9">
         <f t="shared" si="14"/>
-        <v>277998</v>
+        <v>278004</v>
       </c>
       <c r="AO37" s="8">
-        <v>437371</v>
+        <v>437377</v>
       </c>
       <c r="AP37" s="10">
         <f t="shared" si="15"/>
-        <v>0.84683374703278746</v>
+        <v>0.84684536417814504</v>
       </c>
       <c r="AQ37" s="22">
         <v>769503</v>
@@ -6953,14 +6953,14 @@
       </c>
       <c r="AS37" s="9">
         <f t="shared" si="16"/>
-        <v>145912</v>
+        <v>145927</v>
       </c>
       <c r="AT37" s="8">
-        <v>682719</v>
+        <v>682734</v>
       </c>
       <c r="AU37" s="10">
         <f t="shared" si="17"/>
-        <v>0.8872207125898145</v>
+        <v>0.88724020569120587</v>
       </c>
       <c r="AV37" s="22">
         <v>526610</v>
@@ -6970,14 +6970,14 @@
       </c>
       <c r="AX37" s="9">
         <f t="shared" si="18"/>
-        <v>255396</v>
+        <v>255403</v>
       </c>
       <c r="AY37" s="9">
-        <v>463251</v>
+        <v>463258</v>
       </c>
       <c r="AZ37" s="10">
         <f t="shared" si="19"/>
-        <v>0.87968515599779729</v>
+        <v>0.87969844856725088</v>
       </c>
       <c r="BA37" s="22">
         <v>525208</v>
@@ -6987,14 +6987,14 @@
       </c>
       <c r="BC37" s="9">
         <f t="shared" si="20"/>
-        <v>248171</v>
+        <v>248176</v>
       </c>
       <c r="BD37" s="8">
-        <v>471690</v>
+        <v>471695</v>
       </c>
       <c r="BE37" s="10">
         <f t="shared" si="21"/>
-        <v>0.89810132366605233</v>
+        <v>0.89811084370382777</v>
       </c>
       <c r="BF37" s="9">
         <v>765317</v>
@@ -7004,14 +7004,14 @@
       </c>
       <c r="BH37" s="9">
         <f t="shared" si="22"/>
-        <v>359926</v>
+        <v>359931</v>
       </c>
       <c r="BI37" s="6">
-        <v>707095</v>
+        <v>707100</v>
       </c>
       <c r="BJ37" s="10">
         <f t="shared" si="23"/>
-        <v>0.92392433462212387</v>
+        <v>0.92393086786259815</v>
       </c>
     </row>
     <row r="38" spans="1:63" x14ac:dyDescent="0.3">
@@ -7216,14 +7216,14 @@
       </c>
       <c r="BH38" s="9">
         <f t="shared" si="22"/>
-        <v>16722</v>
+        <v>16723</v>
       </c>
       <c r="BI38" s="6">
-        <v>31047</v>
+        <v>31048</v>
       </c>
       <c r="BJ38" s="10">
         <f t="shared" si="23"/>
-        <v>0.87557460729292991</v>
+        <v>0.87560280887785891</v>
       </c>
     </row>
     <row r="39" spans="1:63" x14ac:dyDescent="0.3">
@@ -7453,14 +7453,14 @@
       </c>
       <c r="E40" s="9">
         <f t="shared" si="0"/>
-        <v>58086</v>
+        <v>58090</v>
       </c>
       <c r="F40" s="8">
-        <v>174007</v>
+        <v>174011</v>
       </c>
       <c r="G40" s="10">
         <f t="shared" si="1"/>
-        <v>0.57364818978419829</v>
+        <v>0.5736613765684031</v>
       </c>
       <c r="H40" s="5">
         <v>287028</v>
@@ -7470,14 +7470,14 @@
       </c>
       <c r="J40" s="9">
         <f t="shared" si="2"/>
-        <v>72966</v>
+        <v>72969</v>
       </c>
       <c r="K40" s="8">
-        <v>174658</v>
+        <v>174661</v>
       </c>
       <c r="L40" s="10">
         <f t="shared" si="3"/>
-        <v>0.60850509357972049</v>
+        <v>0.60851554552169129</v>
       </c>
       <c r="M40" s="5">
         <v>303033</v>
@@ -7487,14 +7487,14 @@
       </c>
       <c r="O40" s="9">
         <f t="shared" si="4"/>
-        <v>166281</v>
+        <v>166286</v>
       </c>
       <c r="P40" s="8">
-        <v>273167</v>
+        <v>273172</v>
       </c>
       <c r="Q40" s="10">
         <f t="shared" si="5"/>
-        <v>0.90144307715661331</v>
+        <v>0.90145957700976465</v>
       </c>
       <c r="R40" s="5">
         <v>226941</v>
@@ -7504,14 +7504,14 @@
       </c>
       <c r="T40" s="9">
         <f t="shared" si="6"/>
-        <v>150774</v>
+        <v>150778</v>
       </c>
       <c r="U40" s="8">
-        <v>177636</v>
+        <v>177640</v>
       </c>
       <c r="V40" s="10">
         <f t="shared" si="7"/>
-        <v>0.78274088860100199</v>
+        <v>0.78275851432751242</v>
       </c>
       <c r="W40" s="5">
         <v>224663</v>
@@ -7521,14 +7521,14 @@
       </c>
       <c r="Y40" s="9">
         <f t="shared" si="8"/>
-        <v>132203</v>
+        <v>132207</v>
       </c>
       <c r="Z40" s="8">
-        <v>179928</v>
+        <v>179932</v>
       </c>
       <c r="AA40" s="10">
         <f t="shared" si="9"/>
-        <v>0.80087953957705538</v>
+        <v>0.80089734402193513</v>
       </c>
       <c r="AB40" s="5">
         <v>313197</v>
@@ -7538,14 +7538,14 @@
       </c>
       <c r="AD40" s="9">
         <f t="shared" si="10"/>
-        <v>87371</v>
+        <v>87376</v>
       </c>
       <c r="AE40" s="8">
-        <v>280657</v>
+        <v>280662</v>
       </c>
       <c r="AF40" s="10">
         <f t="shared" si="11"/>
-        <v>0.8961037302400725</v>
+        <v>0.89611969463309038</v>
       </c>
       <c r="AG40" s="5">
         <v>217708</v>
@@ -7555,14 +7555,14 @@
       </c>
       <c r="AI40" s="9">
         <f t="shared" si="12"/>
-        <v>92088</v>
+        <v>92093</v>
       </c>
       <c r="AJ40" s="8">
-        <v>184511</v>
+        <v>184516</v>
       </c>
       <c r="AK40" s="10">
         <f t="shared" si="13"/>
-        <v>0.84751593878038478</v>
+        <v>0.8475389053227258</v>
       </c>
       <c r="AL40" s="5">
         <v>217966</v>
@@ -7572,14 +7572,14 @@
       </c>
       <c r="AN40" s="9">
         <f t="shared" si="14"/>
-        <v>88623</v>
+        <v>88626</v>
       </c>
       <c r="AO40" s="8">
-        <v>187516</v>
+        <v>187519</v>
       </c>
       <c r="AP40" s="10">
         <f t="shared" si="15"/>
-        <v>0.8602993127368489</v>
+        <v>0.86031307635135756</v>
       </c>
       <c r="AQ40" s="22">
         <v>320883</v>
@@ -7589,14 +7589,14 @@
       </c>
       <c r="AS40" s="9">
         <f t="shared" si="16"/>
-        <v>54264</v>
+        <v>54269</v>
       </c>
       <c r="AT40" s="8">
-        <v>291076</v>
+        <v>291081</v>
       </c>
       <c r="AU40" s="10">
         <f t="shared" si="17"/>
-        <v>0.90710944487554657</v>
+        <v>0.90712502687895591</v>
       </c>
       <c r="AV40" s="22">
         <v>237287</v>
@@ -7606,14 +7606,14 @@
       </c>
       <c r="AX40" s="9">
         <f t="shared" si="18"/>
-        <v>104141</v>
+        <v>104145</v>
       </c>
       <c r="AY40" s="9">
-        <v>212771</v>
+        <v>212775</v>
       </c>
       <c r="AZ40" s="10">
         <f t="shared" si="19"/>
-        <v>0.89668207697851121</v>
+        <v>0.89669893420204227</v>
       </c>
       <c r="BA40" s="22">
         <v>231690</v>
@@ -7623,14 +7623,14 @@
       </c>
       <c r="BC40" s="9">
         <f t="shared" si="20"/>
-        <v>100495</v>
+        <v>100500</v>
       </c>
       <c r="BD40" s="8">
-        <v>215377</v>
+        <v>215382</v>
       </c>
       <c r="BE40" s="10">
         <f t="shared" si="21"/>
-        <v>0.92959126418921834</v>
+        <v>0.92961284474944972</v>
       </c>
       <c r="BF40" s="9">
         <v>314391</v>
@@ -7640,14 +7640,14 @@
       </c>
       <c r="BH40" s="9">
         <f t="shared" si="22"/>
-        <v>147483</v>
+        <v>147488</v>
       </c>
       <c r="BI40" s="6">
-        <v>298971</v>
+        <v>298976</v>
       </c>
       <c r="BJ40" s="10">
         <f t="shared" si="23"/>
-        <v>0.95095279445022285</v>
+        <v>0.95096869821337127</v>
       </c>
     </row>
     <row r="41" spans="1:63" x14ac:dyDescent="0.3">
@@ -7665,14 +7665,14 @@
       </c>
       <c r="E41" s="9">
         <f t="shared" si="0"/>
-        <v>174744</v>
+        <v>174780</v>
       </c>
       <c r="F41" s="8">
-        <v>589435</v>
+        <v>589471</v>
       </c>
       <c r="G41" s="10">
         <f t="shared" si="1"/>
-        <v>0.67352530826179313</v>
+        <v>0.67356644411408795</v>
       </c>
       <c r="H41" s="5">
         <v>834053</v>
@@ -7682,14 +7682,14 @@
       </c>
       <c r="J41" s="9">
         <f t="shared" si="2"/>
-        <v>212047</v>
+        <v>212077</v>
       </c>
       <c r="K41" s="8">
-        <v>593128</v>
+        <v>593158</v>
       </c>
       <c r="L41" s="10">
         <f t="shared" si="3"/>
-        <v>0.71113945996237649</v>
+        <v>0.71117542889960228</v>
       </c>
       <c r="M41" s="5">
         <v>879453</v>
@@ -7699,14 +7699,14 @@
       </c>
       <c r="O41" s="9">
         <f t="shared" si="4"/>
-        <v>392381</v>
+        <v>392436</v>
       </c>
       <c r="P41" s="8">
-        <v>788465</v>
+        <v>788520</v>
       </c>
       <c r="Q41" s="10">
         <f t="shared" si="5"/>
-        <v>0.89654023580566555</v>
+        <v>0.89660277467926086</v>
       </c>
       <c r="R41" s="5">
         <v>738453</v>
@@ -7716,14 +7716,14 @@
       </c>
       <c r="T41" s="9">
         <f t="shared" si="6"/>
-        <v>486287</v>
+        <v>486316</v>
       </c>
       <c r="U41" s="8">
-        <v>605655</v>
+        <v>605684</v>
       </c>
       <c r="V41" s="10">
         <f t="shared" si="7"/>
-        <v>0.82016729568435631</v>
+        <v>0.82020656697176397</v>
       </c>
       <c r="W41" s="5">
         <v>740008</v>
@@ -7733,14 +7733,14 @@
       </c>
       <c r="Y41" s="9">
         <f t="shared" si="8"/>
-        <v>428172</v>
+        <v>428204</v>
       </c>
       <c r="Z41" s="8">
-        <v>611289</v>
+        <v>611321</v>
       </c>
       <c r="AA41" s="10">
         <f t="shared" si="9"/>
-        <v>0.82605728586717986</v>
+        <v>0.8261005286429336</v>
       </c>
       <c r="AB41" s="5">
         <v>928683</v>
@@ -7750,14 +7750,14 @@
       </c>
       <c r="AD41" s="9">
         <f t="shared" si="10"/>
-        <v>220714</v>
+        <v>220763</v>
       </c>
       <c r="AE41" s="8">
-        <v>813232</v>
+        <v>813281</v>
       </c>
       <c r="AF41" s="10">
         <f t="shared" si="11"/>
-        <v>0.87568309100091202</v>
+        <v>0.87573585389201702</v>
       </c>
       <c r="AG41" s="5">
         <v>734303</v>
@@ -7767,14 +7767,14 @@
       </c>
       <c r="AI41" s="9">
         <f t="shared" si="12"/>
-        <v>376576</v>
+        <v>376605</v>
       </c>
       <c r="AJ41" s="8">
-        <v>623735</v>
+        <v>623764</v>
       </c>
       <c r="AK41" s="10">
         <f t="shared" si="13"/>
-        <v>0.84942455634799263</v>
+        <v>0.84946404958171218</v>
       </c>
       <c r="AL41" s="5">
         <v>728636</v>
@@ -7784,14 +7784,14 @@
       </c>
       <c r="AN41" s="9">
         <f t="shared" si="14"/>
-        <v>357965</v>
+        <v>357990</v>
       </c>
       <c r="AO41" s="8">
-        <v>631386</v>
+        <v>631411</v>
       </c>
       <c r="AP41" s="10">
         <f t="shared" si="15"/>
-        <v>0.86653143682167777</v>
+        <v>0.86656574750629944</v>
       </c>
       <c r="AQ41" s="22">
         <v>923873</v>
@@ -7801,14 +7801,14 @@
       </c>
       <c r="AS41" s="9">
         <f t="shared" si="16"/>
-        <v>140547</v>
+        <v>140586</v>
       </c>
       <c r="AT41" s="8">
-        <v>842154</v>
+        <v>842193</v>
       </c>
       <c r="AU41" s="10">
         <f t="shared" si="17"/>
-        <v>0.91154736635879607</v>
+        <v>0.91158957995308876</v>
       </c>
       <c r="AV41" s="22">
         <v>726271</v>
@@ -7818,14 +7818,14 @@
       </c>
       <c r="AX41" s="9">
         <f t="shared" si="18"/>
-        <v>325977</v>
+        <v>326001</v>
       </c>
       <c r="AY41" s="9">
-        <v>662974</v>
+        <v>662998</v>
       </c>
       <c r="AZ41" s="10">
         <f t="shared" si="19"/>
-        <v>0.91284658206096625</v>
+        <v>0.91287962757703389</v>
       </c>
       <c r="BA41" s="22">
         <v>715104</v>
@@ -7835,14 +7835,14 @@
       </c>
       <c r="BC41" s="9">
         <f t="shared" si="20"/>
-        <v>312324</v>
+        <v>312348</v>
       </c>
       <c r="BD41" s="8">
-        <v>671082</v>
+        <v>671106</v>
       </c>
       <c r="BE41" s="10">
         <f t="shared" si="21"/>
-        <v>0.93843972345281246</v>
+        <v>0.93847328500469862</v>
       </c>
       <c r="BF41" s="9">
         <v>910875</v>
@@ -7852,14 +7852,14 @@
       </c>
       <c r="BH41" s="9">
         <f t="shared" si="22"/>
-        <v>398006</v>
+        <v>398032</v>
       </c>
       <c r="BI41" s="6">
-        <v>867217</v>
+        <v>867243</v>
       </c>
       <c r="BJ41" s="10">
         <f t="shared" si="23"/>
-        <v>0.95207026211060797</v>
+        <v>0.95209880609304243</v>
       </c>
     </row>
     <row r="42" spans="1:63" x14ac:dyDescent="0.3">
@@ -7962,14 +7962,14 @@
       </c>
       <c r="AD42" s="9">
         <f t="shared" si="10"/>
-        <v>5508</v>
+        <v>5509</v>
       </c>
       <c r="AE42" s="8">
-        <v>17334</v>
+        <v>17335</v>
       </c>
       <c r="AF42" s="10">
         <f t="shared" si="11"/>
-        <v>0.85930993456276028</v>
+        <v>0.85935950822922869</v>
       </c>
       <c r="AG42" s="5">
         <v>15422</v>
@@ -8013,14 +8013,14 @@
       </c>
       <c r="AS42" s="9">
         <f t="shared" si="16"/>
-        <v>3514</v>
+        <v>3515</v>
       </c>
       <c r="AT42" s="8">
-        <v>17764</v>
+        <v>17765</v>
       </c>
       <c r="AU42" s="10">
         <f t="shared" si="17"/>
-        <v>0.88163184277135342</v>
+        <v>0.88168147302595667</v>
       </c>
       <c r="AV42" s="22">
         <v>15728</v>
@@ -8030,14 +8030,14 @@
       </c>
       <c r="AX42" s="9">
         <f t="shared" si="18"/>
-        <v>7276</v>
+        <v>7277</v>
       </c>
       <c r="AY42" s="9">
-        <v>14027</v>
+        <v>14028</v>
       </c>
       <c r="AZ42" s="10">
         <f t="shared" si="19"/>
-        <v>0.89184893184130209</v>
+        <v>0.891912512716175</v>
       </c>
       <c r="BA42" s="22">
         <v>15666</v>
@@ -8352,14 +8352,14 @@
       </c>
       <c r="T44" s="9">
         <f t="shared" si="6"/>
-        <v>159514</v>
+        <v>159515</v>
       </c>
       <c r="U44" s="8">
-        <v>196738</v>
+        <v>196739</v>
       </c>
       <c r="V44" s="10">
         <f t="shared" si="7"/>
-        <v>0.69062621766496179</v>
+        <v>0.69062972805043721</v>
       </c>
       <c r="W44" s="5">
         <v>281986</v>
@@ -8437,14 +8437,14 @@
       </c>
       <c r="AS44" s="9">
         <f t="shared" si="16"/>
-        <v>79475</v>
+        <v>79476</v>
       </c>
       <c r="AT44" s="8">
-        <v>306660</v>
+        <v>306661</v>
       </c>
       <c r="AU44" s="10">
         <f t="shared" si="17"/>
-        <v>0.80443216784317428</v>
+        <v>0.80443479104857385</v>
       </c>
       <c r="AV44" s="22">
         <v>286200</v>
@@ -8454,14 +8454,14 @@
       </c>
       <c r="AX44" s="9">
         <f t="shared" si="18"/>
-        <v>140924</v>
+        <v>140926</v>
       </c>
       <c r="AY44" s="9">
-        <v>225300</v>
+        <v>225302</v>
       </c>
       <c r="AZ44" s="10">
         <f t="shared" si="19"/>
-        <v>0.78721174004192873</v>
+        <v>0.78721872816212435</v>
       </c>
       <c r="BA44" s="22">
         <v>282748</v>
@@ -8471,14 +8471,14 @@
       </c>
       <c r="BC44" s="9">
         <f t="shared" si="20"/>
-        <v>139542</v>
+        <v>139544</v>
       </c>
       <c r="BD44" s="8">
-        <v>229341</v>
+        <v>229343</v>
       </c>
       <c r="BE44" s="10">
         <f t="shared" si="21"/>
-        <v>0.8111144906418436</v>
+        <v>0.81112156407826053</v>
       </c>
       <c r="BF44" s="9">
         <v>372165</v>
@@ -8488,14 +8488,14 @@
       </c>
       <c r="BH44" s="9">
         <f t="shared" si="22"/>
-        <v>189929</v>
+        <v>189931</v>
       </c>
       <c r="BI44" s="6">
-        <v>317817</v>
+        <v>317819</v>
       </c>
       <c r="BJ44" s="10">
         <f t="shared" si="23"/>
-        <v>0.85396799806537427</v>
+        <v>0.85397337202584878</v>
       </c>
     </row>
     <row r="45" spans="1:63" x14ac:dyDescent="0.3">
@@ -8598,14 +8598,14 @@
       </c>
       <c r="AD45" s="9">
         <f t="shared" si="10"/>
-        <v>84797</v>
+        <v>84798</v>
       </c>
       <c r="AE45" s="8">
-        <v>245745</v>
+        <v>245746</v>
       </c>
       <c r="AF45" s="10">
         <f t="shared" si="11"/>
-        <v>0.84216352184015186</v>
+        <v>0.84216694882146115</v>
       </c>
       <c r="AG45" s="5">
         <v>216277</v>
@@ -8649,14 +8649,14 @@
       </c>
       <c r="AS45" s="9">
         <f t="shared" si="16"/>
-        <v>52919</v>
+        <v>52920</v>
       </c>
       <c r="AT45" s="8">
-        <v>255705</v>
+        <v>255706</v>
       </c>
       <c r="AU45" s="10">
         <f t="shared" si="17"/>
-        <v>0.85997511266563531</v>
+        <v>0.85997847581892783</v>
       </c>
       <c r="AV45" s="22">
         <v>215263</v>
@@ -8666,14 +8666,14 @@
       </c>
       <c r="AX45" s="9">
         <f t="shared" si="18"/>
-        <v>99766</v>
+        <v>99767</v>
       </c>
       <c r="AY45" s="9">
-        <v>182757</v>
+        <v>182758</v>
       </c>
       <c r="AZ45" s="10">
         <f t="shared" si="19"/>
-        <v>0.84899402126700829</v>
+        <v>0.84899866674718827</v>
       </c>
       <c r="BA45" s="22">
         <v>211125</v>
@@ -8700,14 +8700,14 @@
       </c>
       <c r="BH45" s="9">
         <f t="shared" si="22"/>
-        <v>145218</v>
+        <v>145219</v>
       </c>
       <c r="BI45" s="6">
-        <v>262772</v>
+        <v>262773</v>
       </c>
       <c r="BJ45" s="10">
         <f t="shared" si="23"/>
-        <v>0.90391601078760531</v>
+        <v>0.90391945071275248</v>
       </c>
     </row>
     <row r="46" spans="1:63" x14ac:dyDescent="0.3">
@@ -9149,15 +9149,15 @@
       </c>
       <c r="E48" s="18">
         <f t="shared" si="0"/>
-        <v>1253742</v>
+        <v>1253819</v>
       </c>
       <c r="F48" s="20">
         <f>SUM(F10:F47)</f>
-        <v>3917899</v>
+        <v>3917976</v>
       </c>
       <c r="G48" s="19">
         <f t="shared" si="1"/>
-        <v>0.37683287560135631</v>
+        <v>0.37684028164511124</v>
       </c>
       <c r="H48" s="20">
         <f>SUM(H10:H47)</f>
@@ -9169,15 +9169,15 @@
       </c>
       <c r="J48" s="18">
         <f t="shared" si="2"/>
-        <v>1452574</v>
+        <v>1452641</v>
       </c>
       <c r="K48" s="20">
         <f>SUM(K10:K47)</f>
-        <v>3929350</v>
+        <v>3929417</v>
       </c>
       <c r="L48" s="19">
         <f t="shared" si="3"/>
-        <v>0.40922054543646219</v>
+        <v>0.40922752312400446</v>
       </c>
       <c r="M48" s="20">
         <f>SUM(M10:M47)</f>
@@ -9189,15 +9189,15 @@
       </c>
       <c r="O48" s="18">
         <f t="shared" si="4"/>
-        <v>5094140</v>
+        <v>5094271</v>
       </c>
       <c r="P48" s="20">
         <f>SUM(P10:P47)</f>
-        <v>9212459</v>
+        <v>9212590</v>
       </c>
       <c r="Q48" s="19">
         <f t="shared" si="5"/>
-        <v>0.88597531144875619</v>
+        <v>0.88598790990545484</v>
       </c>
       <c r="R48" s="20">
         <f>SUM(R10:R47)</f>
@@ -9209,15 +9209,15 @@
       </c>
       <c r="T48" s="18">
         <f t="shared" si="6"/>
-        <v>3085003</v>
+        <v>3085075</v>
       </c>
       <c r="U48" s="20">
         <f>SUM(U10:U47)</f>
-        <v>4004772</v>
+        <v>4004844</v>
       </c>
       <c r="V48" s="19">
         <f t="shared" si="7"/>
-        <v>0.6660981640091912</v>
+        <v>0.66611013948939546</v>
       </c>
       <c r="W48" s="20">
         <f>SUM(W10:W47)</f>
@@ -9229,15 +9229,15 @@
       </c>
       <c r="Y48" s="18">
         <f t="shared" si="8"/>
-        <v>2823396</v>
+        <v>2823472</v>
       </c>
       <c r="Z48" s="20">
         <f>SUM(Z10:Z47)</f>
-        <v>4037053</v>
+        <v>4037129</v>
       </c>
       <c r="AA48" s="19">
         <f t="shared" si="9"/>
-        <v>0.69477218758637216</v>
+        <v>0.69478526709913957</v>
       </c>
       <c r="AB48" s="20">
         <f>SUM(AB10:AB47)</f>
@@ -9249,15 +9249,15 @@
       </c>
       <c r="AD48" s="18">
         <f t="shared" si="10"/>
-        <v>3618285</v>
+        <v>3618419</v>
       </c>
       <c r="AE48" s="20">
         <f>SUM(AE10:AE47)</f>
-        <v>9489307</v>
+        <v>9489441</v>
       </c>
       <c r="AF48" s="19">
         <f t="shared" si="11"/>
-        <v>0.87450942336590731</v>
+        <v>0.87452177245132845</v>
       </c>
       <c r="AG48" s="20">
         <f>SUM(AG10:AG47)</f>
@@ -9269,15 +9269,15 @@
       </c>
       <c r="AI48" s="18">
         <f t="shared" si="12"/>
-        <v>2580153</v>
+        <v>2580225</v>
       </c>
       <c r="AJ48" s="20">
         <f>SUM(AJ10:AJ47)</f>
-        <v>4110385</v>
+        <v>4110457</v>
       </c>
       <c r="AK48" s="19">
         <f t="shared" si="13"/>
-        <v>0.75239141043518565</v>
+        <v>0.75240458978007696</v>
       </c>
       <c r="AL48" s="20">
         <f>SUM(AL10:AL47)</f>
@@ -9289,15 +9289,15 @@
       </c>
       <c r="AN48" s="18">
         <f t="shared" si="14"/>
-        <v>2523264</v>
+        <v>2523334</v>
       </c>
       <c r="AO48" s="20">
         <f>SUM(AO10:AO47)</f>
-        <v>4159134</v>
+        <v>4159204</v>
       </c>
       <c r="AP48" s="19">
         <f t="shared" si="15"/>
-        <v>0.7776605642503811</v>
+        <v>0.77767365260951959</v>
       </c>
       <c r="AQ48" s="20">
         <f>SUM(AQ10:AQ47)</f>
@@ -9309,15 +9309,15 @@
       </c>
       <c r="AS48" s="18">
         <f t="shared" si="16"/>
-        <v>2270692</v>
+        <v>2270820</v>
       </c>
       <c r="AT48" s="20">
         <f>SUM(AT10:AT47)</f>
-        <v>9815764</v>
+        <v>9815892</v>
       </c>
       <c r="AU48" s="19">
         <f t="shared" si="17"/>
-        <v>0.89362461437841612</v>
+        <v>0.89363626746529157</v>
       </c>
       <c r="AV48" s="20">
         <f>SUM(AV10:AV47)</f>
@@ -9329,15 +9329,15 @@
       </c>
       <c r="AX48" s="18">
         <f t="shared" si="18"/>
-        <v>2882269</v>
+        <v>2882356</v>
       </c>
       <c r="AY48" s="20">
         <f>SUM(AY10:AY47)</f>
-        <v>5362542</v>
+        <v>5362629</v>
       </c>
       <c r="AZ48" s="19">
         <f t="shared" si="19"/>
-        <v>0.85630096847080617</v>
+        <v>0.8563148607972918</v>
       </c>
       <c r="BA48" s="20">
         <f>SUM(BA10:BA47)</f>
@@ -9349,15 +9349,15 @@
       </c>
       <c r="BC48" s="18">
         <f t="shared" si="20"/>
-        <v>2728186</v>
+        <v>2728272</v>
       </c>
       <c r="BD48" s="20">
         <f>SUM(BD10:BD47)</f>
-        <v>5477530</v>
+        <v>5477616</v>
       </c>
       <c r="BE48" s="19">
         <f t="shared" si="21"/>
-        <v>0.89258660975870885</v>
+        <v>0.89260062382133176</v>
       </c>
       <c r="BF48" s="20">
         <f>SUM(BF10:BF47)</f>
@@ -9369,15 +9369,15 @@
       </c>
       <c r="BH48" s="18">
         <f t="shared" si="22"/>
-        <v>4902517</v>
+        <v>4902614</v>
       </c>
       <c r="BI48" s="20">
         <f>SUM(BI10:BI47)</f>
-        <v>10081838</v>
+        <v>10081935</v>
       </c>
       <c r="BJ48" s="19">
         <f t="shared" si="23"/>
-        <v>0.9352716148667346</v>
+        <v>0.9352806133595335</v>
       </c>
       <c r="BK48"/>
     </row>
@@ -9389,17 +9389,15 @@
     <row r="54" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="55" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="56" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="57" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="58" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="32" t="s">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A57" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="B59" s="32"/>
-      <c r="C59" s="32"/>
-      <c r="D59" s="32"/>
-      <c r="E59" s="32"/>
-      <c r="F59" s="3"/>
+      <c r="B57" s="32"/>
+      <c r="C57" s="32"/>
+      <c r="D57" s="32"/>
+      <c r="E57" s="32"/>
+      <c r="F57" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="19">
@@ -9418,7 +9416,7 @@
     <mergeCell ref="AG8:AK8"/>
     <mergeCell ref="AL8:AP8"/>
     <mergeCell ref="A48:B48"/>
-    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="A57:E57"/>
     <mergeCell ref="M8:Q8"/>
     <mergeCell ref="R8:V8"/>
     <mergeCell ref="W8:AA8"/>
